--- a/research/traditional_assets/database/data/romania/romania_apparel.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_apparel.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvb_cnte" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.167</v>
+        <v>0.13</v>
       </c>
       <c r="G2">
-        <v>0.2416184971098266</v>
+        <v>-0.05238095238095238</v>
       </c>
       <c r="H2">
-        <v>0.2416184971098266</v>
+        <v>-0.05238095238095238</v>
       </c>
       <c r="I2">
-        <v>-0.146242774566474</v>
+        <v>0.01765873015873016</v>
       </c>
       <c r="J2">
-        <v>-0.146242774566474</v>
+        <v>0.01765873015873016</v>
       </c>
       <c r="K2">
-        <v>-0.304</v>
+        <v>0.02</v>
       </c>
       <c r="L2">
-        <v>-0.1757225433526012</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.095</v>
+        <v>0.149</v>
       </c>
       <c r="V2">
-        <v>0.07539682539682539</v>
+        <v>0.1027586206896552</v>
       </c>
       <c r="W2">
-        <v>-0.1235772357723577</v>
+        <v>0.009523809523809523</v>
       </c>
       <c r="X2">
-        <v>0.07090876954595281</v>
+        <v>0.1395075403412457</v>
       </c>
       <c r="Y2">
-        <v>-0.1944860053183105</v>
+        <v>-0.1299837308174362</v>
       </c>
       <c r="Z2">
-        <v>0.7308829742289819</v>
+        <v>2.513715710723192</v>
       </c>
       <c r="AA2">
-        <v>-0.106886354034643</v>
+        <v>0.04438902743142144</v>
       </c>
       <c r="AB2">
-        <v>0.07090876954595281</v>
+        <v>0.1229497027191641</v>
       </c>
       <c r="AC2">
-        <v>-0.1777951235805958</v>
+        <v>-0.07856067528774263</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="AG2">
-        <v>-0.095</v>
+        <v>0.247</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.2145178764897075</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.180327868852459</v>
       </c>
       <c r="AJ2">
-        <v>-0.0815450643776824</v>
+        <v>0.145550972304066</v>
       </c>
       <c r="AK2">
-        <v>-0.04738154613466335</v>
+        <v>0.1206643869076698</v>
       </c>
       <c r="AL2">
-        <v>0.06</v>
+        <v>0.079</v>
       </c>
       <c r="AM2">
-        <v>0.06</v>
+        <v>0.079</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>2.237288135593221</v>
       </c>
       <c r="AO2">
-        <v>-4.216666666666667</v>
+        <v>1.126582278481013</v>
       </c>
       <c r="AP2">
-        <v>0.6375838926174497</v>
+        <v>1.395480225988701</v>
       </c>
       <c r="AQ2">
-        <v>-4.216666666666667</v>
+        <v>1.126582278481013</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.167</v>
+        <v>0.13</v>
       </c>
       <c r="G3">
-        <v>0.2416184971098266</v>
+        <v>-0.05238095238095238</v>
       </c>
       <c r="H3">
-        <v>0.2416184971098266</v>
+        <v>-0.05238095238095238</v>
       </c>
       <c r="I3">
-        <v>-0.146242774566474</v>
+        <v>0.01765873015873016</v>
       </c>
       <c r="J3">
-        <v>-0.146242774566474</v>
+        <v>0.01765873015873016</v>
       </c>
       <c r="K3">
-        <v>-0.304</v>
+        <v>0.02</v>
       </c>
       <c r="L3">
-        <v>-0.1757225433526012</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.095</v>
+        <v>0.149</v>
       </c>
       <c r="V3">
-        <v>0.07539682539682539</v>
+        <v>0.1027586206896552</v>
       </c>
       <c r="W3">
-        <v>-0.1235772357723577</v>
+        <v>0.009523809523809523</v>
       </c>
       <c r="X3">
-        <v>0.07090876954595281</v>
+        <v>0.1395075403412457</v>
       </c>
       <c r="Y3">
-        <v>-0.1944860053183105</v>
+        <v>-0.1299837308174362</v>
       </c>
       <c r="Z3">
-        <v>0.7308829742289819</v>
+        <v>2.513715710723192</v>
       </c>
       <c r="AA3">
-        <v>-0.106886354034643</v>
+        <v>0.04438902743142144</v>
       </c>
       <c r="AB3">
-        <v>0.07090876954595281</v>
+        <v>0.1229497027191641</v>
       </c>
       <c r="AC3">
-        <v>-0.1777951235805958</v>
+        <v>-0.07856067528774263</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="AG3">
-        <v>-0.095</v>
+        <v>0.247</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.2145178764897075</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.180327868852459</v>
       </c>
       <c r="AJ3">
-        <v>-0.0815450643776824</v>
+        <v>0.145550972304066</v>
       </c>
       <c r="AK3">
-        <v>-0.04738154613466335</v>
+        <v>0.1206643869076698</v>
       </c>
       <c r="AL3">
+        <v>0.079</v>
+      </c>
+      <c r="AM3">
+        <v>0.079</v>
+      </c>
+      <c r="AN3">
+        <v>2.237288135593221</v>
+      </c>
+      <c r="AO3">
+        <v>1.126582278481013</v>
+      </c>
+      <c r="AP3">
+        <v>1.395480225988701</v>
+      </c>
+      <c r="AQ3">
+        <v>1.126582278481013</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S.C. Conted S.A. (BVB:CNTE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVB:CNTE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.214517876489707</v>
+      </c>
+      <c r="F2">
+        <v>0.09</v>
+      </c>
+      <c r="G2">
+        <v>1.45</v>
+      </c>
+      <c r="H2">
+        <v>1.7497780892922</v>
+      </c>
+      <c r="I2">
+        <v>1.697</v>
+      </c>
+      <c r="J2">
+        <v>1.7669180892922</v>
+      </c>
+      <c r="K2">
+        <v>0.396</v>
+      </c>
+      <c r="L2">
+        <v>0.16614</v>
+      </c>
+      <c r="M2">
+        <v>0.122949702719164</v>
+      </c>
+      <c r="N2">
+        <v>0.119619844666159</v>
+      </c>
+      <c r="O2">
+        <v>0.0623212568807339</v>
+      </c>
+      <c r="P2">
+        <v>0.039732</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.139507540341246</v>
+      </c>
+      <c r="T2">
+        <v>0.127520840292482</v>
+      </c>
+      <c r="U2">
+        <v>1.03739983503255</v>
+      </c>
+      <c r="V2">
+        <v>0.913923473570076</v>
+      </c>
+      <c r="W2">
+        <v>11.32542894744008</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1.45</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.07419197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.16</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.177</v>
+      </c>
+      <c r="AH2">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.077</v>
+      </c>
+      <c r="AJ2">
+        <v>0.396</v>
+      </c>
+      <c r="AK2">
+        <v>0.396</v>
+      </c>
+      <c r="AL2">
+        <v>0.079</v>
+      </c>
+      <c r="AM2">
+        <v>0.396</v>
+      </c>
+      <c r="AN2">
+        <v>0.149</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1207155485655019</v>
+      </c>
+      <c r="C2">
+        <v>1.892283760106094</v>
+      </c>
+      <c r="D2">
+        <v>1.743283760106094</v>
+      </c>
+      <c r="E2">
+        <v>-0.396</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.149</v>
+      </c>
+      <c r="H2">
+        <v>1.45</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.177</v>
+      </c>
+      <c r="K2">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L2">
+        <v>0.089</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.089</v>
+      </c>
+      <c r="O2">
+        <v>0.01424</v>
+      </c>
+      <c r="P2">
+        <v>0.07475999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.16276</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1207155485655019</v>
+      </c>
+      <c r="T2">
+        <v>0.8438213889496441</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.16</v>
+      </c>
+      <c r="W2">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1205803636877971</v>
+      </c>
+      <c r="C3">
+        <v>1.876705449441867</v>
+      </c>
+      <c r="D3">
+        <v>1.746165449441867</v>
+      </c>
+      <c r="E3">
+        <v>-0.37754</v>
+      </c>
+      <c r="F3">
+        <v>0.01846</v>
+      </c>
+      <c r="G3">
+        <v>0.149</v>
+      </c>
+      <c r="H3">
+        <v>1.45</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.177</v>
+      </c>
+      <c r="K3">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L3">
+        <v>0.089</v>
+      </c>
+      <c r="M3">
+        <v>0.0008436220000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.08815637799999999</v>
+      </c>
+      <c r="O3">
+        <v>0.01410502048</v>
+      </c>
+      <c r="P3">
+        <v>0.07405135752</v>
+      </c>
+      <c r="Q3">
+        <v>0.16205135752</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1214105895836334</v>
+      </c>
+      <c r="T3">
+        <v>0.8509810855831562</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.16</v>
+      </c>
+      <c r="W3">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>105.4974858408149</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1204451788100923</v>
+      </c>
+      <c r="C4">
+        <v>1.861136681553492</v>
+      </c>
+      <c r="D4">
+        <v>1.749056681553492</v>
+      </c>
+      <c r="E4">
+        <v>-0.35908</v>
+      </c>
+      <c r="F4">
+        <v>0.03692</v>
+      </c>
+      <c r="G4">
+        <v>0.149</v>
+      </c>
+      <c r="H4">
+        <v>1.45</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.177</v>
+      </c>
+      <c r="K4">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.089</v>
+      </c>
+      <c r="M4">
+        <v>0.001687244</v>
+      </c>
+      <c r="N4">
+        <v>0.08731275599999999</v>
+      </c>
+      <c r="O4">
+        <v>0.01397004096</v>
+      </c>
+      <c r="P4">
+        <v>0.07334271503999999</v>
+      </c>
+      <c r="Q4">
+        <v>0.16134271504</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.122119815112339</v>
+      </c>
+      <c r="T4">
+        <v>0.8582868984744951</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.16</v>
+      </c>
+      <c r="W4">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>52.74874292040747</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1203099939323874</v>
+      </c>
+      <c r="C5">
+        <v>1.845577503921247</v>
+      </c>
+      <c r="D5">
+        <v>1.751957503921247</v>
+      </c>
+      <c r="E5">
+        <v>-0.34062</v>
+      </c>
+      <c r="F5">
+        <v>0.05538</v>
+      </c>
+      <c r="G5">
+        <v>0.149</v>
+      </c>
+      <c r="H5">
+        <v>1.45</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.177</v>
+      </c>
+      <c r="K5">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L5">
+        <v>0.089</v>
+      </c>
+      <c r="M5">
+        <v>0.002530866</v>
+      </c>
+      <c r="N5">
+        <v>0.08646913399999999</v>
+      </c>
+      <c r="O5">
+        <v>0.01383506144</v>
+      </c>
+      <c r="P5">
+        <v>0.07263407255999998</v>
+      </c>
+      <c r="Q5">
+        <v>0.16063407256</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1228436638478221</v>
+      </c>
+      <c r="T5">
+        <v>0.8657433466831812</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.16</v>
+      </c>
+      <c r="W5">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>35.16582861360498</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1201748090546826</v>
+      </c>
+      <c r="C6">
+        <v>1.830027964340914</v>
+      </c>
+      <c r="D6">
+        <v>1.754867964340914</v>
+      </c>
+      <c r="E6">
+        <v>-0.32216</v>
+      </c>
+      <c r="F6">
+        <v>0.07384</v>
+      </c>
+      <c r="G6">
+        <v>0.149</v>
+      </c>
+      <c r="H6">
+        <v>1.45</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.177</v>
+      </c>
+      <c r="K6">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L6">
+        <v>0.089</v>
+      </c>
+      <c r="M6">
+        <v>0.003374488000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.085625512</v>
+      </c>
+      <c r="O6">
+        <v>0.01370008192</v>
+      </c>
+      <c r="P6">
+        <v>0.07192543007999999</v>
+      </c>
+      <c r="Q6">
+        <v>0.15992543008</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1235825927652944</v>
+      </c>
+      <c r="T6">
+        <v>0.8733551375628815</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.16</v>
+      </c>
+      <c r="W6">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>26.37437146020374</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1200396241769778</v>
+      </c>
+      <c r="C7">
+        <v>1.814488110926411</v>
+      </c>
+      <c r="D7">
+        <v>1.757788110926411</v>
+      </c>
+      <c r="E7">
+        <v>-0.3037</v>
+      </c>
+      <c r="F7">
+        <v>0.09230000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.149</v>
+      </c>
+      <c r="H7">
+        <v>1.45</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.177</v>
+      </c>
+      <c r="K7">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L7">
+        <v>0.089</v>
+      </c>
+      <c r="M7">
+        <v>0.004218110000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.08478189</v>
+      </c>
+      <c r="O7">
+        <v>0.0135651024</v>
+      </c>
+      <c r="P7">
+        <v>0.0712167876</v>
+      </c>
+      <c r="Q7">
+        <v>0.1592167876</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1243370780810293</v>
+      </c>
+      <c r="T7">
+        <v>0.8811271766716283</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.16</v>
+      </c>
+      <c r="W7">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.09949716816299</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
         <v>0.06</v>
       </c>
-      <c r="AM3">
-        <v>0.06</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-4.216666666666667</v>
-      </c>
-      <c r="AP3">
-        <v>0.6375838926174497</v>
-      </c>
-      <c r="AQ3">
-        <v>-4.216666666666667</v>
+      <c r="B8">
+        <v>0.1199044392992731</v>
+      </c>
+      <c r="C8">
+        <v>1.798957992112442</v>
+      </c>
+      <c r="D8">
+        <v>1.760717992112442</v>
+      </c>
+      <c r="E8">
+        <v>-0.28524</v>
+      </c>
+      <c r="F8">
+        <v>0.11076</v>
+      </c>
+      <c r="G8">
+        <v>0.149</v>
+      </c>
+      <c r="H8">
+        <v>1.45</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.177</v>
+      </c>
+      <c r="K8">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L8">
+        <v>0.089</v>
+      </c>
+      <c r="M8">
+        <v>0.005061732</v>
+      </c>
+      <c r="N8">
+        <v>0.083938268</v>
+      </c>
+      <c r="O8">
+        <v>0.01343012288</v>
+      </c>
+      <c r="P8">
+        <v>0.07050814511999999</v>
+      </c>
+      <c r="Q8">
+        <v>0.15850814512</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1251076162758224</v>
+      </c>
+      <c r="T8">
+        <v>0.8890645783146038</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.16</v>
+      </c>
+      <c r="W8">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>17.58291430680249</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1197692544215682</v>
+      </c>
+      <c r="C9">
+        <v>1.783437656657173</v>
+      </c>
+      <c r="D9">
+        <v>1.763657656657173</v>
+      </c>
+      <c r="E9">
+        <v>-0.26678</v>
+      </c>
+      <c r="F9">
+        <v>0.12922</v>
+      </c>
+      <c r="G9">
+        <v>0.149</v>
+      </c>
+      <c r="H9">
+        <v>1.45</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.177</v>
+      </c>
+      <c r="K9">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L9">
+        <v>0.089</v>
+      </c>
+      <c r="M9">
+        <v>0.005905354000000002</v>
+      </c>
+      <c r="N9">
+        <v>0.08309464599999999</v>
+      </c>
+      <c r="O9">
+        <v>0.01329514336</v>
+      </c>
+      <c r="P9">
+        <v>0.06979950264</v>
+      </c>
+      <c r="Q9">
+        <v>0.15779950264</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.125894725184482</v>
+      </c>
+      <c r="T9">
+        <v>0.8971726767671054</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.16</v>
+      </c>
+      <c r="W9">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.0710694058307</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1196340695438634</v>
+      </c>
+      <c r="C10">
+        <v>1.767927153644936</v>
+      </c>
+      <c r="D10">
+        <v>1.766607153644936</v>
+      </c>
+      <c r="E10">
+        <v>-0.24832</v>
+      </c>
+      <c r="F10">
+        <v>0.14768</v>
+      </c>
+      <c r="G10">
+        <v>0.149</v>
+      </c>
+      <c r="H10">
+        <v>1.45</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.177</v>
+      </c>
+      <c r="K10">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L10">
+        <v>0.089</v>
+      </c>
+      <c r="M10">
+        <v>0.006748976000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.08225102399999999</v>
+      </c>
+      <c r="O10">
+        <v>0.01316016384</v>
+      </c>
+      <c r="P10">
+        <v>0.06909086015999999</v>
+      </c>
+      <c r="Q10">
+        <v>0.15709086016</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1266989451563733</v>
+      </c>
+      <c r="T10">
+        <v>0.9054570382294441</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.16</v>
+      </c>
+      <c r="W10">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.18718573010187</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1196198446661586</v>
+      </c>
+      <c r="C11">
+        <v>1.749778089292201</v>
+      </c>
+      <c r="D11">
+        <v>1.766918089292201</v>
+      </c>
+      <c r="E11">
+        <v>-0.22986</v>
+      </c>
+      <c r="F11">
+        <v>0.16614</v>
+      </c>
+      <c r="G11">
+        <v>0.149</v>
+      </c>
+      <c r="H11">
+        <v>1.45</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.177</v>
+      </c>
+      <c r="K11">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L11">
+        <v>0.089</v>
+      </c>
+      <c r="M11">
+        <v>0.007858422</v>
+      </c>
+      <c r="N11">
+        <v>0.08114157799999999</v>
+      </c>
+      <c r="O11">
+        <v>0.01298265248</v>
+      </c>
+      <c r="P11">
+        <v>0.06815892552</v>
+      </c>
+      <c r="Q11">
+        <v>0.15615892552</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.127520840292482</v>
+      </c>
+      <c r="T11">
+        <v>0.9139234735700761</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.16</v>
+      </c>
+      <c r="W11">
+        <v>0.039732</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.32542894744008</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1198172997884538</v>
+      </c>
+      <c r="C12">
+        <v>1.727011761775513</v>
+      </c>
+      <c r="D12">
+        <v>1.762611761775513</v>
+      </c>
+      <c r="E12">
+        <v>-0.2114</v>
+      </c>
+      <c r="F12">
+        <v>0.1846</v>
+      </c>
+      <c r="G12">
+        <v>0.149</v>
+      </c>
+      <c r="H12">
+        <v>1.45</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.177</v>
+      </c>
+      <c r="K12">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L12">
+        <v>0.089</v>
+      </c>
+      <c r="M12">
+        <v>0.00943306</v>
+      </c>
+      <c r="N12">
+        <v>0.07956694</v>
+      </c>
+      <c r="O12">
+        <v>0.0127307104</v>
+      </c>
+      <c r="P12">
+        <v>0.06683622960000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.1548362296</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1283609997649487</v>
+      </c>
+      <c r="T12">
+        <v>0.9225780519182775</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.16</v>
+      </c>
+      <c r="W12">
+        <v>0.042924</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>9.434902354061142</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.119727474910749</v>
+      </c>
+      <c r="C13">
+        <v>1.710508160218898</v>
+      </c>
+      <c r="D13">
+        <v>1.764568160218898</v>
+      </c>
+      <c r="E13">
+        <v>-0.19294</v>
+      </c>
+      <c r="F13">
+        <v>0.20306</v>
+      </c>
+      <c r="G13">
+        <v>0.149</v>
+      </c>
+      <c r="H13">
+        <v>1.45</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.177</v>
+      </c>
+      <c r="K13">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L13">
+        <v>0.089</v>
+      </c>
+      <c r="M13">
+        <v>0.010376366</v>
+      </c>
+      <c r="N13">
+        <v>0.078623634</v>
+      </c>
+      <c r="O13">
+        <v>0.01257978144</v>
+      </c>
+      <c r="P13">
+        <v>0.06604385255999999</v>
+      </c>
+      <c r="Q13">
+        <v>0.15404385256</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1292200392255607</v>
+      </c>
+      <c r="T13">
+        <v>0.9314271151731802</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.16</v>
+      </c>
+      <c r="W13">
+        <v>0.042924</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.577183958237402</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1196376500330442</v>
+      </c>
+      <c r="C14">
+        <v>1.694008906469298</v>
+      </c>
+      <c r="D14">
+        <v>1.766528906469298</v>
+      </c>
+      <c r="E14">
+        <v>-0.17448</v>
+      </c>
+      <c r="F14">
+        <v>0.22152</v>
+      </c>
+      <c r="G14">
+        <v>0.149</v>
+      </c>
+      <c r="H14">
+        <v>1.45</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.177</v>
+      </c>
+      <c r="K14">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L14">
+        <v>0.089</v>
+      </c>
+      <c r="M14">
+        <v>0.011319672</v>
+      </c>
+      <c r="N14">
+        <v>0.07768032799999999</v>
+      </c>
+      <c r="O14">
+        <v>0.01242885248</v>
+      </c>
+      <c r="P14">
+        <v>0.06525147551999999</v>
+      </c>
+      <c r="Q14">
+        <v>0.15325147552</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1300986023102775</v>
+      </c>
+      <c r="T14">
+        <v>0.9404772935020579</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.16</v>
+      </c>
+      <c r="W14">
+        <v>0.042924</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.862418628384285</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1197553051553394</v>
+      </c>
+      <c r="C15">
+        <v>1.672981549405671</v>
+      </c>
+      <c r="D15">
+        <v>1.763961549405672</v>
+      </c>
+      <c r="E15">
+        <v>-0.15602</v>
+      </c>
+      <c r="F15">
+        <v>0.23998</v>
+      </c>
+      <c r="G15">
+        <v>0.149</v>
+      </c>
+      <c r="H15">
+        <v>1.45</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.177</v>
+      </c>
+      <c r="K15">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L15">
+        <v>0.089</v>
+      </c>
+      <c r="M15">
+        <v>0.01271894</v>
+      </c>
+      <c r="N15">
+        <v>0.07628106</v>
+      </c>
+      <c r="O15">
+        <v>0.0122049696</v>
+      </c>
+      <c r="P15">
+        <v>0.06407609039999999</v>
+      </c>
+      <c r="Q15">
+        <v>0.1520760904</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1309973622475166</v>
+      </c>
+      <c r="T15">
+        <v>0.9497355219074616</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.16</v>
+      </c>
+      <c r="W15">
+        <v>0.04452</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.997438465784096</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1196814402776346</v>
+      </c>
+      <c r="C16">
+        <v>1.656132485161459</v>
+      </c>
+      <c r="D16">
+        <v>1.765572485161458</v>
+      </c>
+      <c r="E16">
+        <v>-0.13756</v>
+      </c>
+      <c r="F16">
+        <v>0.2584400000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.149</v>
+      </c>
+      <c r="H16">
+        <v>1.45</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.177</v>
+      </c>
+      <c r="K16">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L16">
+        <v>0.089</v>
+      </c>
+      <c r="M16">
+        <v>0.01369732</v>
+      </c>
+      <c r="N16">
+        <v>0.07530268</v>
+      </c>
+      <c r="O16">
+        <v>0.0120484288</v>
+      </c>
+      <c r="P16">
+        <v>0.0632542512</v>
+      </c>
+      <c r="Q16">
+        <v>0.1512542512</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1319170235786449</v>
+      </c>
+      <c r="T16">
+        <v>0.9592090579502002</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.16</v>
+      </c>
+      <c r="W16">
+        <v>0.04452</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.497621432513804</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1198595753999298</v>
+      </c>
+      <c r="C17">
+        <v>1.633792493574857</v>
+      </c>
+      <c r="D17">
+        <v>1.761692493574857</v>
+      </c>
+      <c r="E17">
+        <v>-0.1191</v>
+      </c>
+      <c r="F17">
+        <v>0.2769</v>
+      </c>
+      <c r="G17">
+        <v>0.149</v>
+      </c>
+      <c r="H17">
+        <v>1.45</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.177</v>
+      </c>
+      <c r="K17">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L17">
+        <v>0.089</v>
+      </c>
+      <c r="M17">
+        <v>0.0152295</v>
+      </c>
+      <c r="N17">
+        <v>0.0737705</v>
+      </c>
+      <c r="O17">
+        <v>0.01180328</v>
+      </c>
+      <c r="P17">
+        <v>0.06196722</v>
+      </c>
+      <c r="Q17">
+        <v>0.14996722</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1328583239999174</v>
+      </c>
+      <c r="T17">
+        <v>0.968905500723356</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.16</v>
+      </c>
+      <c r="W17">
+        <v>0.0462</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.843921336879084</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.119802510522225</v>
+      </c>
+      <c r="C18">
+        <v>1.616573575685166</v>
+      </c>
+      <c r="D18">
+        <v>1.762933575685166</v>
+      </c>
+      <c r="E18">
+        <v>-0.10064</v>
+      </c>
+      <c r="F18">
+        <v>0.29536</v>
+      </c>
+      <c r="G18">
+        <v>0.149</v>
+      </c>
+      <c r="H18">
+        <v>1.45</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.177</v>
+      </c>
+      <c r="K18">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0.089</v>
+      </c>
+      <c r="M18">
+        <v>0.0162448</v>
+      </c>
+      <c r="N18">
+        <v>0.07275519999999999</v>
+      </c>
+      <c r="O18">
+        <v>0.011640832</v>
+      </c>
+      <c r="P18">
+        <v>0.06111436799999999</v>
+      </c>
+      <c r="Q18">
+        <v>0.149114368</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1338220363359822</v>
+      </c>
+      <c r="T18">
+        <v>0.978832811181587</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.16</v>
+      </c>
+      <c r="W18">
+        <v>0.0462</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.47867625332414</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1197454456445202</v>
+      </c>
+      <c r="C19">
+        <v>1.599356407670303</v>
+      </c>
+      <c r="D19">
+        <v>1.764176407670303</v>
+      </c>
+      <c r="E19">
+        <v>-0.08217999999999998</v>
+      </c>
+      <c r="F19">
+        <v>0.31382</v>
+      </c>
+      <c r="G19">
+        <v>0.149</v>
+      </c>
+      <c r="H19">
+        <v>1.45</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.177</v>
+      </c>
+      <c r="K19">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L19">
+        <v>0.089</v>
+      </c>
+      <c r="M19">
+        <v>0.0172601</v>
+      </c>
+      <c r="N19">
+        <v>0.0717399</v>
+      </c>
+      <c r="O19">
+        <v>0.011478384</v>
+      </c>
+      <c r="P19">
+        <v>0.06026151599999999</v>
+      </c>
+      <c r="Q19">
+        <v>0.148261516</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1348089706560485</v>
+      </c>
+      <c r="T19">
+        <v>0.9889993339400166</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.16</v>
+      </c>
+      <c r="W19">
+        <v>0.0462</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.15640117959919</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1196883807668154</v>
+      </c>
+      <c r="C20">
+        <v>1.582140993233755</v>
+      </c>
+      <c r="D20">
+        <v>1.765420993233755</v>
+      </c>
+      <c r="E20">
+        <v>-0.06372</v>
+      </c>
+      <c r="F20">
+        <v>0.33228</v>
+      </c>
+      <c r="G20">
+        <v>0.149</v>
+      </c>
+      <c r="H20">
+        <v>1.45</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.177</v>
+      </c>
+      <c r="K20">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L20">
+        <v>0.089</v>
+      </c>
+      <c r="M20">
+        <v>0.0182754</v>
+      </c>
+      <c r="N20">
+        <v>0.0707246</v>
+      </c>
+      <c r="O20">
+        <v>0.011315936</v>
+      </c>
+      <c r="P20">
+        <v>0.059408664</v>
+      </c>
+      <c r="Q20">
+        <v>0.147408664</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1358199765448968</v>
+      </c>
+      <c r="T20">
+        <v>0.9994138206681638</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.16</v>
+      </c>
+      <c r="W20">
+        <v>0.0462</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.869934447399237</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1196313158891106</v>
+      </c>
+      <c r="C21">
+        <v>1.56492733608947</v>
+      </c>
+      <c r="D21">
+        <v>1.76666733608947</v>
+      </c>
+      <c r="E21">
+        <v>-0.04526000000000002</v>
+      </c>
+      <c r="F21">
+        <v>0.35074</v>
+      </c>
+      <c r="G21">
+        <v>0.149</v>
+      </c>
+      <c r="H21">
+        <v>1.45</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.177</v>
+      </c>
+      <c r="K21">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L21">
+        <v>0.089</v>
+      </c>
+      <c r="M21">
+        <v>0.0192907</v>
+      </c>
+      <c r="N21">
+        <v>0.0697093</v>
+      </c>
+      <c r="O21">
+        <v>0.011153488</v>
+      </c>
+      <c r="P21">
+        <v>0.058555812</v>
+      </c>
+      <c r="Q21">
+        <v>0.146555812</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1368559455421118</v>
+      </c>
+      <c r="T21">
+        <v>1.010085455216759</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.16</v>
+      </c>
+      <c r="W21">
+        <v>0.0462</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.613622108062434</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1202126510114058</v>
+      </c>
+      <c r="C22">
+        <v>1.533852272470713</v>
+      </c>
+      <c r="D22">
+        <v>1.754052272470713</v>
+      </c>
+      <c r="E22">
+        <v>-0.02679999999999999</v>
+      </c>
+      <c r="F22">
+        <v>0.3692</v>
+      </c>
+      <c r="G22">
+        <v>0.149</v>
+      </c>
+      <c r="H22">
+        <v>1.45</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.177</v>
+      </c>
+      <c r="K22">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L22">
+        <v>0.089</v>
+      </c>
+      <c r="M22">
+        <v>0.02170896</v>
+      </c>
+      <c r="N22">
+        <v>0.06729104</v>
+      </c>
+      <c r="O22">
+        <v>0.0107665664</v>
+      </c>
+      <c r="P22">
+        <v>0.05652447359999999</v>
+      </c>
+      <c r="Q22">
+        <v>0.1445244736</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1379178137642572</v>
+      </c>
+      <c r="T22">
+        <v>1.021023880629069</v>
+      </c>
+      <c r="U22">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.16</v>
+      </c>
+      <c r="W22">
+        <v>0.04939200000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.099689713371806</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.120928386133701</v>
+      </c>
+      <c r="C23">
+        <v>1.50010600085562</v>
+      </c>
+      <c r="D23">
+        <v>1.73876600085562</v>
+      </c>
+      <c r="E23">
+        <v>-0.008340000000000014</v>
+      </c>
+      <c r="F23">
+        <v>0.38766</v>
+      </c>
+      <c r="G23">
+        <v>0.149</v>
+      </c>
+      <c r="H23">
+        <v>1.45</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.177</v>
+      </c>
+      <c r="K23">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L23">
+        <v>0.089</v>
+      </c>
+      <c r="M23">
+        <v>0.02442258</v>
+      </c>
+      <c r="N23">
+        <v>0.06457742</v>
+      </c>
+      <c r="O23">
+        <v>0.0103323872</v>
+      </c>
+      <c r="P23">
+        <v>0.0542450328</v>
+      </c>
+      <c r="Q23">
+        <v>0.1422450328</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1390065647262038</v>
+      </c>
+      <c r="T23">
+        <v>1.032239228203716</v>
+      </c>
+      <c r="U23">
+        <v>0.063</v>
+      </c>
+      <c r="V23">
+        <v>0.16</v>
+      </c>
+      <c r="W23">
+        <v>0.05292</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.644168634108272</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1222506012559962</v>
+      </c>
+      <c r="C24">
+        <v>1.454096496527767</v>
+      </c>
+      <c r="D24">
+        <v>1.711216496527767</v>
+      </c>
+      <c r="E24">
+        <v>0.01012000000000002</v>
+      </c>
+      <c r="F24">
+        <v>0.40612</v>
+      </c>
+      <c r="G24">
+        <v>0.149</v>
+      </c>
+      <c r="H24">
+        <v>1.45</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.177</v>
+      </c>
+      <c r="K24">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L24">
+        <v>0.089</v>
+      </c>
+      <c r="M24">
+        <v>0.028469012</v>
+      </c>
+      <c r="N24">
+        <v>0.06053098799999999</v>
+      </c>
+      <c r="O24">
+        <v>0.00968495808</v>
+      </c>
+      <c r="P24">
+        <v>0.05084602991999999</v>
+      </c>
+      <c r="Q24">
+        <v>0.13884602992</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1401232323794823</v>
+      </c>
+      <c r="T24">
+        <v>1.043742148793098</v>
+      </c>
+      <c r="U24">
+        <v>0.0701</v>
+      </c>
+      <c r="V24">
+        <v>0.16</v>
+      </c>
+      <c r="W24">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.12620613599095</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1264355363782914</v>
+      </c>
+      <c r="C25">
+        <v>1.353919303775535</v>
+      </c>
+      <c r="D25">
+        <v>1.629499303775535</v>
+      </c>
+      <c r="E25">
+        <v>0.02857999999999999</v>
+      </c>
+      <c r="F25">
+        <v>0.42458</v>
+      </c>
+      <c r="G25">
+        <v>0.149</v>
+      </c>
+      <c r="H25">
+        <v>1.45</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.177</v>
+      </c>
+      <c r="K25">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L25">
+        <v>0.089</v>
+      </c>
+      <c r="M25">
+        <v>0.038806612</v>
+      </c>
+      <c r="N25">
+        <v>0.05019338799999999</v>
+      </c>
+      <c r="O25">
+        <v>0.008030942080000001</v>
+      </c>
+      <c r="P25">
+        <v>0.04216244591999999</v>
+      </c>
+      <c r="Q25">
+        <v>0.13016244592</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1412689043873914</v>
+      </c>
+      <c r="T25">
+        <v>1.055543846540646</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.16</v>
+      </c>
+      <c r="W25">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.293423605235108</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1266842315005866</v>
+      </c>
+      <c r="C26">
+        <v>1.330848140638385</v>
+      </c>
+      <c r="D26">
+        <v>1.624888140638384</v>
+      </c>
+      <c r="E26">
+        <v>0.04703999999999997</v>
+      </c>
+      <c r="F26">
+        <v>0.44304</v>
+      </c>
+      <c r="G26">
+        <v>0.149</v>
+      </c>
+      <c r="H26">
+        <v>1.45</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.177</v>
+      </c>
+      <c r="K26">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L26">
+        <v>0.089</v>
+      </c>
+      <c r="M26">
+        <v>0.040493856</v>
+      </c>
+      <c r="N26">
+        <v>0.04850614399999999</v>
+      </c>
+      <c r="O26">
+        <v>0.007760983040000001</v>
+      </c>
+      <c r="P26">
+        <v>0.04074516095999999</v>
+      </c>
+      <c r="Q26">
+        <v>0.12874516096</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1424447256586666</v>
+      </c>
+      <c r="T26">
+        <v>1.06765611528155</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.16</v>
+      </c>
+      <c r="W26">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.197864288350312</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1269329266228818</v>
+      </c>
+      <c r="C27">
+        <v>1.307803001232073</v>
+      </c>
+      <c r="D27">
+        <v>1.620303001232073</v>
+      </c>
+      <c r="E27">
+        <v>0.0655</v>
+      </c>
+      <c r="F27">
+        <v>0.4615</v>
+      </c>
+      <c r="G27">
+        <v>0.149</v>
+      </c>
+      <c r="H27">
+        <v>1.45</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.177</v>
+      </c>
+      <c r="K27">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L27">
+        <v>0.089</v>
+      </c>
+      <c r="M27">
+        <v>0.04218110000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.04681889999999999</v>
+      </c>
+      <c r="O27">
+        <v>0.007491024</v>
+      </c>
+      <c r="P27">
+        <v>0.03932787599999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.127327876</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1436519021638424</v>
+      </c>
+      <c r="T27">
+        <v>1.080091377855545</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.16</v>
+      </c>
+      <c r="W27">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.109949716816299</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.127181621745177</v>
+      </c>
+      <c r="C28">
+        <v>1.284783665873773</v>
+      </c>
+      <c r="D28">
+        <v>1.615743665873773</v>
+      </c>
+      <c r="E28">
+        <v>0.08396000000000003</v>
+      </c>
+      <c r="F28">
+        <v>0.4799600000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.149</v>
+      </c>
+      <c r="H28">
+        <v>1.45</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.177</v>
+      </c>
+      <c r="K28">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0.089</v>
+      </c>
+      <c r="M28">
+        <v>0.04386834400000001</v>
+      </c>
+      <c r="N28">
+        <v>0.04513165599999999</v>
+      </c>
+      <c r="O28">
+        <v>0.007221064959999999</v>
+      </c>
+      <c r="P28">
+        <v>0.03791059103999998</v>
+      </c>
+      <c r="Q28">
+        <v>0.12591059104</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.14489170506105</v>
+      </c>
+      <c r="T28">
+        <v>1.092862728607215</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.16</v>
+      </c>
+      <c r="W28">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.028797804631056</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1322157968674722</v>
+      </c>
+      <c r="C29">
+        <v>1.179251277268157</v>
+      </c>
+      <c r="D29">
+        <v>1.528671277268157</v>
+      </c>
+      <c r="E29">
+        <v>0.10242</v>
+      </c>
+      <c r="F29">
+        <v>0.49842</v>
+      </c>
+      <c r="G29">
+        <v>0.149</v>
+      </c>
+      <c r="H29">
+        <v>1.45</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.177</v>
+      </c>
+      <c r="K29">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L29">
+        <v>0.089</v>
+      </c>
+      <c r="M29">
+        <v>0.05607225</v>
+      </c>
+      <c r="N29">
+        <v>0.03292774999999999</v>
+      </c>
+      <c r="O29">
+        <v>0.00526844</v>
+      </c>
+      <c r="P29">
+        <v>0.02765930999999999</v>
+      </c>
+      <c r="Q29">
+        <v>0.11565931</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1461654751609208</v>
+      </c>
+      <c r="T29">
+        <v>1.105983979379479</v>
+      </c>
+      <c r="U29">
+        <v>0.1125</v>
+      </c>
+      <c r="V29">
+        <v>0.16</v>
+      </c>
+      <c r="W29">
+        <v>0.0945</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>1.587237893967158</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1326417319897674</v>
+      </c>
+      <c r="C30">
+        <v>1.153852841951306</v>
+      </c>
+      <c r="D30">
+        <v>1.521732841951306</v>
+      </c>
+      <c r="E30">
+        <v>0.1208800000000001</v>
+      </c>
+      <c r="F30">
+        <v>0.5168800000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.149</v>
+      </c>
+      <c r="H30">
+        <v>1.45</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.177</v>
+      </c>
+      <c r="K30">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L30">
+        <v>0.089</v>
+      </c>
+      <c r="M30">
+        <v>0.05814900000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.03085099999999998</v>
+      </c>
+      <c r="O30">
+        <v>0.004936159999999998</v>
+      </c>
+      <c r="P30">
+        <v>0.02591483999999998</v>
+      </c>
+      <c r="Q30">
+        <v>0.11391484</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1474746277635658</v>
+      </c>
+      <c r="T30">
+        <v>1.119469709339861</v>
+      </c>
+      <c r="U30">
+        <v>0.1125</v>
+      </c>
+      <c r="V30">
+        <v>0.16</v>
+      </c>
+      <c r="W30">
+        <v>0.0945</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>1.530550826325474</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1555494595363708</v>
+      </c>
+      <c r="C31">
+        <v>0.8368095210471148</v>
+      </c>
+      <c r="D31">
+        <v>1.223149521047115</v>
+      </c>
+      <c r="E31">
+        <v>0.13934</v>
+      </c>
+      <c r="F31">
+        <v>0.53534</v>
+      </c>
+      <c r="G31">
+        <v>0.149</v>
+      </c>
+      <c r="H31">
+        <v>1.45</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.177</v>
+      </c>
+      <c r="K31">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L31">
+        <v>0.089</v>
+      </c>
+      <c r="M31">
+        <v>0.105247844</v>
+      </c>
+      <c r="N31">
+        <v>-0.01624784400000001</v>
+      </c>
+      <c r="O31">
+        <v>-0.002599655040000002</v>
+      </c>
+      <c r="P31">
+        <v>-0.01364818896000001</v>
+      </c>
+      <c r="Q31">
+        <v>0.07435181103999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1496470925366918</v>
+      </c>
+      <c r="T31">
+        <v>1.141848516225803</v>
+      </c>
+      <c r="U31">
+        <v>0.1966</v>
+      </c>
+      <c r="V31">
+        <v>0.1352996836685795</v>
+      </c>
+      <c r="W31">
+        <v>0.1700000821907573</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.8456230229286216</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1571274595363708</v>
+      </c>
+      <c r="C32">
+        <v>0.8020377540931468</v>
+      </c>
+      <c r="D32">
+        <v>1.206837754093147</v>
+      </c>
+      <c r="E32">
+        <v>0.1577999999999999</v>
+      </c>
+      <c r="F32">
+        <v>0.5538</v>
+      </c>
+      <c r="G32">
+        <v>0.149</v>
+      </c>
+      <c r="H32">
+        <v>1.45</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.177</v>
+      </c>
+      <c r="K32">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L32">
+        <v>0.089</v>
+      </c>
+      <c r="M32">
+        <v>0.10887708</v>
+      </c>
+      <c r="N32">
+        <v>-0.01987707999999999</v>
+      </c>
+      <c r="O32">
+        <v>-0.003180332799999999</v>
+      </c>
+      <c r="P32">
+        <v>-0.01669674719999999</v>
+      </c>
+      <c r="Q32">
+        <v>0.07130325279999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1512306224300732</v>
+      </c>
+      <c r="T32">
+        <v>1.158160637886172</v>
+      </c>
+      <c r="U32">
+        <v>0.1966</v>
+      </c>
+      <c r="V32">
+        <v>0.1307896942129602</v>
+      </c>
+      <c r="W32">
+        <v>0.170886746117732</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.817435588831001</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1642960317593294</v>
+      </c>
+      <c r="C33">
+        <v>0.7146408842947378</v>
+      </c>
+      <c r="D33">
+        <v>1.137900884294738</v>
+      </c>
+      <c r="E33">
+        <v>0.17626</v>
+      </c>
+      <c r="F33">
+        <v>0.57226</v>
+      </c>
+      <c r="G33">
+        <v>0.149</v>
+      </c>
+      <c r="H33">
+        <v>1.45</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.177</v>
+      </c>
+      <c r="K33">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L33">
+        <v>0.089</v>
+      </c>
+      <c r="M33">
+        <v>0.122349188</v>
+      </c>
+      <c r="N33">
+        <v>-0.033349188</v>
+      </c>
+      <c r="O33">
+        <v>-0.005335870080000001</v>
+      </c>
+      <c r="P33">
+        <v>-0.02801331792</v>
+      </c>
+      <c r="Q33">
+        <v>0.05998668207999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1532347940927679</v>
+      </c>
+      <c r="T33">
+        <v>1.178805838287366</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1163881855922085</v>
+      </c>
+      <c r="W33">
+        <v>0.1889162059203858</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.7274261599513027</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1660460317593294</v>
+      </c>
+      <c r="C34">
+        <v>0.6805314646626809</v>
+      </c>
+      <c r="D34">
+        <v>1.122251464662681</v>
+      </c>
+      <c r="E34">
+        <v>0.19472</v>
+      </c>
+      <c r="F34">
+        <v>0.59072</v>
+      </c>
+      <c r="G34">
+        <v>0.149</v>
+      </c>
+      <c r="H34">
+        <v>1.45</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.177</v>
+      </c>
+      <c r="K34">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L34">
+        <v>0.089</v>
+      </c>
+      <c r="M34">
+        <v>0.126295936</v>
+      </c>
+      <c r="N34">
+        <v>-0.037295936</v>
+      </c>
+      <c r="O34">
+        <v>-0.005967349760000002</v>
+      </c>
+      <c r="P34">
+        <v>-0.03132858624</v>
+      </c>
+      <c r="Q34">
+        <v>0.05667141376</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1549176587117791</v>
+      </c>
+      <c r="T34">
+        <v>1.19614121826218</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1127510547924519</v>
+      </c>
+      <c r="W34">
+        <v>0.1896938244853738</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.7046940924528244</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1677960317593294</v>
+      </c>
+      <c r="C35">
+        <v>0.6468466547489629</v>
+      </c>
+      <c r="D35">
+        <v>1.107026654748963</v>
+      </c>
+      <c r="E35">
+        <v>0.21318</v>
+      </c>
+      <c r="F35">
+        <v>0.6091800000000001</v>
+      </c>
+      <c r="G35">
+        <v>0.149</v>
+      </c>
+      <c r="H35">
+        <v>1.45</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.177</v>
+      </c>
+      <c r="K35">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L35">
+        <v>0.089</v>
+      </c>
+      <c r="M35">
+        <v>0.130242684</v>
+      </c>
+      <c r="N35">
+        <v>-0.041242684</v>
+      </c>
+      <c r="O35">
+        <v>-0.006598829440000001</v>
+      </c>
+      <c r="P35">
+        <v>-0.03464385456</v>
+      </c>
+      <c r="Q35">
+        <v>0.05335614544</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1566507580955371</v>
+      </c>
+      <c r="T35">
+        <v>1.213994072266094</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1093343561623776</v>
+      </c>
+      <c r="W35">
+        <v>0.1904243146524837</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.68333972601486</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1695460317593294</v>
+      </c>
+      <c r="C36">
+        <v>0.6135694046975292</v>
+      </c>
+      <c r="D36">
+        <v>1.092209404697529</v>
+      </c>
+      <c r="E36">
+        <v>0.2316400000000001</v>
+      </c>
+      <c r="F36">
+        <v>0.6276400000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.149</v>
+      </c>
+      <c r="H36">
+        <v>1.45</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.177</v>
+      </c>
+      <c r="K36">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L36">
+        <v>0.089</v>
+      </c>
+      <c r="M36">
+        <v>0.134189432</v>
+      </c>
+      <c r="N36">
+        <v>-0.04518943200000003</v>
+      </c>
+      <c r="O36">
+        <v>-0.007230309120000006</v>
+      </c>
+      <c r="P36">
+        <v>-0.03795912288000002</v>
+      </c>
+      <c r="Q36">
+        <v>0.05004087711999997</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1584363756424391</v>
+      </c>
+      <c r="T36">
+        <v>1.232387921845883</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1061186398046606</v>
+      </c>
+      <c r="W36">
+        <v>0.1911118348097635</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6632414987791287</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1712960317593294</v>
+      </c>
+      <c r="C37">
+        <v>0.5806835654264142</v>
+      </c>
+      <c r="D37">
+        <v>1.077783565426414</v>
+      </c>
+      <c r="E37">
+        <v>0.2501000000000001</v>
+      </c>
+      <c r="F37">
+        <v>0.6461000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.149</v>
+      </c>
+      <c r="H37">
+        <v>1.45</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.177</v>
+      </c>
+      <c r="K37">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L37">
+        <v>0.089</v>
+      </c>
+      <c r="M37">
+        <v>0.13813618</v>
+      </c>
+      <c r="N37">
+        <v>-0.04913618000000003</v>
+      </c>
+      <c r="O37">
+        <v>-0.007861788800000007</v>
+      </c>
+      <c r="P37">
+        <v>-0.04127439120000002</v>
+      </c>
+      <c r="Q37">
+        <v>0.04672560879999997</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1602769352677074</v>
+      </c>
+      <c r="T37">
+        <v>1.251347736028127</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1030866786673846</v>
+      </c>
+      <c r="W37">
+        <v>0.1917600681009131</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6442917416711537</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1730460317593294</v>
+      </c>
+      <c r="C38">
+        <v>0.5481738299163352</v>
+      </c>
+      <c r="D38">
+        <v>1.063733829916335</v>
+      </c>
+      <c r="E38">
+        <v>0.26856</v>
+      </c>
+      <c r="F38">
+        <v>0.66456</v>
+      </c>
+      <c r="G38">
+        <v>0.149</v>
+      </c>
+      <c r="H38">
+        <v>1.45</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.177</v>
+      </c>
+      <c r="K38">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L38">
+        <v>0.089</v>
+      </c>
+      <c r="M38">
+        <v>0.142082928</v>
+      </c>
+      <c r="N38">
+        <v>-0.053082928</v>
+      </c>
+      <c r="O38">
+        <v>-0.008493268480000002</v>
+      </c>
+      <c r="P38">
+        <v>-0.04458965952</v>
+      </c>
+      <c r="Q38">
+        <v>0.04341034048</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1621750123812654</v>
+      </c>
+      <c r="T38">
+        <v>1.270900044403567</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1002231598155128</v>
+      </c>
+      <c r="W38">
+        <v>0.1923722884314434</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.626394748846955</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1747960317593295</v>
+      </c>
+      <c r="C39">
+        <v>0.5160256790322862</v>
+      </c>
+      <c r="D39">
+        <v>1.050045679032286</v>
+      </c>
+      <c r="E39">
+        <v>0.2870200000000001</v>
+      </c>
+      <c r="F39">
+        <v>0.6830200000000001</v>
+      </c>
+      <c r="G39">
+        <v>0.149</v>
+      </c>
+      <c r="H39">
+        <v>1.45</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.177</v>
+      </c>
+      <c r="K39">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L39">
+        <v>0.089</v>
+      </c>
+      <c r="M39">
+        <v>0.146029676</v>
+      </c>
+      <c r="N39">
+        <v>-0.057029676</v>
+      </c>
+      <c r="O39">
+        <v>-0.009124748160000001</v>
+      </c>
+      <c r="P39">
+        <v>-0.04790492784</v>
+      </c>
+      <c r="Q39">
+        <v>0.04009507215999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1641333459111267</v>
+      </c>
+      <c r="T39">
+        <v>1.291073060981401</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.09751442576644491</v>
+      </c>
+      <c r="W39">
+        <v>0.1929514157711341</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6094651610402806</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1765460317593294</v>
+      </c>
+      <c r="C40">
+        <v>0.4842253314749999</v>
+      </c>
+      <c r="D40">
+        <v>1.036705331475</v>
+      </c>
+      <c r="E40">
+        <v>0.30548</v>
+      </c>
+      <c r="F40">
+        <v>0.70148</v>
+      </c>
+      <c r="G40">
+        <v>0.149</v>
+      </c>
+      <c r="H40">
+        <v>1.45</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.177</v>
+      </c>
+      <c r="K40">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L40">
+        <v>0.089</v>
+      </c>
+      <c r="M40">
+        <v>0.149976424</v>
+      </c>
+      <c r="N40">
+        <v>-0.060976424</v>
+      </c>
+      <c r="O40">
+        <v>-0.009756227840000003</v>
+      </c>
+      <c r="P40">
+        <v>-0.05122019615999999</v>
+      </c>
+      <c r="Q40">
+        <v>0.03677980384</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1661548514903384</v>
+      </c>
+      <c r="T40">
+        <v>1.311896820029488</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.09494825666732794</v>
+      </c>
+      <c r="W40">
+        <v>0.1935000627245253</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5934266041707995</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1782960317593294</v>
+      </c>
+      <c r="C41">
+        <v>0.4527596974996095</v>
+      </c>
+      <c r="D41">
+        <v>1.02369969749961</v>
+      </c>
+      <c r="E41">
+        <v>0.32394</v>
+      </c>
+      <c r="F41">
+        <v>0.71994</v>
+      </c>
+      <c r="G41">
+        <v>0.149</v>
+      </c>
+      <c r="H41">
+        <v>1.45</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.177</v>
+      </c>
+      <c r="K41">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L41">
+        <v>0.089</v>
+      </c>
+      <c r="M41">
+        <v>0.153923172</v>
+      </c>
+      <c r="N41">
+        <v>-0.064923172</v>
+      </c>
+      <c r="O41">
+        <v>-0.01038770752</v>
+      </c>
+      <c r="P41">
+        <v>-0.05453546448</v>
+      </c>
+      <c r="Q41">
+        <v>0.03346453552</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1682426359409997</v>
+      </c>
+      <c r="T41">
+        <v>1.333403325275873</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.09251368598355031</v>
+      </c>
+      <c r="W41">
+        <v>0.194020573936717</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5782105373971893</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1800460317593294</v>
+      </c>
+      <c r="C42">
+        <v>0.4216163360747957</v>
+      </c>
+      <c r="D42">
+        <v>1.011016336074796</v>
+      </c>
+      <c r="E42">
+        <v>0.3424</v>
+      </c>
+      <c r="F42">
+        <v>0.7384000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.149</v>
+      </c>
+      <c r="H42">
+        <v>1.45</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.177</v>
+      </c>
+      <c r="K42">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L42">
+        <v>0.089</v>
+      </c>
+      <c r="M42">
+        <v>0.15786992</v>
+      </c>
+      <c r="N42">
+        <v>-0.06886992</v>
+      </c>
+      <c r="O42">
+        <v>-0.0110191872</v>
+      </c>
+      <c r="P42">
+        <v>-0.0578507328</v>
+      </c>
+      <c r="Q42">
+        <v>0.0301492672</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.170400013206683</v>
+      </c>
+      <c r="T42">
+        <v>1.355626714030471</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.09020084383396154</v>
+      </c>
+      <c r="W42">
+        <v>0.194515059588299</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5637552739622596</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1817960317593295</v>
+      </c>
+      <c r="C43">
+        <v>0.390783415187671</v>
+      </c>
+      <c r="D43">
+        <v>0.9986434151876712</v>
+      </c>
+      <c r="E43">
+        <v>0.3608600000000001</v>
+      </c>
+      <c r="F43">
+        <v>0.7568600000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.149</v>
+      </c>
+      <c r="H43">
+        <v>1.45</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.177</v>
+      </c>
+      <c r="K43">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L43">
+        <v>0.089</v>
+      </c>
+      <c r="M43">
+        <v>0.161816668</v>
+      </c>
+      <c r="N43">
+        <v>-0.07281666800000003</v>
+      </c>
+      <c r="O43">
+        <v>-0.01165066688000001</v>
+      </c>
+      <c r="P43">
+        <v>-0.06116600112000002</v>
+      </c>
+      <c r="Q43">
+        <v>0.02683399887999997</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1726305219051014</v>
+      </c>
+      <c r="T43">
+        <v>1.37860343799709</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.0880008232526454</v>
+      </c>
+      <c r="W43">
+        <v>0.1949854239885844</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5500051453290336</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1835460317593294</v>
+      </c>
+      <c r="C44">
+        <v>0.3602496750281883</v>
+      </c>
+      <c r="D44">
+        <v>0.9865696750281883</v>
+      </c>
+      <c r="E44">
+        <v>0.37932</v>
+      </c>
+      <c r="F44">
+        <v>0.77532</v>
+      </c>
+      <c r="G44">
+        <v>0.149</v>
+      </c>
+      <c r="H44">
+        <v>1.45</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.177</v>
+      </c>
+      <c r="K44">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L44">
+        <v>0.089</v>
+      </c>
+      <c r="M44">
+        <v>0.165763416</v>
+      </c>
+      <c r="N44">
+        <v>-0.076763416</v>
+      </c>
+      <c r="O44">
+        <v>-0.01228214656</v>
+      </c>
+      <c r="P44">
+        <v>-0.06448126944</v>
+      </c>
+      <c r="Q44">
+        <v>0.02351873055999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1749379446965686</v>
+      </c>
+      <c r="T44">
+        <v>1.402372462790143</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.08590556555615386</v>
+      </c>
+      <c r="W44">
+        <v>0.1954333900840943</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5369097847259614</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1852960317593294</v>
+      </c>
+      <c r="C45">
+        <v>0.3300043938122733</v>
+      </c>
+      <c r="D45">
+        <v>0.9747843938122733</v>
+      </c>
+      <c r="E45">
+        <v>0.39778</v>
+      </c>
+      <c r="F45">
+        <v>0.79378</v>
+      </c>
+      <c r="G45">
+        <v>0.149</v>
+      </c>
+      <c r="H45">
+        <v>1.45</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.177</v>
+      </c>
+      <c r="K45">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L45">
+        <v>0.089</v>
+      </c>
+      <c r="M45">
+        <v>0.169710164</v>
+      </c>
+      <c r="N45">
+        <v>-0.080710164</v>
+      </c>
+      <c r="O45">
+        <v>-0.01291362624</v>
+      </c>
+      <c r="P45">
+        <v>-0.06779653776</v>
+      </c>
+      <c r="Q45">
+        <v>0.02020346224</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1773263296912453</v>
+      </c>
+      <c r="T45">
+        <v>1.426975488453128</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.08390776170601073</v>
+      </c>
+      <c r="W45">
+        <v>0.1958605205472549</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.524423510662567</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1870460317593294</v>
+      </c>
+      <c r="C46">
+        <v>0.3000373560256504</v>
+      </c>
+      <c r="D46">
+        <v>0.9632773560256506</v>
+      </c>
+      <c r="E46">
+        <v>0.4162400000000001</v>
+      </c>
+      <c r="F46">
+        <v>0.8122400000000001</v>
+      </c>
+      <c r="G46">
+        <v>0.149</v>
+      </c>
+      <c r="H46">
+        <v>1.45</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.177</v>
+      </c>
+      <c r="K46">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L46">
+        <v>0.089</v>
+      </c>
+      <c r="M46">
+        <v>0.173656912</v>
+      </c>
+      <c r="N46">
+        <v>-0.084656912</v>
+      </c>
+      <c r="O46">
+        <v>-0.01354510592</v>
+      </c>
+      <c r="P46">
+        <v>-0.07111180607999999</v>
+      </c>
+      <c r="Q46">
+        <v>0.01688819392</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1798000141500175</v>
+      </c>
+      <c r="T46">
+        <v>1.452457193604076</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.08200076712178322</v>
+      </c>
+      <c r="W46">
+        <v>0.1962682359893627</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5125047945111451</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1887960317593294</v>
+      </c>
+      <c r="C47">
+        <v>0.2703388228906561</v>
+      </c>
+      <c r="D47">
+        <v>0.9520388228906562</v>
+      </c>
+      <c r="E47">
+        <v>0.4347000000000001</v>
+      </c>
+      <c r="F47">
+        <v>0.8307000000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.149</v>
+      </c>
+      <c r="H47">
+        <v>1.45</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.177</v>
+      </c>
+      <c r="K47">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L47">
+        <v>0.089</v>
+      </c>
+      <c r="M47">
+        <v>0.17760366</v>
+      </c>
+      <c r="N47">
+        <v>-0.08860366000000003</v>
+      </c>
+      <c r="O47">
+        <v>-0.01417658560000001</v>
+      </c>
+      <c r="P47">
+        <v>-0.07442707440000002</v>
+      </c>
+      <c r="Q47">
+        <v>0.01357292559999998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1823636507709269</v>
+      </c>
+      <c r="T47">
+        <v>1.478865506215059</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.08017852785241025</v>
+      </c>
+      <c r="W47">
+        <v>0.1966578307451547</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.501115799077564</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2023554476556331</v>
+      </c>
+      <c r="C48">
+        <v>0.1729509086326001</v>
+      </c>
+      <c r="D48">
+        <v>0.8731109086326001</v>
+      </c>
+      <c r="E48">
+        <v>0.45316</v>
+      </c>
+      <c r="F48">
+        <v>0.84916</v>
+      </c>
+      <c r="G48">
+        <v>0.149</v>
+      </c>
+      <c r="H48">
+        <v>1.45</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.177</v>
+      </c>
+      <c r="K48">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L48">
+        <v>0.089</v>
+      </c>
+      <c r="M48">
+        <v>0.202779408</v>
+      </c>
+      <c r="N48">
+        <v>-0.113779408</v>
+      </c>
+      <c r="O48">
+        <v>-0.01820470528000001</v>
+      </c>
+      <c r="P48">
+        <v>-0.09557470272000002</v>
+      </c>
+      <c r="Q48">
+        <v>-0.007574702720000021</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1855952292968767</v>
+      </c>
+      <c r="T48">
+        <v>1.512154364411331</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07022409297101805</v>
+      </c>
+      <c r="W48">
+        <v>0.2220304865985209</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4389005810688626</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.204355447655633</v>
+      </c>
+      <c r="C49">
+        <v>0.1439432531975615</v>
+      </c>
+      <c r="D49">
+        <v>0.8625632531975616</v>
+      </c>
+      <c r="E49">
+        <v>0.47162</v>
+      </c>
+      <c r="F49">
+        <v>0.8676200000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.149</v>
+      </c>
+      <c r="H49">
+        <v>1.45</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.177</v>
+      </c>
+      <c r="K49">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L49">
+        <v>0.089</v>
+      </c>
+      <c r="M49">
+        <v>0.207187656</v>
+      </c>
+      <c r="N49">
+        <v>-0.118187656</v>
+      </c>
+      <c r="O49">
+        <v>-0.01891002496000001</v>
+      </c>
+      <c r="P49">
+        <v>-0.09927763104000002</v>
+      </c>
+      <c r="Q49">
+        <v>-0.01127763104000003</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1883649506043649</v>
+      </c>
+      <c r="T49">
+        <v>1.540685578834186</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.06872996333333681</v>
+      </c>
+      <c r="W49">
+        <v>0.2223872847559992</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.429562270833355</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.206355447655633</v>
+      </c>
+      <c r="C50">
+        <v>0.1151873987175529</v>
+      </c>
+      <c r="D50">
+        <v>0.852267398717553</v>
+      </c>
+      <c r="E50">
+        <v>0.49008</v>
+      </c>
+      <c r="F50">
+        <v>0.88608</v>
+      </c>
+      <c r="G50">
+        <v>0.149</v>
+      </c>
+      <c r="H50">
+        <v>1.45</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.177</v>
+      </c>
+      <c r="K50">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L50">
+        <v>0.089</v>
+      </c>
+      <c r="M50">
+        <v>0.211595904</v>
+      </c>
+      <c r="N50">
+        <v>-0.122595904</v>
+      </c>
+      <c r="O50">
+        <v>-0.01961534464</v>
+      </c>
+      <c r="P50">
+        <v>-0.10298055936</v>
+      </c>
+      <c r="Q50">
+        <v>-0.01498055936000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1912411996544489</v>
+      </c>
+      <c r="T50">
+        <v>1.570314147657921</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.06729808909722564</v>
+      </c>
+      <c r="W50">
+        <v>0.2227292163235825</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4206130568576602</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.208355447655633</v>
+      </c>
+      <c r="C51">
+        <v>0.08667443479924219</v>
+      </c>
+      <c r="D51">
+        <v>0.8422144347992422</v>
+      </c>
+      <c r="E51">
+        <v>0.50854</v>
+      </c>
+      <c r="F51">
+        <v>0.90454</v>
+      </c>
+      <c r="G51">
+        <v>0.149</v>
+      </c>
+      <c r="H51">
+        <v>1.45</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.177</v>
+      </c>
+      <c r="K51">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L51">
+        <v>0.089</v>
+      </c>
+      <c r="M51">
+        <v>0.216004152</v>
+      </c>
+      <c r="N51">
+        <v>-0.127004152</v>
+      </c>
+      <c r="O51">
+        <v>-0.02032066432</v>
+      </c>
+      <c r="P51">
+        <v>-0.10668348768</v>
+      </c>
+      <c r="Q51">
+        <v>-0.01868348768000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1942302427849283</v>
+      </c>
+      <c r="T51">
+        <v>1.601104621141409</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06592465870748633</v>
+      </c>
+      <c r="W51">
+        <v>0.2230571915006523</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4120291169217896</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.210355447655633</v>
+      </c>
+      <c r="C52">
+        <v>0.05839586656012874</v>
+      </c>
+      <c r="D52">
+        <v>0.8323958665601288</v>
+      </c>
+      <c r="E52">
+        <v>0.527</v>
+      </c>
+      <c r="F52">
+        <v>0.923</v>
+      </c>
+      <c r="G52">
+        <v>0.149</v>
+      </c>
+      <c r="H52">
+        <v>1.45</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.177</v>
+      </c>
+      <c r="K52">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L52">
+        <v>0.089</v>
+      </c>
+      <c r="M52">
+        <v>0.2204124</v>
+      </c>
+      <c r="N52">
+        <v>-0.1314124</v>
+      </c>
+      <c r="O52">
+        <v>-0.021025984</v>
+      </c>
+      <c r="P52">
+        <v>-0.110386416</v>
+      </c>
+      <c r="Q52">
+        <v>-0.02238641600000002</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1973388476406268</v>
+      </c>
+      <c r="T52">
+        <v>1.633126713564237</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0646061655333366</v>
+      </c>
+      <c r="W52">
+        <v>0.2233720476706392</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4037885345833537</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.212355447655633</v>
+      </c>
+      <c r="C53">
+        <v>0.0303435906874433</v>
+      </c>
+      <c r="D53">
+        <v>0.8228035906874434</v>
+      </c>
+      <c r="E53">
+        <v>0.5454600000000001</v>
+      </c>
+      <c r="F53">
+        <v>0.9414600000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.149</v>
+      </c>
+      <c r="H53">
+        <v>1.45</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.177</v>
+      </c>
+      <c r="K53">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L53">
+        <v>0.089</v>
+      </c>
+      <c r="M53">
+        <v>0.224820648</v>
+      </c>
+      <c r="N53">
+        <v>-0.135820648</v>
+      </c>
+      <c r="O53">
+        <v>-0.02173130368000001</v>
+      </c>
+      <c r="P53">
+        <v>-0.11408934432</v>
+      </c>
+      <c r="Q53">
+        <v>-0.02608934432000004</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2005743343271703</v>
+      </c>
+      <c r="T53">
+        <v>1.666455830167589</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06333937797385941</v>
+      </c>
+      <c r="W53">
+        <v>0.2236745565398424</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3958711123366212</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.214355447655633</v>
+      </c>
+      <c r="C54">
+        <v>0.002509873133528906</v>
+      </c>
+      <c r="D54">
+        <v>0.813429873133529</v>
+      </c>
+      <c r="E54">
+        <v>0.5639200000000001</v>
+      </c>
+      <c r="F54">
+        <v>0.9599200000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.149</v>
+      </c>
+      <c r="H54">
+        <v>1.45</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.177</v>
+      </c>
+      <c r="K54">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L54">
+        <v>0.089</v>
+      </c>
+      <c r="M54">
+        <v>0.229228896</v>
+      </c>
+      <c r="N54">
+        <v>-0.140228896</v>
+      </c>
+      <c r="O54">
+        <v>-0.02243662336000001</v>
+      </c>
+      <c r="P54">
+        <v>-0.11779227264</v>
+      </c>
+      <c r="Q54">
+        <v>-0.02979227264000003</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2039446329589863</v>
+      </c>
+      <c r="T54">
+        <v>1.701173659962747</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06212131301282365</v>
+      </c>
+      <c r="W54">
+        <v>0.2239654304525377</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3882582063301477</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.216355447655633</v>
+      </c>
+      <c r="C55">
+        <v>-0.02511267168133002</v>
+      </c>
+      <c r="D55">
+        <v>0.8042673283186701</v>
+      </c>
+      <c r="E55">
+        <v>0.5823800000000001</v>
+      </c>
+      <c r="F55">
+        <v>0.9783800000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.149</v>
+      </c>
+      <c r="H55">
+        <v>1.45</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.177</v>
+      </c>
+      <c r="K55">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L55">
+        <v>0.089</v>
+      </c>
+      <c r="M55">
+        <v>0.233637144</v>
+      </c>
+      <c r="N55">
+        <v>-0.1446371440000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.02314194304000001</v>
+      </c>
+      <c r="P55">
+        <v>-0.12149520096</v>
+      </c>
+      <c r="Q55">
+        <v>-0.03349520096000004</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2074583485538583</v>
+      </c>
+      <c r="T55">
+        <v>1.737368844217274</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06094921276729868</v>
+      </c>
+      <c r="W55">
+        <v>0.2242453279911691</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3809325797956167</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.218355447655633</v>
+      </c>
+      <c r="C56">
+        <v>-0.05253110027616903</v>
+      </c>
+      <c r="D56">
+        <v>0.795308899723831</v>
+      </c>
+      <c r="E56">
+        <v>0.60084</v>
+      </c>
+      <c r="F56">
+        <v>0.9968400000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.149</v>
+      </c>
+      <c r="H56">
+        <v>1.45</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.177</v>
+      </c>
+      <c r="K56">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L56">
+        <v>0.089</v>
+      </c>
+      <c r="M56">
+        <v>0.238045392</v>
+      </c>
+      <c r="N56">
+        <v>-0.149045392</v>
+      </c>
+      <c r="O56">
+        <v>-0.02384726272000001</v>
+      </c>
+      <c r="P56">
+        <v>-0.12519812928</v>
+      </c>
+      <c r="Q56">
+        <v>-0.03719812928000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2111248343919857</v>
+      </c>
+      <c r="T56">
+        <v>1.775137732135041</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.05982052364197833</v>
+      </c>
+      <c r="W56">
+        <v>0.2245148589542956</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3738782727623645</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.220355447655633</v>
+      </c>
+      <c r="C57">
+        <v>-0.07975215823387172</v>
+      </c>
+      <c r="D57">
+        <v>0.7865478417661284</v>
+      </c>
+      <c r="E57">
+        <v>0.6193000000000001</v>
+      </c>
+      <c r="F57">
+        <v>1.0153</v>
+      </c>
+      <c r="G57">
+        <v>0.149</v>
+      </c>
+      <c r="H57">
+        <v>1.45</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.177</v>
+      </c>
+      <c r="K57">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L57">
+        <v>0.089</v>
+      </c>
+      <c r="M57">
+        <v>0.24245364</v>
+      </c>
+      <c r="N57">
+        <v>-0.15345364</v>
+      </c>
+      <c r="O57">
+        <v>-0.02455258240000001</v>
+      </c>
+      <c r="P57">
+        <v>-0.1289010576</v>
+      </c>
+      <c r="Q57">
+        <v>-0.04090105760000004</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2149542751562521</v>
+      </c>
+      <c r="T57">
+        <v>1.814585237293598</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05873287775757872</v>
+      </c>
+      <c r="W57">
+        <v>0.2247745887914902</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.367080485984867</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2223554476556331</v>
+      </c>
+      <c r="C58">
+        <v>-0.1067822971408006</v>
+      </c>
+      <c r="D58">
+        <v>0.7779777028591996</v>
+      </c>
+      <c r="E58">
+        <v>0.6377600000000002</v>
+      </c>
+      <c r="F58">
+        <v>1.03376</v>
+      </c>
+      <c r="G58">
+        <v>0.149</v>
+      </c>
+      <c r="H58">
+        <v>1.45</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.177</v>
+      </c>
+      <c r="K58">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L58">
+        <v>0.089</v>
+      </c>
+      <c r="M58">
+        <v>0.2468618880000001</v>
+      </c>
+      <c r="N58">
+        <v>-0.1578618880000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.02525790208000002</v>
+      </c>
+      <c r="P58">
+        <v>-0.1326039859200001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.04460398592000006</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2189577814098032</v>
+      </c>
+      <c r="T58">
+        <v>1.855825810868452</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.05768407636905053</v>
+      </c>
+      <c r="W58">
+        <v>0.2250250425630708</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3605254773065657</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.224355447655633</v>
+      </c>
+      <c r="C59">
+        <v>-0.1336276904309293</v>
+      </c>
+      <c r="D59">
+        <v>0.7695923095690709</v>
+      </c>
+      <c r="E59">
+        <v>0.6562200000000001</v>
+      </c>
+      <c r="F59">
+        <v>1.05222</v>
+      </c>
+      <c r="G59">
+        <v>0.149</v>
+      </c>
+      <c r="H59">
+        <v>1.45</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.177</v>
+      </c>
+      <c r="K59">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L59">
+        <v>0.089</v>
+      </c>
+      <c r="M59">
+        <v>0.251270136</v>
+      </c>
+      <c r="N59">
+        <v>-0.162270136</v>
+      </c>
+      <c r="O59">
+        <v>-0.02596322176000001</v>
+      </c>
+      <c r="P59">
+        <v>-0.13630691424</v>
+      </c>
+      <c r="Q59">
+        <v>-0.04830691424000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2231474972565428</v>
+      </c>
+      <c r="T59">
+        <v>1.89898455065609</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.05667207502924264</v>
+      </c>
+      <c r="W59">
+        <v>0.2252667084830169</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3542004689327664</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.226355447655633</v>
+      </c>
+      <c r="C60">
+        <v>-0.1602942482162525</v>
+      </c>
+      <c r="D60">
+        <v>0.7613857517837476</v>
+      </c>
+      <c r="E60">
+        <v>0.6746800000000001</v>
+      </c>
+      <c r="F60">
+        <v>1.07068</v>
+      </c>
+      <c r="G60">
+        <v>0.149</v>
+      </c>
+      <c r="H60">
+        <v>1.45</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.177</v>
+      </c>
+      <c r="K60">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L60">
+        <v>0.089</v>
+      </c>
+      <c r="M60">
+        <v>0.255678384</v>
+      </c>
+      <c r="N60">
+        <v>-0.166678384</v>
+      </c>
+      <c r="O60">
+        <v>-0.02666854144000001</v>
+      </c>
+      <c r="P60">
+        <v>-0.14000984256</v>
+      </c>
+      <c r="Q60">
+        <v>-0.05200984256000005</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2275367233816986</v>
+      </c>
+      <c r="T60">
+        <v>1.944198468528854</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05569497028735913</v>
+      </c>
+      <c r="W60">
+        <v>0.2255000410953786</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3480935642959946</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.228355447655633</v>
+      </c>
+      <c r="C61">
+        <v>-0.1867876311783392</v>
+      </c>
+      <c r="D61">
+        <v>0.7533523688216608</v>
+      </c>
+      <c r="E61">
+        <v>0.69314</v>
+      </c>
+      <c r="F61">
+        <v>1.08914</v>
+      </c>
+      <c r="G61">
+        <v>0.149</v>
+      </c>
+      <c r="H61">
+        <v>1.45</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.177</v>
+      </c>
+      <c r="K61">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L61">
+        <v>0.089</v>
+      </c>
+      <c r="M61">
+        <v>0.260086632</v>
+      </c>
+      <c r="N61">
+        <v>-0.171086632</v>
+      </c>
+      <c r="O61">
+        <v>-0.02737386112000001</v>
+      </c>
+      <c r="P61">
+        <v>-0.14371277088</v>
+      </c>
+      <c r="Q61">
+        <v>-0.05571277088000004</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2321400580983254</v>
+      </c>
+      <c r="T61">
+        <v>1.991617943371021</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05475098774011576</v>
+      </c>
+      <c r="W61">
+        <v>0.2257254641276604</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3421936733757235</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.230355447655633</v>
+      </c>
+      <c r="C62">
+        <v>-0.2131132635896501</v>
+      </c>
+      <c r="D62">
+        <v>0.7454867364103498</v>
+      </c>
+      <c r="E62">
+        <v>0.7115999999999999</v>
+      </c>
+      <c r="F62">
+        <v>1.1076</v>
+      </c>
+      <c r="G62">
+        <v>0.149</v>
+      </c>
+      <c r="H62">
+        <v>1.45</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.177</v>
+      </c>
+      <c r="K62">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L62">
+        <v>0.089</v>
+      </c>
+      <c r="M62">
+        <v>0.26449488</v>
+      </c>
+      <c r="N62">
+        <v>-0.17549488</v>
+      </c>
+      <c r="O62">
+        <v>-0.0280791808</v>
+      </c>
+      <c r="P62">
+        <v>-0.1474156992</v>
+      </c>
+      <c r="Q62">
+        <v>-0.05941569920000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2369735595507835</v>
+      </c>
+      <c r="T62">
+        <v>2.041408391955296</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05383847127778051</v>
+      </c>
+      <c r="W62">
+        <v>0.225943373058866</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3364904454861282</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.232355447655633</v>
+      </c>
+      <c r="C63">
+        <v>-0.2392763455275629</v>
+      </c>
+      <c r="D63">
+        <v>0.7377836544724371</v>
+      </c>
+      <c r="E63">
+        <v>0.73006</v>
+      </c>
+      <c r="F63">
+        <v>1.12606</v>
+      </c>
+      <c r="G63">
+        <v>0.149</v>
+      </c>
+      <c r="H63">
+        <v>1.45</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.177</v>
+      </c>
+      <c r="K63">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L63">
+        <v>0.089</v>
+      </c>
+      <c r="M63">
+        <v>0.268903128</v>
+      </c>
+      <c r="N63">
+        <v>-0.1799031280000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.02878450048000001</v>
+      </c>
+      <c r="P63">
+        <v>-0.15111862752</v>
+      </c>
+      <c r="Q63">
+        <v>-0.06311862752000005</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2420549328725985</v>
+      </c>
+      <c r="T63">
+        <v>2.093752196877228</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05295587338798081</v>
+      </c>
+      <c r="W63">
+        <v>0.2261541374349502</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.33097420867488</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.234355447655633</v>
+      </c>
+      <c r="C64">
+        <v>-0.2652818643388992</v>
+      </c>
+      <c r="D64">
+        <v>0.7302381356611007</v>
+      </c>
+      <c r="E64">
+        <v>0.74852</v>
+      </c>
+      <c r="F64">
+        <v>1.14452</v>
+      </c>
+      <c r="G64">
+        <v>0.149</v>
+      </c>
+      <c r="H64">
+        <v>1.45</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.177</v>
+      </c>
+      <c r="K64">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L64">
+        <v>0.089</v>
+      </c>
+      <c r="M64">
+        <v>0.273311376</v>
+      </c>
+      <c r="N64">
+        <v>-0.184311376</v>
+      </c>
+      <c r="O64">
+        <v>-0.02948982016000001</v>
+      </c>
+      <c r="P64">
+        <v>-0.15482155584</v>
+      </c>
+      <c r="Q64">
+        <v>-0.06682155583999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2474037468955616</v>
+      </c>
+      <c r="T64">
+        <v>2.148850938900313</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0521017463978521</v>
+      </c>
+      <c r="W64">
+        <v>0.2263581029601929</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3256359149865756</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.236355447655633</v>
+      </c>
+      <c r="C65">
+        <v>-0.29113460540807</v>
+      </c>
+      <c r="D65">
+        <v>0.7228453945919301</v>
+      </c>
+      <c r="E65">
+        <v>0.7669800000000001</v>
+      </c>
+      <c r="F65">
+        <v>1.16298</v>
+      </c>
+      <c r="G65">
+        <v>0.149</v>
+      </c>
+      <c r="H65">
+        <v>1.45</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.177</v>
+      </c>
+      <c r="K65">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L65">
+        <v>0.089</v>
+      </c>
+      <c r="M65">
+        <v>0.2777196240000001</v>
+      </c>
+      <c r="N65">
+        <v>-0.1887196240000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.03019513984000002</v>
+      </c>
+      <c r="P65">
+        <v>-0.15852448416</v>
+      </c>
+      <c r="Q65">
+        <v>-0.07052448416000004</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2530416860008471</v>
+      </c>
+      <c r="T65">
+        <v>2.206927991303024</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05127473455026715</v>
+      </c>
+      <c r="W65">
+        <v>0.2265555933893962</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3204670909391696</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.238355447655633</v>
+      </c>
+      <c r="C66">
+        <v>-0.3168391622776906</v>
+      </c>
+      <c r="D66">
+        <v>0.7156008377223094</v>
+      </c>
+      <c r="E66">
+        <v>0.78544</v>
+      </c>
+      <c r="F66">
+        <v>1.18144</v>
+      </c>
+      <c r="G66">
+        <v>0.149</v>
+      </c>
+      <c r="H66">
+        <v>1.45</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.177</v>
+      </c>
+      <c r="K66">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L66">
+        <v>0.089</v>
+      </c>
+      <c r="M66">
+        <v>0.282127872</v>
+      </c>
+      <c r="N66">
+        <v>-0.193127872</v>
+      </c>
+      <c r="O66">
+        <v>-0.03090045952000001</v>
+      </c>
+      <c r="P66">
+        <v>-0.16222741248</v>
+      </c>
+      <c r="Q66">
+        <v>-0.07422741248</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2589928439453151</v>
+      </c>
+      <c r="T66">
+        <v>2.268231546616997</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05047356682291922</v>
+      </c>
+      <c r="W66">
+        <v>0.2267469122426869</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3154597926432451</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.240355447655633</v>
+      </c>
+      <c r="C67">
+        <v>-0.3423999461666478</v>
+      </c>
+      <c r="D67">
+        <v>0.7085000538333524</v>
+      </c>
+      <c r="E67">
+        <v>0.8039000000000002</v>
+      </c>
+      <c r="F67">
+        <v>1.1999</v>
+      </c>
+      <c r="G67">
+        <v>0.149</v>
+      </c>
+      <c r="H67">
+        <v>1.45</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.177</v>
+      </c>
+      <c r="K67">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L67">
+        <v>0.089</v>
+      </c>
+      <c r="M67">
+        <v>0.2865361200000001</v>
+      </c>
+      <c r="N67">
+        <v>-0.1975361200000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.03160577920000002</v>
+      </c>
+      <c r="P67">
+        <v>-0.1659303408</v>
+      </c>
+      <c r="Q67">
+        <v>-0.07793034080000005</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2652840680580384</v>
+      </c>
+      <c r="T67">
+        <v>2.333038162234625</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04969705041025892</v>
+      </c>
+      <c r="W67">
+        <v>0.2269323443620302</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3106065650641182</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.242355447655633</v>
+      </c>
+      <c r="C68">
+        <v>-0.367821194927054</v>
+      </c>
+      <c r="D68">
+        <v>0.7015388050729461</v>
+      </c>
+      <c r="E68">
+        <v>0.8223600000000001</v>
+      </c>
+      <c r="F68">
+        <v>1.21836</v>
+      </c>
+      <c r="G68">
+        <v>0.149</v>
+      </c>
+      <c r="H68">
+        <v>1.45</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.177</v>
+      </c>
+      <c r="K68">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L68">
+        <v>0.089</v>
+      </c>
+      <c r="M68">
+        <v>0.2909443680000001</v>
+      </c>
+      <c r="N68">
+        <v>-0.2019443680000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.03231109888000002</v>
+      </c>
+      <c r="P68">
+        <v>-0.16963326912</v>
+      </c>
+      <c r="Q68">
+        <v>-0.08163326912000005</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2719453641773925</v>
+      </c>
+      <c r="T68">
+        <v>2.401656931712114</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04894406479798227</v>
+      </c>
+      <c r="W68">
+        <v>0.2271121573262418</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3059004049873891</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2443554476556331</v>
+      </c>
+      <c r="C69">
+        <v>-0.3931069814783131</v>
+      </c>
+      <c r="D69">
+        <v>0.6947130185216869</v>
+      </c>
+      <c r="E69">
+        <v>0.84082</v>
+      </c>
+      <c r="F69">
+        <v>1.23682</v>
+      </c>
+      <c r="G69">
+        <v>0.149</v>
+      </c>
+      <c r="H69">
+        <v>1.45</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.177</v>
+      </c>
+      <c r="K69">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L69">
+        <v>0.089</v>
+      </c>
+      <c r="M69">
+        <v>0.295352616</v>
+      </c>
+      <c r="N69">
+        <v>-0.206352616</v>
+      </c>
+      <c r="O69">
+        <v>-0.03301641856000001</v>
+      </c>
+      <c r="P69">
+        <v>-0.17333619744</v>
+      </c>
+      <c r="Q69">
+        <v>-0.08533619744000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.279010375213071</v>
+      </c>
+      <c r="T69">
+        <v>2.474434414491269</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04821355636816164</v>
+      </c>
+      <c r="W69">
+        <v>0.227286602739283</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3013347273010102</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2463554476556331</v>
+      </c>
+      <c r="C70">
+        <v>-0.4182612217535608</v>
+      </c>
+      <c r="D70">
+        <v>0.6880187782464393</v>
+      </c>
+      <c r="E70">
+        <v>0.8592800000000002</v>
+      </c>
+      <c r="F70">
+        <v>1.25528</v>
+      </c>
+      <c r="G70">
+        <v>0.149</v>
+      </c>
+      <c r="H70">
+        <v>1.45</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.177</v>
+      </c>
+      <c r="K70">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L70">
+        <v>0.089</v>
+      </c>
+      <c r="M70">
+        <v>0.2997608640000001</v>
+      </c>
+      <c r="N70">
+        <v>-0.2107608640000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.03372173824000002</v>
+      </c>
+      <c r="P70">
+        <v>-0.1770391257600001</v>
+      </c>
+      <c r="Q70">
+        <v>-0.08903912576000006</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2865169494384795</v>
+      </c>
+      <c r="T70">
+        <v>2.551760489944122</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04750453348039455</v>
+      </c>
+      <c r="W70">
+        <v>0.2274559174048818</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.296903334252466</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2483554476556331</v>
+      </c>
+      <c r="C71">
+        <v>-0.4432876821910585</v>
+      </c>
+      <c r="D71">
+        <v>0.6814523178089416</v>
+      </c>
+      <c r="E71">
+        <v>0.8777400000000001</v>
+      </c>
+      <c r="F71">
+        <v>1.27374</v>
+      </c>
+      <c r="G71">
+        <v>0.149</v>
+      </c>
+      <c r="H71">
+        <v>1.45</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.177</v>
+      </c>
+      <c r="K71">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L71">
+        <v>0.089</v>
+      </c>
+      <c r="M71">
+        <v>0.304169112</v>
+      </c>
+      <c r="N71">
+        <v>-0.215169112</v>
+      </c>
+      <c r="O71">
+        <v>-0.03442705792000001</v>
+      </c>
+      <c r="P71">
+        <v>-0.18074205408</v>
+      </c>
+      <c r="Q71">
+        <v>-0.09274205408000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2945078187752047</v>
+      </c>
+      <c r="T71">
+        <v>2.634075344458448</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0468160619806787</v>
+      </c>
+      <c r="W71">
+        <v>0.2276203243990139</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2926003873792418</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.250355447655633</v>
+      </c>
+      <c r="C72">
+        <v>-0.4681899868006586</v>
+      </c>
+      <c r="D72">
+        <v>0.6750100131993416</v>
+      </c>
+      <c r="E72">
+        <v>0.8962000000000002</v>
+      </c>
+      <c r="F72">
+        <v>1.2922</v>
+      </c>
+      <c r="G72">
+        <v>0.149</v>
+      </c>
+      <c r="H72">
+        <v>1.45</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.177</v>
+      </c>
+      <c r="K72">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L72">
+        <v>0.089</v>
+      </c>
+      <c r="M72">
+        <v>0.3085773600000001</v>
+      </c>
+      <c r="N72">
+        <v>-0.2195773600000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.03513237760000002</v>
+      </c>
+      <c r="P72">
+        <v>-0.1844449824000001</v>
+      </c>
+      <c r="Q72">
+        <v>-0.09644498240000007</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3030314127343781</v>
+      </c>
+      <c r="T72">
+        <v>2.721877855940396</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04614726109524042</v>
+      </c>
+      <c r="W72">
+        <v>0.2277800340504566</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2884203818452525</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.252355447655633</v>
+      </c>
+      <c r="C73">
+        <v>-0.4929716238331898</v>
+      </c>
+      <c r="D73">
+        <v>0.6686883761668101</v>
+      </c>
+      <c r="E73">
+        <v>0.9146599999999999</v>
+      </c>
+      <c r="F73">
+        <v>1.31066</v>
+      </c>
+      <c r="G73">
+        <v>0.149</v>
+      </c>
+      <c r="H73">
+        <v>1.45</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.177</v>
+      </c>
+      <c r="K73">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L73">
+        <v>0.089</v>
+      </c>
+      <c r="M73">
+        <v>0.312985608</v>
+      </c>
+      <c r="N73">
+        <v>-0.223985608</v>
+      </c>
+      <c r="O73">
+        <v>-0.03583769728000001</v>
+      </c>
+      <c r="P73">
+        <v>-0.18814791072</v>
+      </c>
+      <c r="Q73">
+        <v>-0.10014791072</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3121428407597014</v>
+      </c>
+      <c r="T73">
+        <v>2.815735713041788</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04549729967136381</v>
+      </c>
+      <c r="W73">
+        <v>0.2279352448384783</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2843581229460237</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.254355447655633</v>
+      </c>
+      <c r="C74">
+        <v>-0.5176359520785617</v>
+      </c>
+      <c r="D74">
+        <v>0.6624840479214383</v>
+      </c>
+      <c r="E74">
+        <v>0.9331200000000001</v>
+      </c>
+      <c r="F74">
+        <v>1.32912</v>
+      </c>
+      <c r="G74">
+        <v>0.149</v>
+      </c>
+      <c r="H74">
+        <v>1.45</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.177</v>
+      </c>
+      <c r="K74">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L74">
+        <v>0.089</v>
+      </c>
+      <c r="M74">
+        <v>0.317393856</v>
+      </c>
+      <c r="N74">
+        <v>-0.228393856</v>
+      </c>
+      <c r="O74">
+        <v>-0.03654301696000001</v>
+      </c>
+      <c r="P74">
+        <v>-0.19185083904</v>
+      </c>
+      <c r="Q74">
+        <v>-0.10385083904</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3219050850725479</v>
+      </c>
+      <c r="T74">
+        <v>2.916297702793281</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04486539273148375</v>
+      </c>
+      <c r="W74">
+        <v>0.2280861442157217</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2804087045717734</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.256355447655633</v>
+      </c>
+      <c r="C75">
+        <v>-0.5421862068164719</v>
+      </c>
+      <c r="D75">
+        <v>0.6563937931835281</v>
+      </c>
+      <c r="E75">
+        <v>0.95158</v>
+      </c>
+      <c r="F75">
+        <v>1.34758</v>
+      </c>
+      <c r="G75">
+        <v>0.149</v>
+      </c>
+      <c r="H75">
+        <v>1.45</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.177</v>
+      </c>
+      <c r="K75">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L75">
+        <v>0.089</v>
+      </c>
+      <c r="M75">
+        <v>0.321802104</v>
+      </c>
+      <c r="N75">
+        <v>-0.232802104</v>
+      </c>
+      <c r="O75">
+        <v>-0.03724833664000001</v>
+      </c>
+      <c r="P75">
+        <v>-0.19555376736</v>
+      </c>
+      <c r="Q75">
+        <v>-0.10755376736</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3323904585937534</v>
+      </c>
+      <c r="T75">
+        <v>3.024308728822662</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04425079831050453</v>
+      </c>
+      <c r="W75">
+        <v>0.2282329093634515</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2765674894406532</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.258355447655633</v>
+      </c>
+      <c r="C76">
+        <v>-0.566625505441875</v>
+      </c>
+      <c r="D76">
+        <v>0.6504144945581252</v>
+      </c>
+      <c r="E76">
+        <v>0.9700400000000001</v>
+      </c>
+      <c r="F76">
+        <v>1.36604</v>
+      </c>
+      <c r="G76">
+        <v>0.149</v>
+      </c>
+      <c r="H76">
+        <v>1.45</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.177</v>
+      </c>
+      <c r="K76">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L76">
+        <v>0.089</v>
+      </c>
+      <c r="M76">
+        <v>0.326210352</v>
+      </c>
+      <c r="N76">
+        <v>-0.237210352</v>
+      </c>
+      <c r="O76">
+        <v>-0.03795365632000001</v>
+      </c>
+      <c r="P76">
+        <v>-0.19925669568</v>
+      </c>
+      <c r="Q76">
+        <v>-0.11125669568</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3436823993088978</v>
+      </c>
+      <c r="T76">
+        <v>3.140628295315841</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04365281454955176</v>
+      </c>
+      <c r="W76">
+        <v>0.228375707885567</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2728300909346985</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.260355447655633</v>
+      </c>
+      <c r="C77">
+        <v>-0.5909568527857603</v>
+      </c>
+      <c r="D77">
+        <v>0.6445431472142398</v>
+      </c>
+      <c r="E77">
+        <v>0.9885</v>
+      </c>
+      <c r="F77">
+        <v>1.3845</v>
+      </c>
+      <c r="G77">
+        <v>0.149</v>
+      </c>
+      <c r="H77">
+        <v>1.45</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.177</v>
+      </c>
+      <c r="K77">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L77">
+        <v>0.089</v>
+      </c>
+      <c r="M77">
+        <v>0.3306186</v>
+      </c>
+      <c r="N77">
+        <v>-0.2416186</v>
+      </c>
+      <c r="O77">
+        <v>-0.03865897600000001</v>
+      </c>
+      <c r="P77">
+        <v>-0.202959624</v>
+      </c>
+      <c r="Q77">
+        <v>-0.114959624</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3558776952812537</v>
+      </c>
+      <c r="T77">
+        <v>3.266253427128475</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0430707770222244</v>
+      </c>
+      <c r="W77">
+        <v>0.2285146984470928</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2691923563889025</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.262355447655633</v>
+      </c>
+      <c r="C78">
+        <v>-0.6151831461503227</v>
+      </c>
+      <c r="D78">
+        <v>0.6387768538496773</v>
+      </c>
+      <c r="E78">
+        <v>1.00696</v>
+      </c>
+      <c r="F78">
+        <v>1.40296</v>
+      </c>
+      <c r="G78">
+        <v>0.149</v>
+      </c>
+      <c r="H78">
+        <v>1.45</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.177</v>
+      </c>
+      <c r="K78">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L78">
+        <v>0.089</v>
+      </c>
+      <c r="M78">
+        <v>0.335026848</v>
+      </c>
+      <c r="N78">
+        <v>-0.246026848</v>
+      </c>
+      <c r="O78">
+        <v>-0.03936429568000001</v>
+      </c>
+      <c r="P78">
+        <v>-0.20666255232</v>
+      </c>
+      <c r="Q78">
+        <v>-0.11866255232</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3690892659179726</v>
+      </c>
+      <c r="T78">
+        <v>3.402347319925495</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04250405627193198</v>
+      </c>
+      <c r="W78">
+        <v>0.2286500313622626</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2656503516995748</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.264355447655633</v>
+      </c>
+      <c r="C79">
+        <v>-0.6393071800762506</v>
+      </c>
+      <c r="D79">
+        <v>0.6331128199237495</v>
+      </c>
+      <c r="E79">
+        <v>1.02542</v>
+      </c>
+      <c r="F79">
+        <v>1.42142</v>
+      </c>
+      <c r="G79">
+        <v>0.149</v>
+      </c>
+      <c r="H79">
+        <v>1.45</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.177</v>
+      </c>
+      <c r="K79">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L79">
+        <v>0.089</v>
+      </c>
+      <c r="M79">
+        <v>0.339435096</v>
+      </c>
+      <c r="N79">
+        <v>-0.250435096</v>
+      </c>
+      <c r="O79">
+        <v>-0.04006961536000001</v>
+      </c>
+      <c r="P79">
+        <v>-0.21036548064</v>
+      </c>
+      <c r="Q79">
+        <v>-0.12236548064</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3834496687839714</v>
+      </c>
+      <c r="T79">
+        <v>3.550275464270081</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04195205554112766</v>
+      </c>
+      <c r="W79">
+        <v>0.2287818491367787</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2622003471320479</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.266355447655633</v>
+      </c>
+      <c r="C80">
+        <v>-0.6633316508586146</v>
+      </c>
+      <c r="D80">
+        <v>0.6275483491413855</v>
+      </c>
+      <c r="E80">
+        <v>1.04388</v>
+      </c>
+      <c r="F80">
+        <v>1.43988</v>
+      </c>
+      <c r="G80">
+        <v>0.149</v>
+      </c>
+      <c r="H80">
+        <v>1.45</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.177</v>
+      </c>
+      <c r="K80">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L80">
+        <v>0.089</v>
+      </c>
+      <c r="M80">
+        <v>0.3438433440000001</v>
+      </c>
+      <c r="N80">
+        <v>-0.2548433440000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.04077493504000002</v>
+      </c>
+      <c r="P80">
+        <v>-0.2140684089600001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.1260684089600001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3991155628196065</v>
+      </c>
+      <c r="T80">
+        <v>3.711651621736904</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04141420867521577</v>
+      </c>
+      <c r="W80">
+        <v>0.2289102869683585</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2588388042200984</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.268355447655633</v>
+      </c>
+      <c r="C81">
+        <v>-0.6872591608266884</v>
+      </c>
+      <c r="D81">
+        <v>0.6220808391733118</v>
+      </c>
+      <c r="E81">
+        <v>1.06234</v>
+      </c>
+      <c r="F81">
+        <v>1.45834</v>
+      </c>
+      <c r="G81">
+        <v>0.149</v>
+      </c>
+      <c r="H81">
+        <v>1.45</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.177</v>
+      </c>
+      <c r="K81">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L81">
+        <v>0.089</v>
+      </c>
+      <c r="M81">
+        <v>0.3482515920000001</v>
+      </c>
+      <c r="N81">
+        <v>-0.259251592</v>
+      </c>
+      <c r="O81">
+        <v>-0.04148025472000001</v>
+      </c>
+      <c r="P81">
+        <v>-0.21777133728</v>
+      </c>
+      <c r="Q81">
+        <v>-0.12977133728</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4162734467633973</v>
+      </c>
+      <c r="T81">
+        <v>3.888396937057709</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04088997818565607</v>
+      </c>
+      <c r="W81">
+        <v>0.2290354732092653</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2555623636603505</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.270355447655633</v>
+      </c>
+      <c r="C82">
+        <v>-0.7110922224019741</v>
+      </c>
+      <c r="D82">
+        <v>0.616707777598026</v>
+      </c>
+      <c r="E82">
+        <v>1.0808</v>
+      </c>
+      <c r="F82">
+        <v>1.4768</v>
+      </c>
+      <c r="G82">
+        <v>0.149</v>
+      </c>
+      <c r="H82">
+        <v>1.45</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.177</v>
+      </c>
+      <c r="K82">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L82">
+        <v>0.089</v>
+      </c>
+      <c r="M82">
+        <v>0.3526598400000001</v>
+      </c>
+      <c r="N82">
+        <v>-0.2636598400000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.04218557440000002</v>
+      </c>
+      <c r="P82">
+        <v>-0.2214742656000001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.1334742656000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4351471191015672</v>
+      </c>
+      <c r="T82">
+        <v>4.082816783910594</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04037885345833538</v>
+      </c>
+      <c r="W82">
+        <v>0.2291575297941495</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.252367834114596</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.272355447655633</v>
+      </c>
+      <c r="C83">
+        <v>-0.7348332619477299</v>
+      </c>
+      <c r="D83">
+        <v>0.6114267380522703</v>
+      </c>
+      <c r="E83">
+        <v>1.09926</v>
+      </c>
+      <c r="F83">
+        <v>1.49526</v>
+      </c>
+      <c r="G83">
+        <v>0.149</v>
+      </c>
+      <c r="H83">
+        <v>1.45</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.177</v>
+      </c>
+      <c r="K83">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L83">
+        <v>0.089</v>
+      </c>
+      <c r="M83">
+        <v>0.3570680880000001</v>
+      </c>
+      <c r="N83">
+        <v>-0.268068088</v>
+      </c>
+      <c r="O83">
+        <v>-0.04289089408000001</v>
+      </c>
+      <c r="P83">
+        <v>-0.22517719392</v>
+      </c>
+      <c r="Q83">
+        <v>-0.13717719392</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4560074937911234</v>
+      </c>
+      <c r="T83">
+        <v>4.297701877800626</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03988034909465222</v>
+      </c>
+      <c r="W83">
+        <v>0.2292765726361971</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2492521818415764</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2743554476556331</v>
+      </c>
+      <c r="C84">
+        <v>-0.7584846234223849</v>
+      </c>
+      <c r="D84">
+        <v>0.6062353765776153</v>
+      </c>
+      <c r="E84">
+        <v>1.11772</v>
+      </c>
+      <c r="F84">
+        <v>1.51372</v>
+      </c>
+      <c r="G84">
+        <v>0.149</v>
+      </c>
+      <c r="H84">
+        <v>1.45</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.177</v>
+      </c>
+      <c r="K84">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L84">
+        <v>0.089</v>
+      </c>
+      <c r="M84">
+        <v>0.3614763360000001</v>
+      </c>
+      <c r="N84">
+        <v>-0.2724763360000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.04359621376000002</v>
+      </c>
+      <c r="P84">
+        <v>-0.2288801222400001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.1408801222400001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4791856878906302</v>
+      </c>
+      <c r="T84">
+        <v>4.536463093233994</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03939400337398573</v>
+      </c>
+      <c r="W84">
+        <v>0.2293927119942922</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2462125210874107</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2763554476556331</v>
+      </c>
+      <c r="C85">
+        <v>-0.7820485718484081</v>
+      </c>
+      <c r="D85">
+        <v>0.6011314281515919</v>
+      </c>
+      <c r="E85">
+        <v>1.13618</v>
+      </c>
+      <c r="F85">
+        <v>1.53218</v>
+      </c>
+      <c r="G85">
+        <v>0.149</v>
+      </c>
+      <c r="H85">
+        <v>1.45</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.177</v>
+      </c>
+      <c r="K85">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L85">
+        <v>0.089</v>
+      </c>
+      <c r="M85">
+        <v>0.3658845840000001</v>
+      </c>
+      <c r="N85">
+        <v>-0.276884584</v>
+      </c>
+      <c r="O85">
+        <v>-0.04430153344000001</v>
+      </c>
+      <c r="P85">
+        <v>-0.23258305056</v>
+      </c>
+      <c r="Q85">
+        <v>-0.14458305056</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.505090728354785</v>
+      </c>
+      <c r="T85">
+        <v>4.80331386342423</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0389193768273112</v>
+      </c>
+      <c r="W85">
+        <v>0.2295060528136381</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.243246105170695</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.278355447655633</v>
+      </c>
+      <c r="C86">
+        <v>-0.8055272966074102</v>
+      </c>
+      <c r="D86">
+        <v>0.5961127033925898</v>
+      </c>
+      <c r="E86">
+        <v>1.15464</v>
+      </c>
+      <c r="F86">
+        <v>1.55064</v>
+      </c>
+      <c r="G86">
+        <v>0.149</v>
+      </c>
+      <c r="H86">
+        <v>1.45</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.177</v>
+      </c>
+      <c r="K86">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L86">
+        <v>0.089</v>
+      </c>
+      <c r="M86">
+        <v>0.370292832</v>
+      </c>
+      <c r="N86">
+        <v>-0.281292832</v>
+      </c>
+      <c r="O86">
+        <v>-0.04500685312000001</v>
+      </c>
+      <c r="P86">
+        <v>-0.23628597888</v>
+      </c>
+      <c r="Q86">
+        <v>-0.14828597888</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5342338988769588</v>
+      </c>
+      <c r="T86">
+        <v>5.103520979888241</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03845605091270037</v>
+      </c>
+      <c r="W86">
+        <v>0.2296166950420472</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2403503182043772</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.280355447655633</v>
+      </c>
+      <c r="C87">
+        <v>-0.8289229145715508</v>
+      </c>
+      <c r="D87">
+        <v>0.5911770854284492</v>
+      </c>
+      <c r="E87">
+        <v>1.1731</v>
+      </c>
+      <c r="F87">
+        <v>1.5691</v>
+      </c>
+      <c r="G87">
+        <v>0.149</v>
+      </c>
+      <c r="H87">
+        <v>1.45</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.177</v>
+      </c>
+      <c r="K87">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L87">
+        <v>0.089</v>
+      </c>
+      <c r="M87">
+        <v>0.37470108</v>
+      </c>
+      <c r="N87">
+        <v>-0.2857010800000001</v>
+      </c>
+      <c r="O87">
+        <v>-0.04571217280000002</v>
+      </c>
+      <c r="P87">
+        <v>-0.2399889072</v>
+      </c>
+      <c r="Q87">
+        <v>-0.1519889072000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5672628254687559</v>
+      </c>
+      <c r="T87">
+        <v>5.44375571188079</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03800362678431565</v>
+      </c>
+      <c r="W87">
+        <v>0.2297247339239054</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2375226674019727</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.282355447655633</v>
+      </c>
+      <c r="C88">
+        <v>-0.8522374730806614</v>
+      </c>
+      <c r="D88">
+        <v>0.5863225269193386</v>
+      </c>
+      <c r="E88">
+        <v>1.19156</v>
+      </c>
+      <c r="F88">
+        <v>1.58756</v>
+      </c>
+      <c r="G88">
+        <v>0.149</v>
+      </c>
+      <c r="H88">
+        <v>1.45</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.177</v>
+      </c>
+      <c r="K88">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L88">
+        <v>0.089</v>
+      </c>
+      <c r="M88">
+        <v>0.379109328</v>
+      </c>
+      <c r="N88">
+        <v>-0.290109328</v>
+      </c>
+      <c r="O88">
+        <v>-0.04641749248000001</v>
+      </c>
+      <c r="P88">
+        <v>-0.24369183552</v>
+      </c>
+      <c r="Q88">
+        <v>-0.15569183552</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6050101701450958</v>
+      </c>
+      <c r="T88">
+        <v>5.832595405586562</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03756172414728872</v>
+      </c>
+      <c r="W88">
+        <v>0.2298302602736275</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2347607759205546</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.284355447655633</v>
+      </c>
+      <c r="C89">
+        <v>-0.87547295277388</v>
+      </c>
+      <c r="D89">
+        <v>0.5815470472261199</v>
+      </c>
+      <c r="E89">
+        <v>1.21002</v>
+      </c>
+      <c r="F89">
+        <v>1.60602</v>
+      </c>
+      <c r="G89">
+        <v>0.149</v>
+      </c>
+      <c r="H89">
+        <v>1.45</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.177</v>
+      </c>
+      <c r="K89">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L89">
+        <v>0.089</v>
+      </c>
+      <c r="M89">
+        <v>0.383517576</v>
+      </c>
+      <c r="N89">
+        <v>-0.2945175760000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.04712281216000002</v>
+      </c>
+      <c r="P89">
+        <v>-0.24739476384</v>
+      </c>
+      <c r="Q89">
+        <v>-0.15939476384</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6485647986177954</v>
+      </c>
+      <c r="T89">
+        <v>6.281256590631681</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03712998019157276</v>
+      </c>
+      <c r="W89">
+        <v>0.2299333607302524</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2320623761973296</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.286355447655633</v>
+      </c>
+      <c r="C90">
+        <v>-0.898631270284025</v>
+      </c>
+      <c r="D90">
+        <v>0.5768487297159751</v>
+      </c>
+      <c r="E90">
+        <v>1.22848</v>
+      </c>
+      <c r="F90">
+        <v>1.62448</v>
+      </c>
+      <c r="G90">
+        <v>0.149</v>
+      </c>
+      <c r="H90">
+        <v>1.45</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.177</v>
+      </c>
+      <c r="K90">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L90">
+        <v>0.089</v>
+      </c>
+      <c r="M90">
+        <v>0.387925824</v>
+      </c>
+      <c r="N90">
+        <v>-0.298925824</v>
+      </c>
+      <c r="O90">
+        <v>-0.04782813184000001</v>
+      </c>
+      <c r="P90">
+        <v>-0.25109769216</v>
+      </c>
+      <c r="Q90">
+        <v>-0.16309769216</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6993785318359451</v>
+      </c>
+      <c r="T90">
+        <v>6.80469463985099</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0367080485984867</v>
+      </c>
+      <c r="W90">
+        <v>0.2300341179946814</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2294253037405419</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.288355447655633</v>
+      </c>
+      <c r="C91">
+        <v>-0.9217142808024087</v>
+      </c>
+      <c r="D91">
+        <v>0.5722257191975914</v>
+      </c>
+      <c r="E91">
+        <v>1.24694</v>
+      </c>
+      <c r="F91">
+        <v>1.64294</v>
+      </c>
+      <c r="G91">
+        <v>0.149</v>
+      </c>
+      <c r="H91">
+        <v>1.45</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.177</v>
+      </c>
+      <c r="K91">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L91">
+        <v>0.089</v>
+      </c>
+      <c r="M91">
+        <v>0.392334072</v>
+      </c>
+      <c r="N91">
+        <v>-0.3033340720000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.04853345152000002</v>
+      </c>
+      <c r="P91">
+        <v>-0.2548006204800001</v>
+      </c>
+      <c r="Q91">
+        <v>-0.1668006204800001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.759431125639213</v>
+      </c>
+      <c r="T91">
+        <v>7.423303243473807</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03629559861423405</v>
+      </c>
+      <c r="W91">
+        <v>0.2301326110509209</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2268474913389626</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.290355447655633</v>
+      </c>
+      <c r="C92">
+        <v>-0.9447237805213015</v>
+      </c>
+      <c r="D92">
+        <v>0.5676762194786987</v>
+      </c>
+      <c r="E92">
+        <v>1.2654</v>
+      </c>
+      <c r="F92">
+        <v>1.6614</v>
+      </c>
+      <c r="G92">
+        <v>0.149</v>
+      </c>
+      <c r="H92">
+        <v>1.45</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.177</v>
+      </c>
+      <c r="K92">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L92">
+        <v>0.089</v>
+      </c>
+      <c r="M92">
+        <v>0.3967423200000001</v>
+      </c>
+      <c r="N92">
+        <v>-0.3077423200000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.04923877120000003</v>
+      </c>
+      <c r="P92">
+        <v>-0.2585035488000001</v>
+      </c>
+      <c r="Q92">
+        <v>-0.1705035488000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8314942382031343</v>
+      </c>
+      <c r="T92">
+        <v>8.165633567821189</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.035892314185187</v>
+      </c>
+      <c r="W92">
+        <v>0.2302289153725774</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2243269636574187</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.292355447655633</v>
+      </c>
+      <c r="C93">
+        <v>-0.9676615089607999</v>
+      </c>
+      <c r="D93">
+        <v>0.5631984910392002</v>
+      </c>
+      <c r="E93">
+        <v>1.28386</v>
+      </c>
+      <c r="F93">
+        <v>1.67986</v>
+      </c>
+      <c r="G93">
+        <v>0.149</v>
+      </c>
+      <c r="H93">
+        <v>1.45</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.177</v>
+      </c>
+      <c r="K93">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L93">
+        <v>0.089</v>
+      </c>
+      <c r="M93">
+        <v>0.401150568</v>
+      </c>
+      <c r="N93">
+        <v>-0.3121505680000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.04994409088000002</v>
+      </c>
+      <c r="P93">
+        <v>-0.2622064771200001</v>
+      </c>
+      <c r="Q93">
+        <v>-0.1742064771200001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9195713757812605</v>
+      </c>
+      <c r="T93">
+        <v>9.072926186467988</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03549789315018495</v>
+      </c>
+      <c r="W93">
+        <v>0.2303231031157358</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2218618321886558</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.294355447655633</v>
+      </c>
+      <c r="C94">
+        <v>-0.9905291511864363</v>
+      </c>
+      <c r="D94">
+        <v>0.5587908488135638</v>
+      </c>
+      <c r="E94">
+        <v>1.30232</v>
+      </c>
+      <c r="F94">
+        <v>1.69832</v>
+      </c>
+      <c r="G94">
+        <v>0.149</v>
+      </c>
+      <c r="H94">
+        <v>1.45</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.177</v>
+      </c>
+      <c r="K94">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L94">
+        <v>0.089</v>
+      </c>
+      <c r="M94">
+        <v>0.405558816</v>
+      </c>
+      <c r="N94">
+        <v>-0.316558816</v>
+      </c>
+      <c r="O94">
+        <v>-0.05064941056000001</v>
+      </c>
+      <c r="P94">
+        <v>-0.26590940544</v>
+      </c>
+      <c r="Q94">
+        <v>-0.17790940544</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.029667797753918</v>
+      </c>
+      <c r="T94">
+        <v>10.20704195977649</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03511204648550902</v>
+      </c>
+      <c r="W94">
+        <v>0.2304152432992605</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2194502905344314</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.296355447655633</v>
+      </c>
+      <c r="C95">
+        <v>-1.013328339923463</v>
+      </c>
+      <c r="D95">
+        <v>0.5544516600765372</v>
+      </c>
+      <c r="E95">
+        <v>1.32078</v>
+      </c>
+      <c r="F95">
+        <v>1.71678</v>
+      </c>
+      <c r="G95">
+        <v>0.149</v>
+      </c>
+      <c r="H95">
+        <v>1.45</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.177</v>
+      </c>
+      <c r="K95">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L95">
+        <v>0.089</v>
+      </c>
+      <c r="M95">
+        <v>0.409967064</v>
+      </c>
+      <c r="N95">
+        <v>-0.3209670640000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.05135473024000002</v>
+      </c>
+      <c r="P95">
+        <v>-0.26961233376</v>
+      </c>
+      <c r="Q95">
+        <v>-0.18161233376</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.171220340290192</v>
+      </c>
+      <c r="T95">
+        <v>11.66519081117313</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03473449759856807</v>
+      </c>
+      <c r="W95">
+        <v>0.2305054019734619</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2170906099910503</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.298355447655633</v>
+      </c>
+      <c r="C96">
+        <v>-1.036060657573387</v>
+      </c>
+      <c r="D96">
+        <v>0.5501793424266134</v>
+      </c>
+      <c r="E96">
+        <v>1.33924</v>
+      </c>
+      <c r="F96">
+        <v>1.73524</v>
+      </c>
+      <c r="G96">
+        <v>0.149</v>
+      </c>
+      <c r="H96">
+        <v>1.45</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.177</v>
+      </c>
+      <c r="K96">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L96">
+        <v>0.089</v>
+      </c>
+      <c r="M96">
+        <v>0.4143753120000001</v>
+      </c>
+      <c r="N96">
+        <v>-0.325375312</v>
+      </c>
+      <c r="O96">
+        <v>-0.05206004992000002</v>
+      </c>
+      <c r="P96">
+        <v>-0.27331526208</v>
+      </c>
+      <c r="Q96">
+        <v>-0.18531526208</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.359957063671891</v>
+      </c>
+      <c r="T96">
+        <v>13.60938927970199</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0343649816666684</v>
+      </c>
+      <c r="W96">
+        <v>0.2305936423779996</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2147811354166775</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.300355447655633</v>
+      </c>
+      <c r="C97">
+        <v>-1.05872763813799</v>
+      </c>
+      <c r="D97">
+        <v>0.5459723618620106</v>
+      </c>
+      <c r="E97">
+        <v>1.3577</v>
+      </c>
+      <c r="F97">
+        <v>1.7537</v>
+      </c>
+      <c r="G97">
+        <v>0.149</v>
+      </c>
+      <c r="H97">
+        <v>1.45</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.177</v>
+      </c>
+      <c r="K97">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L97">
+        <v>0.089</v>
+      </c>
+      <c r="M97">
+        <v>0.4187835600000001</v>
+      </c>
+      <c r="N97">
+        <v>-0.3297835600000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.05276536960000002</v>
+      </c>
+      <c r="P97">
+        <v>-0.2770181904000001</v>
+      </c>
+      <c r="Q97">
+        <v>-0.1890181904000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.624188476406271</v>
+      </c>
+      <c r="T97">
+        <v>16.3312671356424</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03400324501754558</v>
+      </c>
+      <c r="W97">
+        <v>0.2306800250898101</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2125202813596598</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.302355447655633</v>
+      </c>
+      <c r="C98">
+        <v>-1.081330769055741</v>
+      </c>
+      <c r="D98">
+        <v>0.5418292309442586</v>
+      </c>
+      <c r="E98">
+        <v>1.37616</v>
+      </c>
+      <c r="F98">
+        <v>1.77216</v>
+      </c>
+      <c r="G98">
+        <v>0.149</v>
+      </c>
+      <c r="H98">
+        <v>1.45</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.177</v>
+      </c>
+      <c r="K98">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L98">
+        <v>0.089</v>
+      </c>
+      <c r="M98">
+        <v>0.423191808</v>
+      </c>
+      <c r="N98">
+        <v>-0.334191808</v>
+      </c>
+      <c r="O98">
+        <v>-0.05347068928000002</v>
+      </c>
+      <c r="P98">
+        <v>-0.28072111872</v>
+      </c>
+      <c r="Q98">
+        <v>-0.19272111872</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.020535595507834</v>
+      </c>
+      <c r="T98">
+        <v>20.41408391955295</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03364904454861282</v>
+      </c>
+      <c r="W98">
+        <v>0.2307646081617913</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.21030652842883</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.304355447655633</v>
+      </c>
+      <c r="C99">
+        <v>-1.103871492955233</v>
+      </c>
+      <c r="D99">
+        <v>0.5377485070447672</v>
+      </c>
+      <c r="E99">
+        <v>1.39462</v>
+      </c>
+      <c r="F99">
+        <v>1.79062</v>
+      </c>
+      <c r="G99">
+        <v>0.149</v>
+      </c>
+      <c r="H99">
+        <v>1.45</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.177</v>
+      </c>
+      <c r="K99">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L99">
+        <v>0.089</v>
+      </c>
+      <c r="M99">
+        <v>0.4276000560000001</v>
+      </c>
+      <c r="N99">
+        <v>-0.3386000560000001</v>
+      </c>
+      <c r="O99">
+        <v>-0.05417600896000003</v>
+      </c>
+      <c r="P99">
+        <v>-0.2844240470400001</v>
+      </c>
+      <c r="Q99">
+        <v>-0.1964240470400001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.681114127343779</v>
+      </c>
+      <c r="T99">
+        <v>27.21877855940394</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03330214718213226</v>
+      </c>
+      <c r="W99">
+        <v>0.2308474472529068</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2081384198883266</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.306355447655633</v>
+      </c>
+      <c r="C100">
+        <v>-1.126351209329963</v>
+      </c>
+      <c r="D100">
+        <v>0.5337287906700372</v>
+      </c>
+      <c r="E100">
+        <v>1.41308</v>
+      </c>
+      <c r="F100">
+        <v>1.80908</v>
+      </c>
+      <c r="G100">
+        <v>0.149</v>
+      </c>
+      <c r="H100">
+        <v>1.45</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.177</v>
+      </c>
+      <c r="K100">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L100">
+        <v>0.089</v>
+      </c>
+      <c r="M100">
+        <v>0.432008304</v>
+      </c>
+      <c r="N100">
+        <v>-0.343008304</v>
+      </c>
+      <c r="O100">
+        <v>-0.05488132864000002</v>
+      </c>
+      <c r="P100">
+        <v>-0.28812697536</v>
+      </c>
+      <c r="Q100">
+        <v>-0.20012697536</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.002271191015668</v>
+      </c>
+      <c r="T100">
+        <v>40.8281678391059</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03296232935374317</v>
+      </c>
+      <c r="W100">
+        <v>0.2309285957503261</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2060145584608947</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3083554476556331</v>
+      </c>
+      <c r="C101">
+        <v>-1.148771276138569</v>
+      </c>
+      <c r="D101">
+        <v>0.5297687238614308</v>
+      </c>
+      <c r="E101">
+        <v>1.43154</v>
+      </c>
+      <c r="F101">
+        <v>1.82754</v>
+      </c>
+      <c r="G101">
+        <v>0.149</v>
+      </c>
+      <c r="H101">
+        <v>1.45</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.177</v>
+      </c>
+      <c r="K101">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L101">
+        <v>0.089</v>
+      </c>
+      <c r="M101">
+        <v>0.4364165520000001</v>
+      </c>
+      <c r="N101">
+        <v>-0.3474165520000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.05558664832000003</v>
+      </c>
+      <c r="P101">
+        <v>-0.2918299036800001</v>
+      </c>
+      <c r="Q101">
+        <v>-0.2038299036800001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.965742382031337</v>
+      </c>
+      <c r="T101">
+        <v>81.65633567821182</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03262937653198818</v>
+      </c>
+      <c r="W101">
+        <v>0.2310081048841612</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.203933603324926</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_apparel.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_apparel.xlsx
@@ -1653,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1790,22 +1790,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1020053951511319</v>
+        <v>0.1018799865188901</v>
       </c>
       <c r="C2">
-        <v>3.605466317574304</v>
+        <v>3.572489888145935</v>
       </c>
       <c r="D2">
-        <v>3.161466317574304</v>
+        <v>3.164409888145935</v>
       </c>
       <c r="E2">
-        <v>-0.172</v>
+        <v>-0.13608</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03592</v>
       </c>
       <c r="G2">
         <v>0.444</v>
@@ -1826,28 +1826,28 @@
         <v>0.277</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001806776</v>
       </c>
       <c r="N2">
-        <v>0.277</v>
+        <v>0.275193224</v>
       </c>
       <c r="O2">
-        <v>0.04432000000000001</v>
+        <v>0.04403091584</v>
       </c>
       <c r="P2">
-        <v>0.23268</v>
+        <v>0.23116230816</v>
       </c>
       <c r="Q2">
-        <v>0.37368</v>
+        <v>0.37216230816</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1020053951511319</v>
+        <v>0.1024822894130203</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461267</v>
+        <v>0.7802530492663969</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>153.3117553033691</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1872,22 +1872,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1018799865188901</v>
+        <v>0.1017545778866483</v>
       </c>
       <c r="C3">
-        <v>3.572489888145935</v>
+        <v>3.539518945211352</v>
       </c>
       <c r="D3">
-        <v>3.164409888145935</v>
+        <v>3.167358945211352</v>
       </c>
       <c r="E3">
-        <v>-0.13608</v>
+        <v>-0.10016</v>
       </c>
       <c r="F3">
-        <v>0.03592</v>
+        <v>0.07184</v>
       </c>
       <c r="G3">
         <v>0.444</v>
@@ -1908,28 +1908,28 @@
         <v>0.277</v>
       </c>
       <c r="M3">
-        <v>0.001806776</v>
+        <v>0.003613552</v>
       </c>
       <c r="N3">
-        <v>0.275193224</v>
+        <v>0.273386448</v>
       </c>
       <c r="O3">
-        <v>0.04403091584</v>
+        <v>0.04374183168</v>
       </c>
       <c r="P3">
-        <v>0.23116230816</v>
+        <v>0.22964461632</v>
       </c>
       <c r="Q3">
-        <v>0.37216230816</v>
+        <v>0.37064461632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1024822894130203</v>
+        <v>0.1029689162108656</v>
       </c>
       <c r="T3">
-        <v>0.7802530492663969</v>
+        <v>0.7869516503074889</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>153.3117553033691</v>
+        <v>76.65587765168455</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1954,22 +1954,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1017545778866483</v>
+        <v>0.1016291692544065</v>
       </c>
       <c r="C4">
-        <v>3.539518945211352</v>
+        <v>3.506553504124199</v>
       </c>
       <c r="D4">
-        <v>3.167358945211352</v>
+        <v>3.170313504124199</v>
       </c>
       <c r="E4">
-        <v>-0.10016</v>
+        <v>-0.06423999999999999</v>
       </c>
       <c r="F4">
-        <v>0.07184</v>
+        <v>0.10776</v>
       </c>
       <c r="G4">
         <v>0.444</v>
@@ -1990,28 +1990,28 @@
         <v>0.277</v>
       </c>
       <c r="M4">
-        <v>0.003613552</v>
+        <v>0.005420327999999999</v>
       </c>
       <c r="N4">
-        <v>0.273386448</v>
+        <v>0.271579672</v>
       </c>
       <c r="O4">
-        <v>0.04374183168</v>
+        <v>0.04345274752000001</v>
       </c>
       <c r="P4">
-        <v>0.22964461632</v>
+        <v>0.22812692448</v>
       </c>
       <c r="Q4">
-        <v>0.37064461632</v>
+        <v>0.3691269244800001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1029689162108656</v>
+        <v>0.1034655765509346</v>
       </c>
       <c r="T4">
-        <v>0.7869516503074889</v>
+        <v>0.7937883668339643</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.65587765168455</v>
+        <v>51.10391843445638</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2036,22 +2036,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1016291692544065</v>
+        <v>0.1015037606221647</v>
       </c>
       <c r="C5">
-        <v>3.506553504124199</v>
+        <v>3.473593580295464</v>
       </c>
       <c r="D5">
-        <v>3.170313504124199</v>
+        <v>3.173273580295464</v>
       </c>
       <c r="E5">
-        <v>-0.06423999999999999</v>
+        <v>-0.02831999999999998</v>
       </c>
       <c r="F5">
-        <v>0.10776</v>
+        <v>0.14368</v>
       </c>
       <c r="G5">
         <v>0.444</v>
@@ -2072,28 +2072,28 @@
         <v>0.277</v>
       </c>
       <c r="M5">
-        <v>0.005420327999999999</v>
+        <v>0.007227104</v>
       </c>
       <c r="N5">
-        <v>0.271579672</v>
+        <v>0.269772896</v>
       </c>
       <c r="O5">
-        <v>0.04345274752000001</v>
+        <v>0.04316366336000001</v>
       </c>
       <c r="P5">
-        <v>0.22812692448</v>
+        <v>0.22660923264</v>
       </c>
       <c r="Q5">
-        <v>0.3691269244800001</v>
+        <v>0.36760923264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1034655765509346</v>
+        <v>0.1039725839814216</v>
       </c>
       <c r="T5">
-        <v>0.7937883668339643</v>
+        <v>0.8007675149547411</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.10391843445638</v>
+        <v>38.32793882584228</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1015037606221647</v>
+        <v>0.1013783519899229</v>
       </c>
       <c r="C6">
-        <v>3.473593580295464</v>
+        <v>3.440639189193745</v>
       </c>
       <c r="D6">
-        <v>3.173273580295464</v>
+        <v>3.176239189193745</v>
       </c>
       <c r="E6">
-        <v>-0.02831999999999998</v>
+        <v>0.007600000000000023</v>
       </c>
       <c r="F6">
-        <v>0.14368</v>
+        <v>0.1796</v>
       </c>
       <c r="G6">
         <v>0.444</v>
@@ -2154,28 +2154,28 @@
         <v>0.277</v>
       </c>
       <c r="M6">
-        <v>0.007227104</v>
+        <v>0.009033879999999999</v>
       </c>
       <c r="N6">
-        <v>0.269772896</v>
+        <v>0.26796612</v>
       </c>
       <c r="O6">
-        <v>0.04316366336000001</v>
+        <v>0.04287457920000001</v>
       </c>
       <c r="P6">
-        <v>0.22660923264</v>
+        <v>0.2250915408</v>
       </c>
       <c r="Q6">
-        <v>0.36760923264</v>
+        <v>0.3660915408</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1039725839814216</v>
+        <v>0.1044902652525504</v>
       </c>
       <c r="T6">
-        <v>0.8007675149547411</v>
+        <v>0.8078935925096397</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.32793882584228</v>
+        <v>30.66235106067382</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2200,22 +2200,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1013783519899229</v>
+        <v>0.1012529433576811</v>
       </c>
       <c r="C7">
-        <v>3.440639189193745</v>
+        <v>3.407690346345518</v>
       </c>
       <c r="D7">
-        <v>3.176239189193745</v>
+        <v>3.179210346345518</v>
       </c>
       <c r="E7">
-        <v>0.007600000000000023</v>
+        <v>0.04352000000000003</v>
       </c>
       <c r="F7">
-        <v>0.1796</v>
+        <v>0.21552</v>
       </c>
       <c r="G7">
         <v>0.444</v>
@@ -2236,28 +2236,28 @@
         <v>0.277</v>
       </c>
       <c r="M7">
-        <v>0.009033879999999999</v>
+        <v>0.010840656</v>
       </c>
       <c r="N7">
-        <v>0.26796612</v>
+        <v>0.266159344</v>
       </c>
       <c r="O7">
-        <v>0.04287457920000001</v>
+        <v>0.04258549504</v>
       </c>
       <c r="P7">
-        <v>0.2250915408</v>
+        <v>0.22357384896</v>
       </c>
       <c r="Q7">
-        <v>0.3660915408</v>
+        <v>0.36457384896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1044902652525504</v>
+        <v>0.1050189610188097</v>
       </c>
       <c r="T7">
-        <v>0.8078935925096397</v>
+        <v>0.8151712887359192</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.66235106067382</v>
+        <v>25.55195921722818</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2282,22 +2282,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1012529433576811</v>
+        <v>0.1011275347254393</v>
       </c>
       <c r="C8">
-        <v>3.407690346345518</v>
+        <v>3.374747067335412</v>
       </c>
       <c r="D8">
-        <v>3.179210346345518</v>
+        <v>3.182187067335412</v>
       </c>
       <c r="E8">
-        <v>0.04352</v>
+        <v>0.07944000000000001</v>
       </c>
       <c r="F8">
-        <v>0.21552</v>
+        <v>0.25144</v>
       </c>
       <c r="G8">
         <v>0.444</v>
@@ -2318,28 +2318,28 @@
         <v>0.277</v>
       </c>
       <c r="M8">
-        <v>0.010840656</v>
+        <v>0.012647432</v>
       </c>
       <c r="N8">
-        <v>0.266159344</v>
+        <v>0.264352568</v>
       </c>
       <c r="O8">
-        <v>0.04258549504</v>
+        <v>0.04229641088</v>
       </c>
       <c r="P8">
-        <v>0.22357384896</v>
+        <v>0.22205615712</v>
       </c>
       <c r="Q8">
-        <v>0.36457384896</v>
+        <v>0.36305615712</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1050189610188097</v>
+        <v>0.1055590265864938</v>
       </c>
       <c r="T8">
-        <v>0.8151712887359192</v>
+        <v>0.8226054945584624</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.55195921722819</v>
+        <v>21.90167932905273</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2364,22 +2364,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1011275347254393</v>
+        <v>0.1010021260931975</v>
       </c>
       <c r="C9">
-        <v>3.374747067335412</v>
+        <v>3.341809367806474</v>
       </c>
       <c r="D9">
-        <v>3.182187067335412</v>
+        <v>3.185169367806474</v>
       </c>
       <c r="E9">
-        <v>0.07944000000000007</v>
+        <v>0.11536</v>
       </c>
       <c r="F9">
-        <v>0.2514400000000001</v>
+        <v>0.28736</v>
       </c>
       <c r="G9">
         <v>0.444</v>
@@ -2400,28 +2400,28 @@
         <v>0.277</v>
       </c>
       <c r="M9">
-        <v>0.012647432</v>
+        <v>0.014454208</v>
       </c>
       <c r="N9">
-        <v>0.264352568</v>
+        <v>0.262545792</v>
       </c>
       <c r="O9">
-        <v>0.04229641088</v>
+        <v>0.04200732672</v>
       </c>
       <c r="P9">
-        <v>0.22205615712</v>
+        <v>0.22053846528</v>
       </c>
       <c r="Q9">
-        <v>0.36305615712</v>
+        <v>0.36153846528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1055590265864938</v>
+        <v>0.1061108327099972</v>
       </c>
       <c r="T9">
-        <v>0.8226054945584624</v>
+        <v>0.8302013135510612</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.90167932905273</v>
+        <v>19.16396941292114</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2446,22 +2446,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1010021260931975</v>
+        <v>0.1008767174609557</v>
       </c>
       <c r="C10">
-        <v>3.341809367806474</v>
+        <v>3.308877263460454</v>
       </c>
       <c r="D10">
-        <v>3.185169367806474</v>
+        <v>3.188157263460454</v>
       </c>
       <c r="E10">
-        <v>0.11536</v>
+        <v>0.15128</v>
       </c>
       <c r="F10">
-        <v>0.28736</v>
+        <v>0.32328</v>
       </c>
       <c r="G10">
         <v>0.444</v>
@@ -2482,28 +2482,28 @@
         <v>0.277</v>
       </c>
       <c r="M10">
-        <v>0.014454208</v>
+        <v>0.016260984</v>
       </c>
       <c r="N10">
-        <v>0.262545792</v>
+        <v>0.260739016</v>
       </c>
       <c r="O10">
-        <v>0.04200732672</v>
+        <v>0.04171824256000001</v>
       </c>
       <c r="P10">
-        <v>0.22053846528</v>
+        <v>0.21902077344</v>
       </c>
       <c r="Q10">
-        <v>0.36153846528</v>
+        <v>0.3600207734400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1061108327099972</v>
+        <v>0.1066747664406106</v>
       </c>
       <c r="T10">
-        <v>0.8302013135510612</v>
+        <v>0.8379640736204202</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.16396941292114</v>
+        <v>17.03463947815213</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2528,22 +2528,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1008767174609557</v>
+        <v>0.1007513088287138</v>
       </c>
       <c r="C11">
-        <v>3.308877263460454</v>
+        <v>3.27595077005807</v>
       </c>
       <c r="D11">
-        <v>3.188157263460454</v>
+        <v>3.19115077005807</v>
       </c>
       <c r="E11">
-        <v>0.15128</v>
+        <v>0.1872</v>
       </c>
       <c r="F11">
-        <v>0.32328</v>
+        <v>0.3592</v>
       </c>
       <c r="G11">
         <v>0.444</v>
@@ -2564,28 +2564,28 @@
         <v>0.277</v>
       </c>
       <c r="M11">
-        <v>0.016260984</v>
+        <v>0.01806776</v>
       </c>
       <c r="N11">
-        <v>0.260739016</v>
+        <v>0.25893224</v>
       </c>
       <c r="O11">
-        <v>0.04171824256000001</v>
+        <v>0.04142915840000001</v>
       </c>
       <c r="P11">
-        <v>0.21902077344</v>
+        <v>0.2175030816</v>
       </c>
       <c r="Q11">
-        <v>0.3600207734400001</v>
+        <v>0.3585030816</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1066747664406106</v>
+        <v>0.1072512320319043</v>
       </c>
       <c r="T11">
-        <v>0.8379640736204202</v>
+        <v>0.8458993394690985</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.03463947815213</v>
+        <v>15.33117553033691</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2610,22 +2610,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1007513088287138</v>
+        <v>0.100625900196472</v>
       </c>
       <c r="C12">
-        <v>3.27595077005807</v>
+        <v>3.243029903419288</v>
       </c>
       <c r="D12">
-        <v>3.19115077005807</v>
+        <v>3.194149903419288</v>
       </c>
       <c r="E12">
-        <v>0.1872</v>
+        <v>0.22312</v>
       </c>
       <c r="F12">
-        <v>0.3592</v>
+        <v>0.39512</v>
       </c>
       <c r="G12">
         <v>0.444</v>
@@ -2646,28 +2646,28 @@
         <v>0.277</v>
       </c>
       <c r="M12">
-        <v>0.01806776</v>
+        <v>0.019874536</v>
       </c>
       <c r="N12">
-        <v>0.25893224</v>
+        <v>0.257125464</v>
       </c>
       <c r="O12">
-        <v>0.04142915840000001</v>
+        <v>0.04114007424</v>
       </c>
       <c r="P12">
-        <v>0.2175030816</v>
+        <v>0.21598538976</v>
       </c>
       <c r="Q12">
-        <v>0.3585030816</v>
+        <v>0.35698538976</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1072512320319043</v>
+        <v>0.1078406519061483</v>
       </c>
       <c r="T12">
-        <v>0.8458993394690985</v>
+        <v>0.854012925898646</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.33117553033691</v>
+        <v>13.93743230030628</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2692,22 +2692,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.100625900196472</v>
+        <v>0.1006516915642302</v>
       </c>
       <c r="C13">
-        <v>3.243029903419288</v>
+        <v>3.206492645376937</v>
       </c>
       <c r="D13">
-        <v>3.194149903419288</v>
+        <v>3.193532645376937</v>
       </c>
       <c r="E13">
-        <v>0.22312</v>
+        <v>0.25904</v>
       </c>
       <c r="F13">
-        <v>0.39512</v>
+        <v>0.43104</v>
       </c>
       <c r="G13">
         <v>0.444</v>
@@ -2728,45 +2728,45 @@
         <v>0.277</v>
       </c>
       <c r="M13">
-        <v>0.019874536</v>
+        <v>0.022327872</v>
       </c>
       <c r="N13">
-        <v>0.257125464</v>
+        <v>0.2546721280000001</v>
       </c>
       <c r="O13">
-        <v>0.04114007424</v>
+        <v>0.04074754048000001</v>
       </c>
       <c r="P13">
-        <v>0.21598538976</v>
+        <v>0.21392458752</v>
       </c>
       <c r="Q13">
-        <v>0.35698538976</v>
+        <v>0.35492458752</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1078406519061483</v>
+        <v>0.1084434676866252</v>
       </c>
       <c r="T13">
-        <v>0.854012925898646</v>
+        <v>0.8623109120197739</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.16</v>
       </c>
       <c r="W13">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.93743230030628</v>
+        <v>12.40601880913685</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2774,22 +2774,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1006516915642302</v>
+        <v>0.1005388829319884</v>
       </c>
       <c r="C14">
-        <v>3.206492645376937</v>
+        <v>3.173274226546004</v>
       </c>
       <c r="D14">
-        <v>3.193532645376937</v>
+        <v>3.196234226546004</v>
       </c>
       <c r="E14">
-        <v>0.25904</v>
+        <v>0.2949600000000001</v>
       </c>
       <c r="F14">
-        <v>0.43104</v>
+        <v>0.46696</v>
       </c>
       <c r="G14">
         <v>0.444</v>
@@ -2810,28 +2810,28 @@
         <v>0.277</v>
       </c>
       <c r="M14">
-        <v>0.022327872</v>
+        <v>0.024188528</v>
       </c>
       <c r="N14">
-        <v>0.2546721280000001</v>
+        <v>0.252811472</v>
       </c>
       <c r="O14">
-        <v>0.04074754048000001</v>
+        <v>0.04044983552</v>
       </c>
       <c r="P14">
-        <v>0.21392458752</v>
+        <v>0.21236163648</v>
       </c>
       <c r="Q14">
-        <v>0.35492458752</v>
+        <v>0.35336163648</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1084434676866252</v>
+        <v>0.1090601413011361</v>
       </c>
       <c r="T14">
-        <v>0.8623109120197739</v>
+        <v>0.8707996564425372</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.40601880913685</v>
+        <v>11.45170966997248</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2856,22 +2856,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1005388829319884</v>
+        <v>0.1004260742997466</v>
       </c>
       <c r="C15">
-        <v>3.173274226546004</v>
+        <v>3.140060382410921</v>
       </c>
       <c r="D15">
-        <v>3.196234226546004</v>
+        <v>3.198940382410921</v>
       </c>
       <c r="E15">
-        <v>0.2949600000000001</v>
+        <v>0.3308800000000001</v>
       </c>
       <c r="F15">
-        <v>0.46696</v>
+        <v>0.5028800000000001</v>
       </c>
       <c r="G15">
         <v>0.444</v>
@@ -2892,28 +2892,28 @@
         <v>0.277</v>
       </c>
       <c r="M15">
-        <v>0.024188528</v>
+        <v>0.02604918400000001</v>
       </c>
       <c r="N15">
-        <v>0.252811472</v>
+        <v>0.250950816</v>
       </c>
       <c r="O15">
-        <v>0.04044983552</v>
+        <v>0.04015213056000001</v>
       </c>
       <c r="P15">
-        <v>0.21236163648</v>
+        <v>0.21079868544</v>
       </c>
       <c r="Q15">
-        <v>0.35336163648</v>
+        <v>0.35179868544</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1090601413011361</v>
+        <v>0.1096911561624961</v>
       </c>
       <c r="T15">
-        <v>0.8707996564425372</v>
+        <v>0.8794858135262948</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.45170966997248</v>
+        <v>10.63373040783158</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2938,22 +2938,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1004260742997466</v>
+        <v>0.1003132656675048</v>
       </c>
       <c r="C16">
-        <v>3.140060382410921</v>
+        <v>3.106851124601309</v>
       </c>
       <c r="D16">
-        <v>3.198940382410921</v>
+        <v>3.201651124601309</v>
       </c>
       <c r="E16">
-        <v>0.3308800000000001</v>
+        <v>0.3668000000000001</v>
       </c>
       <c r="F16">
-        <v>0.5028800000000001</v>
+        <v>0.5388000000000001</v>
       </c>
       <c r="G16">
         <v>0.444</v>
@@ -2974,28 +2974,28 @@
         <v>0.277</v>
       </c>
       <c r="M16">
-        <v>0.02604918400000001</v>
+        <v>0.02790984</v>
       </c>
       <c r="N16">
-        <v>0.250950816</v>
+        <v>0.24909016</v>
       </c>
       <c r="O16">
-        <v>0.04015213056000001</v>
+        <v>0.03985442560000001</v>
       </c>
       <c r="P16">
-        <v>0.21079868544</v>
+        <v>0.2092357344</v>
       </c>
       <c r="Q16">
-        <v>0.35179868544</v>
+        <v>0.3502357344</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1096911561624961</v>
+        <v>0.1103370184323586</v>
       </c>
       <c r="T16">
-        <v>0.8794858135262948</v>
+        <v>0.8883763507767291</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.63373040783158</v>
+        <v>9.92481504730948</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3020,22 +3020,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1003132656675048</v>
+        <v>0.100428937035263</v>
       </c>
       <c r="C17">
-        <v>3.10685112460131</v>
+        <v>3.068151651845495</v>
       </c>
       <c r="D17">
-        <v>3.201651124601309</v>
+        <v>3.198871651845495</v>
       </c>
       <c r="E17">
-        <v>0.3668</v>
+        <v>0.40272</v>
       </c>
       <c r="F17">
-        <v>0.5387999999999999</v>
+        <v>0.57472</v>
       </c>
       <c r="G17">
         <v>0.444</v>
@@ -3056,45 +3056,45 @@
         <v>0.277</v>
       </c>
       <c r="M17">
-        <v>0.02790984</v>
+        <v>0.03074752</v>
       </c>
       <c r="N17">
-        <v>0.24909016</v>
+        <v>0.24625248</v>
       </c>
       <c r="O17">
-        <v>0.03985442560000001</v>
+        <v>0.03940039680000001</v>
       </c>
       <c r="P17">
-        <v>0.2092357344</v>
+        <v>0.2068520832</v>
       </c>
       <c r="Q17">
-        <v>0.3502357344</v>
+        <v>0.3478520832</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1103370184323586</v>
+        <v>0.110998258375313</v>
       </c>
       <c r="T17">
-        <v>0.8883763507767291</v>
+        <v>0.8974785674855069</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.16</v>
       </c>
       <c r="W17">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.924815047309481</v>
+        <v>9.008856649251713</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3102,22 +3102,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.100428937035263</v>
+        <v>0.1003304084030212</v>
       </c>
       <c r="C18">
-        <v>3.068151651845495</v>
+        <v>3.034598896166734</v>
       </c>
       <c r="D18">
-        <v>3.198871651845495</v>
+        <v>3.201238896166734</v>
       </c>
       <c r="E18">
-        <v>0.40272</v>
+        <v>0.4386400000000001</v>
       </c>
       <c r="F18">
-        <v>0.57472</v>
+        <v>0.6106400000000001</v>
       </c>
       <c r="G18">
         <v>0.444</v>
@@ -3138,28 +3138,28 @@
         <v>0.277</v>
       </c>
       <c r="M18">
-        <v>0.03074752</v>
+        <v>0.03266924</v>
       </c>
       <c r="N18">
-        <v>0.24625248</v>
+        <v>0.24433076</v>
       </c>
       <c r="O18">
-        <v>0.03940039680000001</v>
+        <v>0.0390929216</v>
       </c>
       <c r="P18">
-        <v>0.2068520832</v>
+        <v>0.2052378384</v>
       </c>
       <c r="Q18">
-        <v>0.3478520832</v>
+        <v>0.3462378384</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.110998258375313</v>
+        <v>0.1116754318108689</v>
       </c>
       <c r="T18">
-        <v>0.8974785674855069</v>
+        <v>0.9068001147173881</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.008856649251713</v>
+        <v>8.478923905178082</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3184,22 +3184,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1003304084030212</v>
+        <v>0.1002318797707793</v>
       </c>
       <c r="C19">
-        <v>3.034598896166734</v>
+        <v>3.001049646721635</v>
       </c>
       <c r="D19">
-        <v>3.201238896166734</v>
+        <v>3.203609646721635</v>
       </c>
       <c r="E19">
-        <v>0.4386400000000001</v>
+        <v>0.4745600000000001</v>
       </c>
       <c r="F19">
-        <v>0.6106400000000001</v>
+        <v>0.6465600000000001</v>
       </c>
       <c r="G19">
         <v>0.444</v>
@@ -3220,28 +3220,28 @@
         <v>0.277</v>
       </c>
       <c r="M19">
-        <v>0.03266924</v>
+        <v>0.03459096</v>
       </c>
       <c r="N19">
-        <v>0.24433076</v>
+        <v>0.24240904</v>
       </c>
       <c r="O19">
-        <v>0.0390929216</v>
+        <v>0.03878544640000001</v>
       </c>
       <c r="P19">
-        <v>0.2052378384</v>
+        <v>0.2036235936</v>
       </c>
       <c r="Q19">
-        <v>0.3462378384</v>
+        <v>0.3446235936</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1116754318108689</v>
+        <v>0.1123691216716821</v>
       </c>
       <c r="T19">
-        <v>0.9068001147173881</v>
+        <v>0.9163490167598027</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.478923905178082</v>
+        <v>8.007872577112632</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3266,22 +3266,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1002318797707794</v>
+        <v>0.1002610311385375</v>
       </c>
       <c r="C20">
-        <v>3.001049646721635</v>
+        <v>2.964427854254112</v>
       </c>
       <c r="D20">
-        <v>3.203609646721635</v>
+        <v>3.202907854254112</v>
       </c>
       <c r="E20">
-        <v>0.47456</v>
+        <v>0.51048</v>
       </c>
       <c r="F20">
-        <v>0.64656</v>
+        <v>0.68248</v>
       </c>
       <c r="G20">
         <v>0.444</v>
@@ -3302,45 +3302,45 @@
         <v>0.277</v>
       </c>
       <c r="M20">
-        <v>0.03459096</v>
+        <v>0.037058664</v>
       </c>
       <c r="N20">
-        <v>0.24240904</v>
+        <v>0.239941336</v>
       </c>
       <c r="O20">
-        <v>0.03878544640000001</v>
+        <v>0.03839061376</v>
       </c>
       <c r="P20">
-        <v>0.2036235936</v>
+        <v>0.20155072224</v>
       </c>
       <c r="Q20">
-        <v>0.3446235936</v>
+        <v>0.34255072224</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1123691216716821</v>
+        <v>0.1130799396772068</v>
       </c>
       <c r="T20">
-        <v>0.9163490167598027</v>
+        <v>0.9261336941612893</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.16</v>
       </c>
       <c r="W20">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>8.007872577112632</v>
+        <v>7.474635351128687</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3348,22 +3348,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1002610311385375</v>
+        <v>0.1001692225062957</v>
       </c>
       <c r="C21">
-        <v>2.964427854254112</v>
+        <v>2.93071910434444</v>
       </c>
       <c r="D21">
-        <v>3.202907854254112</v>
+        <v>3.20511910434444</v>
       </c>
       <c r="E21">
-        <v>0.51048</v>
+        <v>0.5464</v>
       </c>
       <c r="F21">
-        <v>0.68248</v>
+        <v>0.7184</v>
       </c>
       <c r="G21">
         <v>0.444</v>
@@ -3384,28 +3384,28 @@
         <v>0.277</v>
       </c>
       <c r="M21">
-        <v>0.037058664</v>
+        <v>0.03900912</v>
       </c>
       <c r="N21">
-        <v>0.239941336</v>
+        <v>0.23799088</v>
       </c>
       <c r="O21">
-        <v>0.03839061376</v>
+        <v>0.0380785408</v>
       </c>
       <c r="P21">
-        <v>0.20155072224</v>
+        <v>0.1999123392</v>
       </c>
       <c r="Q21">
-        <v>0.34255072224</v>
+        <v>0.3409123392</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1130799396772068</v>
+        <v>0.1138085281328697</v>
       </c>
       <c r="T21">
-        <v>0.9261336941612893</v>
+        <v>0.9361629884978133</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.474635351128687</v>
+        <v>7.100903583572252</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3430,22 +3430,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1001692225062957</v>
+        <v>0.1000774138740539</v>
       </c>
       <c r="C22">
-        <v>2.93071910434444</v>
+        <v>2.897013409786505</v>
       </c>
       <c r="D22">
-        <v>3.20511910434444</v>
+        <v>3.207333409786505</v>
       </c>
       <c r="E22">
-        <v>0.5464</v>
+        <v>0.5823200000000002</v>
       </c>
       <c r="F22">
-        <v>0.7184</v>
+        <v>0.7543200000000001</v>
       </c>
       <c r="G22">
         <v>0.444</v>
@@ -3466,28 +3466,28 @@
         <v>0.277</v>
       </c>
       <c r="M22">
-        <v>0.03900912</v>
+        <v>0.040959576</v>
       </c>
       <c r="N22">
-        <v>0.23799088</v>
+        <v>0.236040424</v>
       </c>
       <c r="O22">
-        <v>0.0380785408</v>
+        <v>0.03776646784000001</v>
       </c>
       <c r="P22">
-        <v>0.1999123392</v>
+        <v>0.19827395616</v>
       </c>
       <c r="Q22">
-        <v>0.3409123392</v>
+        <v>0.33927395616</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1138085281328697</v>
+        <v>0.114555561865891</v>
       </c>
       <c r="T22">
-        <v>0.9361629884978133</v>
+        <v>0.946446189020072</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.100903583572252</v>
+        <v>6.762765317687859</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3512,22 +3512,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1000774138740539</v>
+        <v>0.0999856052418121</v>
       </c>
       <c r="C23">
-        <v>2.897013409786505</v>
+        <v>2.863310776917191</v>
       </c>
       <c r="D23">
-        <v>3.207333409786505</v>
+        <v>3.209550776917192</v>
       </c>
       <c r="E23">
-        <v>0.5823199999999999</v>
+        <v>0.6182400000000001</v>
       </c>
       <c r="F23">
-        <v>0.75432</v>
+        <v>0.7902400000000001</v>
       </c>
       <c r="G23">
         <v>0.444</v>
@@ -3548,28 +3548,28 @@
         <v>0.277</v>
       </c>
       <c r="M23">
-        <v>0.040959576</v>
+        <v>0.042910032</v>
       </c>
       <c r="N23">
-        <v>0.236040424</v>
+        <v>0.234089968</v>
       </c>
       <c r="O23">
-        <v>0.03776646784000001</v>
+        <v>0.03745439488000001</v>
       </c>
       <c r="P23">
-        <v>0.19827395616</v>
+        <v>0.19663557312</v>
       </c>
       <c r="Q23">
-        <v>0.33927395616</v>
+        <v>0.33763557312</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.114555561865891</v>
+        <v>0.1153217503100155</v>
       </c>
       <c r="T23">
-        <v>0.946446189020072</v>
+        <v>0.9569930613505936</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.76276531768786</v>
+        <v>6.455366894156593</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3594,22 +3594,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0999856052418121</v>
+        <v>0.09989379660957029</v>
       </c>
       <c r="C24">
-        <v>2.863310776917191</v>
+        <v>2.829611212090923</v>
       </c>
       <c r="D24">
-        <v>3.209550776917192</v>
+        <v>3.211771212090923</v>
       </c>
       <c r="E24">
-        <v>0.6182400000000001</v>
+        <v>0.6541600000000001</v>
       </c>
       <c r="F24">
-        <v>0.7902400000000001</v>
+        <v>0.82616</v>
       </c>
       <c r="G24">
         <v>0.444</v>
@@ -3630,28 +3630,28 @@
         <v>0.277</v>
       </c>
       <c r="M24">
-        <v>0.042910032</v>
+        <v>0.044860488</v>
       </c>
       <c r="N24">
-        <v>0.234089968</v>
+        <v>0.232139512</v>
       </c>
       <c r="O24">
-        <v>0.03745439488000001</v>
+        <v>0.03714232192000001</v>
       </c>
       <c r="P24">
-        <v>0.19663557312</v>
+        <v>0.19499719008</v>
       </c>
       <c r="Q24">
-        <v>0.33763557312</v>
+        <v>0.33599719008</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1153217503100155</v>
+        <v>0.1161078397526887</v>
       </c>
       <c r="T24">
-        <v>0.9569930613505936</v>
+        <v>0.9678138784169731</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.455366894156593</v>
+        <v>6.174698768323697</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3676,22 +3676,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09989379660957029</v>
+        <v>0.1000035879773285</v>
       </c>
       <c r="C25">
-        <v>2.829611212090923</v>
+        <v>2.791036215482812</v>
       </c>
       <c r="D25">
-        <v>3.211771212090923</v>
+        <v>3.209116215482812</v>
       </c>
       <c r="E25">
-        <v>0.6541600000000001</v>
+        <v>0.69008</v>
       </c>
       <c r="F25">
-        <v>0.82616</v>
+        <v>0.8620800000000001</v>
       </c>
       <c r="G25">
         <v>0.444</v>
@@ -3712,45 +3712,45 @@
         <v>0.277</v>
       </c>
       <c r="M25">
-        <v>0.044860488</v>
+        <v>0.04767302400000001</v>
       </c>
       <c r="N25">
-        <v>0.232139512</v>
+        <v>0.229326976</v>
       </c>
       <c r="O25">
-        <v>0.03714232192000001</v>
+        <v>0.03669231616</v>
       </c>
       <c r="P25">
-        <v>0.19499719008</v>
+        <v>0.19263465984</v>
       </c>
       <c r="Q25">
-        <v>0.33599719008</v>
+        <v>0.33363465984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1161078397526887</v>
+        <v>0.1169146157596427</v>
       </c>
       <c r="T25">
-        <v>0.9678138784169731</v>
+        <v>0.9789194538272046</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.174698768323697</v>
+        <v>5.810413872633713</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3758,22 +3758,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1000035879773285</v>
+        <v>0.09992017934508667</v>
       </c>
       <c r="C26">
-        <v>2.791036215482812</v>
+        <v>2.757132818640028</v>
       </c>
       <c r="D26">
-        <v>3.209116215482812</v>
+        <v>3.211132818640028</v>
       </c>
       <c r="E26">
-        <v>0.69008</v>
+        <v>0.726</v>
       </c>
       <c r="F26">
-        <v>0.86208</v>
+        <v>0.898</v>
       </c>
       <c r="G26">
         <v>0.444</v>
@@ -3794,28 +3794,28 @@
         <v>0.277</v>
       </c>
       <c r="M26">
-        <v>0.047673024</v>
+        <v>0.04965940000000001</v>
       </c>
       <c r="N26">
-        <v>0.229326976</v>
+        <v>0.2273406</v>
       </c>
       <c r="O26">
-        <v>0.03669231616</v>
+        <v>0.036374496</v>
       </c>
       <c r="P26">
-        <v>0.19263465984</v>
+        <v>0.190966104</v>
       </c>
       <c r="Q26">
-        <v>0.33363465984</v>
+        <v>0.331966104</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1169146157596427</v>
+        <v>0.1177429057934489</v>
       </c>
       <c r="T26">
-        <v>0.9789194538272046</v>
+        <v>0.9903211779150423</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.810413872633714</v>
+        <v>5.577997317728365</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3840,22 +3840,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09992017934508667</v>
+        <v>0.09983677071284486</v>
       </c>
       <c r="C27">
-        <v>2.757132818640028</v>
+        <v>2.723231957850865</v>
       </c>
       <c r="D27">
-        <v>3.211132818640028</v>
+        <v>3.213151957850866</v>
       </c>
       <c r="E27">
-        <v>0.726</v>
+        <v>0.7619200000000002</v>
       </c>
       <c r="F27">
-        <v>0.898</v>
+        <v>0.9339200000000001</v>
       </c>
       <c r="G27">
         <v>0.444</v>
@@ -3876,28 +3876,28 @@
         <v>0.277</v>
       </c>
       <c r="M27">
-        <v>0.04965940000000001</v>
+        <v>0.051645776</v>
       </c>
       <c r="N27">
-        <v>0.2273406</v>
+        <v>0.225354224</v>
       </c>
       <c r="O27">
-        <v>0.036374496</v>
+        <v>0.03605667584</v>
       </c>
       <c r="P27">
-        <v>0.190966104</v>
+        <v>0.18929754816</v>
       </c>
       <c r="Q27">
-        <v>0.331966104</v>
+        <v>0.33029754816</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1177429057934489</v>
+        <v>0.1185935820443849</v>
       </c>
       <c r="T27">
-        <v>0.9903211779150423</v>
+        <v>1.002031056707957</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.577997317728365</v>
+        <v>5.363458959354197</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3922,22 +3922,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09983677071284486</v>
+        <v>0.09975336208060305</v>
       </c>
       <c r="C28">
-        <v>2.723231957850865</v>
+        <v>2.689333637902297</v>
       </c>
       <c r="D28">
-        <v>3.213151957850866</v>
+        <v>3.215173637902297</v>
       </c>
       <c r="E28">
-        <v>0.7619200000000002</v>
+        <v>0.7978400000000001</v>
       </c>
       <c r="F28">
-        <v>0.9339200000000001</v>
+        <v>0.96984</v>
       </c>
       <c r="G28">
         <v>0.444</v>
@@ -3958,28 +3958,28 @@
         <v>0.277</v>
       </c>
       <c r="M28">
-        <v>0.051645776</v>
+        <v>0.053632152</v>
       </c>
       <c r="N28">
-        <v>0.225354224</v>
+        <v>0.223367848</v>
       </c>
       <c r="O28">
-        <v>0.03605667584</v>
+        <v>0.03573885568000001</v>
       </c>
       <c r="P28">
-        <v>0.18929754816</v>
+        <v>0.18762899232</v>
       </c>
       <c r="Q28">
-        <v>0.33029754816</v>
+        <v>0.32862899232</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1185935820443849</v>
+        <v>0.1194675644939768</v>
       </c>
       <c r="T28">
-        <v>1.002031056707957</v>
+        <v>1.014061754097937</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.363458959354197</v>
+        <v>5.164812331229968</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4004,22 +4004,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09975336208060305</v>
+        <v>0.09966995344836123</v>
       </c>
       <c r="C29">
-        <v>2.689333637902297</v>
+        <v>2.655437863593348</v>
       </c>
       <c r="D29">
-        <v>3.215173637902297</v>
+        <v>3.217197863593348</v>
       </c>
       <c r="E29">
-        <v>0.7978400000000001</v>
+        <v>0.8337600000000003</v>
       </c>
       <c r="F29">
-        <v>0.96984</v>
+        <v>1.00576</v>
       </c>
       <c r="G29">
         <v>0.444</v>
@@ -4040,28 +4040,28 @@
         <v>0.277</v>
       </c>
       <c r="M29">
-        <v>0.053632152</v>
+        <v>0.05561852800000001</v>
       </c>
       <c r="N29">
-        <v>0.223367848</v>
+        <v>0.221381472</v>
       </c>
       <c r="O29">
-        <v>0.03573885568000001</v>
+        <v>0.03542103552</v>
       </c>
       <c r="P29">
-        <v>0.18762899232</v>
+        <v>0.18596043648</v>
       </c>
       <c r="Q29">
-        <v>0.32862899232</v>
+        <v>0.32696043648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1194675644939768</v>
+        <v>0.120365824233835</v>
       </c>
       <c r="T29">
-        <v>1.014061754097937</v>
+        <v>1.026426637526528</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.164812331229968</v>
+        <v>4.980354747971754</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4086,22 +4086,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09966995344836123</v>
+        <v>0.09958654481611943</v>
       </c>
       <c r="C30">
-        <v>2.655437863593348</v>
+        <v>2.62154463973514</v>
       </c>
       <c r="D30">
-        <v>3.217197863593348</v>
+        <v>3.21922463973514</v>
       </c>
       <c r="E30">
-        <v>0.8337600000000003</v>
+        <v>0.8696800000000002</v>
       </c>
       <c r="F30">
-        <v>1.00576</v>
+        <v>1.04168</v>
       </c>
       <c r="G30">
         <v>0.444</v>
@@ -4122,28 +4122,28 @@
         <v>0.277</v>
       </c>
       <c r="M30">
-        <v>0.05561852800000001</v>
+        <v>0.05760490400000001</v>
       </c>
       <c r="N30">
-        <v>0.221381472</v>
+        <v>0.219395096</v>
       </c>
       <c r="O30">
-        <v>0.03542103552</v>
+        <v>0.03510321536</v>
       </c>
       <c r="P30">
-        <v>0.18596043648</v>
+        <v>0.18429188064</v>
       </c>
       <c r="Q30">
-        <v>0.32696043648</v>
+        <v>0.32529188064</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.120365824233835</v>
+        <v>0.121289387064957</v>
       </c>
       <c r="T30">
-        <v>1.026426637526528</v>
+        <v>1.039139827530573</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.980354747971754</v>
+        <v>4.808618377352039</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4168,22 +4168,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09958654481611941</v>
+        <v>0.0995031361838776</v>
       </c>
       <c r="C31">
-        <v>2.62154463973514</v>
+        <v>2.587653971150923</v>
       </c>
       <c r="D31">
-        <v>3.21922463973514</v>
+        <v>3.221253971150923</v>
       </c>
       <c r="E31">
-        <v>0.86968</v>
+        <v>0.9056</v>
       </c>
       <c r="F31">
-        <v>1.04168</v>
+        <v>1.0776</v>
       </c>
       <c r="G31">
         <v>0.444</v>
@@ -4204,28 +4204,28 @@
         <v>0.277</v>
       </c>
       <c r="M31">
-        <v>0.057604904</v>
+        <v>0.05959128</v>
       </c>
       <c r="N31">
-        <v>0.219395096</v>
+        <v>0.21740872</v>
       </c>
       <c r="O31">
-        <v>0.03510321536</v>
+        <v>0.03478539520000001</v>
       </c>
       <c r="P31">
-        <v>0.18429188064</v>
+        <v>0.1826233248</v>
       </c>
       <c r="Q31">
-        <v>0.32529188064</v>
+        <v>0.3236233248</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1212893870649569</v>
+        <v>0.1222393374055394</v>
       </c>
       <c r="T31">
-        <v>1.039139827530572</v>
+        <v>1.052216251534732</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.808618377352039</v>
+        <v>4.648331098106972</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4250,22 +4250,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0995031361838776</v>
+        <v>0.1000707275516358</v>
       </c>
       <c r="C32">
-        <v>2.587653971150923</v>
+        <v>2.537974794766289</v>
       </c>
       <c r="D32">
-        <v>3.221253971150923</v>
+        <v>3.207494794766289</v>
       </c>
       <c r="E32">
-        <v>0.9056</v>
+        <v>0.9415200000000001</v>
       </c>
       <c r="F32">
-        <v>1.0776</v>
+        <v>1.11352</v>
       </c>
       <c r="G32">
         <v>0.444</v>
@@ -4286,45 +4286,45 @@
         <v>0.277</v>
       </c>
       <c r="M32">
-        <v>0.05959128</v>
+        <v>0.06436145600000001</v>
       </c>
       <c r="N32">
-        <v>0.21740872</v>
+        <v>0.212638544</v>
       </c>
       <c r="O32">
-        <v>0.03478539520000001</v>
+        <v>0.03402216704</v>
       </c>
       <c r="P32">
-        <v>0.1826233248</v>
+        <v>0.17861637696</v>
       </c>
       <c r="Q32">
-        <v>0.3236233248</v>
+        <v>0.31961637696</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1222393374055394</v>
+        <v>0.1232168225386026</v>
       </c>
       <c r="T32">
-        <v>1.052216251534732</v>
+        <v>1.065671702321622</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.648331098106972</v>
+        <v>4.303818111262119</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4332,22 +4332,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1000707275516358</v>
+        <v>0.100008318919394</v>
       </c>
       <c r="C33">
-        <v>2.537974794766289</v>
+        <v>2.503561909548108</v>
       </c>
       <c r="D33">
-        <v>3.207494794766289</v>
+        <v>3.209001909548109</v>
       </c>
       <c r="E33">
-        <v>0.9415200000000001</v>
+        <v>0.9774400000000001</v>
       </c>
       <c r="F33">
-        <v>1.11352</v>
+        <v>1.14944</v>
       </c>
       <c r="G33">
         <v>0.444</v>
@@ -4368,28 +4368,28 @@
         <v>0.277</v>
       </c>
       <c r="M33">
-        <v>0.06436145600000001</v>
+        <v>0.06643763200000001</v>
       </c>
       <c r="N33">
-        <v>0.212638544</v>
+        <v>0.210562368</v>
       </c>
       <c r="O33">
-        <v>0.03402216704</v>
+        <v>0.03368997888</v>
       </c>
       <c r="P33">
-        <v>0.17861637696</v>
+        <v>0.17687238912</v>
       </c>
       <c r="Q33">
-        <v>0.31961637696</v>
+        <v>0.31787238912</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1232168225386026</v>
+        <v>0.1242230572344029</v>
       </c>
       <c r="T33">
-        <v>1.065671702321622</v>
+        <v>1.079522901661066</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.303818111262119</v>
+        <v>4.169323795285178</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4414,22 +4414,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.100008318919394</v>
+        <v>0.09994591028715218</v>
       </c>
       <c r="C34">
-        <v>2.503561909548108</v>
+        <v>2.469150441300417</v>
       </c>
       <c r="D34">
-        <v>3.209001909548109</v>
+        <v>3.210510441300417</v>
       </c>
       <c r="E34">
-        <v>0.9774400000000001</v>
+        <v>1.01336</v>
       </c>
       <c r="F34">
-        <v>1.14944</v>
+        <v>1.18536</v>
       </c>
       <c r="G34">
         <v>0.444</v>
@@ -4450,28 +4450,28 @@
         <v>0.277</v>
       </c>
       <c r="M34">
-        <v>0.06643763200000001</v>
+        <v>0.06851380800000001</v>
       </c>
       <c r="N34">
-        <v>0.210562368</v>
+        <v>0.208486192</v>
       </c>
       <c r="O34">
-        <v>0.03368997888</v>
+        <v>0.03335779072</v>
       </c>
       <c r="P34">
-        <v>0.17687238912</v>
+        <v>0.17512840128</v>
       </c>
       <c r="Q34">
-        <v>0.31787238912</v>
+        <v>0.31612840128</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1242230572344029</v>
+        <v>0.1252593287867943</v>
       </c>
       <c r="T34">
-        <v>1.079522901661066</v>
+        <v>1.093787569637509</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.169323795285178</v>
+        <v>4.042980649973506</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4496,22 +4496,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09994591028715218</v>
+        <v>0.1008831016549104</v>
       </c>
       <c r="C35">
-        <v>2.469150441300417</v>
+        <v>2.410725022843774</v>
       </c>
       <c r="D35">
-        <v>3.210510441300417</v>
+        <v>3.188005022843774</v>
       </c>
       <c r="E35">
-        <v>1.01336</v>
+        <v>1.04928</v>
       </c>
       <c r="F35">
-        <v>1.18536</v>
+        <v>1.22128</v>
       </c>
       <c r="G35">
         <v>0.444</v>
@@ -4532,45 +4532,45 @@
         <v>0.277</v>
       </c>
       <c r="M35">
-        <v>0.06851380800000001</v>
+        <v>0.07486446400000001</v>
       </c>
       <c r="N35">
-        <v>0.208486192</v>
+        <v>0.202135536</v>
       </c>
       <c r="O35">
-        <v>0.03335779072</v>
+        <v>0.03234168576</v>
       </c>
       <c r="P35">
-        <v>0.17512840128</v>
+        <v>0.16979385024</v>
       </c>
       <c r="Q35">
-        <v>0.31612840128</v>
+        <v>0.3107938502399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1252593287867943</v>
+        <v>0.12632700250744</v>
       </c>
       <c r="T35">
-        <v>1.093787569637509</v>
+        <v>1.108484500279905</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.16</v>
       </c>
       <c r="W35">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.042980649973506</v>
+        <v>3.700019811802833</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4578,22 +4578,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1008831016549104</v>
+        <v>0.1008500930226685</v>
       </c>
       <c r="C36">
-        <v>2.410725022843774</v>
+        <v>2.375592319651424</v>
       </c>
       <c r="D36">
-        <v>3.188005022843774</v>
+        <v>3.188792319651424</v>
       </c>
       <c r="E36">
-        <v>1.04928</v>
+        <v>1.0852</v>
       </c>
       <c r="F36">
-        <v>1.22128</v>
+        <v>1.2572</v>
       </c>
       <c r="G36">
         <v>0.444</v>
@@ -4614,28 +4614,28 @@
         <v>0.277</v>
       </c>
       <c r="M36">
-        <v>0.07486446400000001</v>
+        <v>0.07706636</v>
       </c>
       <c r="N36">
-        <v>0.202135536</v>
+        <v>0.19993364</v>
       </c>
       <c r="O36">
-        <v>0.03234168576</v>
+        <v>0.0319893824</v>
       </c>
       <c r="P36">
-        <v>0.16979385024</v>
+        <v>0.1679442576</v>
       </c>
       <c r="Q36">
-        <v>0.3107938502399999</v>
+        <v>0.3089442576</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.12632700250744</v>
+        <v>0.1274275277271824</v>
       </c>
       <c r="T36">
-        <v>1.108484500279905</v>
+        <v>1.123633644172836</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.700019811802833</v>
+        <v>3.594304960037038</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4660,22 +4660,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1008500930226685</v>
+        <v>0.1016638043904267</v>
       </c>
       <c r="C37">
-        <v>2.375592319651424</v>
+        <v>2.320376968423276</v>
       </c>
       <c r="D37">
-        <v>3.188792319651424</v>
+        <v>3.169496968423277</v>
       </c>
       <c r="E37">
-        <v>1.0852</v>
+        <v>1.12112</v>
       </c>
       <c r="F37">
-        <v>1.2572</v>
+        <v>1.29312</v>
       </c>
       <c r="G37">
         <v>0.444</v>
@@ -4696,45 +4696,45 @@
         <v>0.277</v>
       </c>
       <c r="M37">
-        <v>0.07706636</v>
+        <v>0.08288899200000002</v>
       </c>
       <c r="N37">
-        <v>0.19993364</v>
+        <v>0.194111008</v>
       </c>
       <c r="O37">
-        <v>0.0319893824</v>
+        <v>0.03105776128</v>
       </c>
       <c r="P37">
-        <v>0.1679442576</v>
+        <v>0.16305324672</v>
       </c>
       <c r="Q37">
-        <v>0.3089442576</v>
+        <v>0.30405324672</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1274275277271824</v>
+        <v>0.1285624443600418</v>
       </c>
       <c r="T37">
-        <v>1.123633644172836</v>
+        <v>1.139256198812422</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.16</v>
       </c>
       <c r="W37">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.594304960037038</v>
+        <v>3.341818899185069</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4742,22 +4742,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1016638043904267</v>
+        <v>0.1016543157581849</v>
       </c>
       <c r="C38">
-        <v>2.320376968423278</v>
+        <v>2.284680624483358</v>
       </c>
       <c r="D38">
-        <v>3.169496968423278</v>
+        <v>3.169720624483358</v>
       </c>
       <c r="E38">
-        <v>1.12112</v>
+        <v>1.15704</v>
       </c>
       <c r="F38">
-        <v>1.29312</v>
+        <v>1.32904</v>
       </c>
       <c r="G38">
         <v>0.444</v>
@@ -4778,28 +4778,28 @@
         <v>0.277</v>
       </c>
       <c r="M38">
-        <v>0.08288899200000001</v>
+        <v>0.08519146400000001</v>
       </c>
       <c r="N38">
-        <v>0.194111008</v>
+        <v>0.191808536</v>
       </c>
       <c r="O38">
-        <v>0.03105776128000001</v>
+        <v>0.03068936576000001</v>
       </c>
       <c r="P38">
-        <v>0.16305324672</v>
+        <v>0.16111917024</v>
       </c>
       <c r="Q38">
-        <v>0.30405324672</v>
+        <v>0.30211917024</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1285624443600418</v>
+        <v>0.129733390092357</v>
       </c>
       <c r="T38">
-        <v>1.139256198812421</v>
+        <v>1.155374707567549</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.341818899185069</v>
+        <v>3.251499469477364</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4824,22 +4824,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1016543157581849</v>
+        <v>0.1016448271259431</v>
       </c>
       <c r="C39">
-        <v>2.284680624483358</v>
+        <v>2.248984312110318</v>
       </c>
       <c r="D39">
-        <v>3.169720624483358</v>
+        <v>3.169944312110318</v>
       </c>
       <c r="E39">
-        <v>1.15704</v>
+        <v>1.19296</v>
       </c>
       <c r="F39">
-        <v>1.32904</v>
+        <v>1.36496</v>
       </c>
       <c r="G39">
         <v>0.444</v>
@@ -4860,28 +4860,28 @@
         <v>0.277</v>
       </c>
       <c r="M39">
-        <v>0.08519146400000001</v>
+        <v>0.08749393600000001</v>
       </c>
       <c r="N39">
-        <v>0.191808536</v>
+        <v>0.189506064</v>
       </c>
       <c r="O39">
-        <v>0.03068936576000001</v>
+        <v>0.03032097024000001</v>
       </c>
       <c r="P39">
-        <v>0.16111917024</v>
+        <v>0.15918509376</v>
       </c>
       <c r="Q39">
-        <v>0.30211917024</v>
+        <v>0.30018509376</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.129733390092357</v>
+        <v>0.1309421082676502</v>
       </c>
       <c r="T39">
-        <v>1.155374707567549</v>
+        <v>1.172013168218003</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.251499469477364</v>
+        <v>3.165933693964802</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4906,22 +4906,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1016448271259431</v>
+        <v>0.1016353384937013</v>
       </c>
       <c r="C40">
-        <v>2.248984312110318</v>
+        <v>2.21328803131084</v>
       </c>
       <c r="D40">
-        <v>3.169944312110318</v>
+        <v>3.17016803131084</v>
       </c>
       <c r="E40">
-        <v>1.19296</v>
+        <v>1.22888</v>
       </c>
       <c r="F40">
-        <v>1.36496</v>
+        <v>1.40088</v>
       </c>
       <c r="G40">
         <v>0.444</v>
@@ -4942,28 +4942,28 @@
         <v>0.277</v>
       </c>
       <c r="M40">
-        <v>0.08749393600000001</v>
+        <v>0.08979640800000001</v>
       </c>
       <c r="N40">
-        <v>0.189506064</v>
+        <v>0.187203592</v>
       </c>
       <c r="O40">
-        <v>0.03032097024000001</v>
+        <v>0.02995257472000001</v>
       </c>
       <c r="P40">
-        <v>0.15918509376</v>
+        <v>0.15725101728</v>
       </c>
       <c r="Q40">
-        <v>0.30018509376</v>
+        <v>0.29825101728</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1309421082676502</v>
+        <v>0.1321904565470513</v>
       </c>
       <c r="T40">
-        <v>1.172013168218003</v>
+        <v>1.189197152168473</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.165933693964802</v>
+        <v>3.084755906940064</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4988,22 +4988,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1016353384937013</v>
+        <v>0.1016258498614595</v>
       </c>
       <c r="C41">
-        <v>2.21328803131084</v>
+        <v>2.177591782091609</v>
       </c>
       <c r="D41">
-        <v>3.17016803131084</v>
+        <v>3.170391782091609</v>
       </c>
       <c r="E41">
-        <v>1.22888</v>
+        <v>1.2648</v>
       </c>
       <c r="F41">
-        <v>1.40088</v>
+        <v>1.4368</v>
       </c>
       <c r="G41">
         <v>0.444</v>
@@ -5024,28 +5024,28 @@
         <v>0.277</v>
       </c>
       <c r="M41">
-        <v>0.08979640800000001</v>
+        <v>0.09209888000000001</v>
       </c>
       <c r="N41">
-        <v>0.187203592</v>
+        <v>0.18490112</v>
       </c>
       <c r="O41">
-        <v>0.02995257472000001</v>
+        <v>0.0295841792</v>
       </c>
       <c r="P41">
-        <v>0.15725101728</v>
+        <v>0.1553169408</v>
       </c>
       <c r="Q41">
-        <v>0.29825101728</v>
+        <v>0.2963169408</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1321904565470513</v>
+        <v>0.1334804164357659</v>
       </c>
       <c r="T41">
-        <v>1.189197152168473</v>
+        <v>1.206953935583958</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.084755906940064</v>
+        <v>3.007637009266563</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5070,22 +5070,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1016258498614595</v>
+        <v>0.1043026812292177</v>
       </c>
       <c r="C42">
-        <v>2.177591782091609</v>
+        <v>2.079777546402018</v>
       </c>
       <c r="D42">
-        <v>3.170391782091609</v>
+        <v>3.108497546402018</v>
       </c>
       <c r="E42">
-        <v>1.2648</v>
+        <v>1.30072</v>
       </c>
       <c r="F42">
-        <v>1.4368</v>
+        <v>1.47272</v>
       </c>
       <c r="G42">
         <v>0.444</v>
@@ -5106,45 +5106,45 @@
         <v>0.277</v>
       </c>
       <c r="M42">
-        <v>0.09209888000000001</v>
+        <v>0.105888568</v>
       </c>
       <c r="N42">
-        <v>0.18490112</v>
+        <v>0.171111432</v>
       </c>
       <c r="O42">
-        <v>0.0295841792</v>
+        <v>0.02737782912</v>
       </c>
       <c r="P42">
-        <v>0.1553169408</v>
+        <v>0.14373360288</v>
       </c>
       <c r="Q42">
-        <v>0.2963169408</v>
+        <v>0.28473360288</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1334804164357659</v>
+        <v>0.1348141037783351</v>
       </c>
       <c r="T42">
-        <v>1.206953935583958</v>
+        <v>1.225312643860984</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.16</v>
       </c>
       <c r="W42">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.007637009266563</v>
+        <v>2.615957560215565</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5152,22 +5152,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1043026812292177</v>
+        <v>0.1043587125969759</v>
       </c>
       <c r="C43">
-        <v>2.079777546402018</v>
+        <v>2.04258778952317</v>
       </c>
       <c r="D43">
-        <v>3.108497546402018</v>
+        <v>3.10722778952317</v>
       </c>
       <c r="E43">
-        <v>1.30072</v>
+        <v>1.33664</v>
       </c>
       <c r="F43">
-        <v>1.47272</v>
+        <v>1.50864</v>
       </c>
       <c r="G43">
         <v>0.444</v>
@@ -5188,28 +5188,28 @@
         <v>0.277</v>
       </c>
       <c r="M43">
-        <v>0.105888568</v>
+        <v>0.108471216</v>
       </c>
       <c r="N43">
-        <v>0.171111432</v>
+        <v>0.168528784</v>
       </c>
       <c r="O43">
-        <v>0.02737782912</v>
+        <v>0.02696460544</v>
       </c>
       <c r="P43">
-        <v>0.14373360288</v>
+        <v>0.14156417856</v>
       </c>
       <c r="Q43">
-        <v>0.28473360288</v>
+        <v>0.2825641785599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1348141037783351</v>
+        <v>0.1361937803396136</v>
       </c>
       <c r="T43">
-        <v>1.225312643860984</v>
+        <v>1.244304411044115</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.615957560215565</v>
+        <v>2.553672856400909</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5234,22 +5234,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1043587125969759</v>
+        <v>0.1058234239647341</v>
       </c>
       <c r="C44">
-        <v>2.04258778952317</v>
+        <v>1.97383928165056</v>
       </c>
       <c r="D44">
-        <v>3.10722778952317</v>
+        <v>3.07439928165056</v>
       </c>
       <c r="E44">
-        <v>1.33664</v>
+        <v>1.37256</v>
       </c>
       <c r="F44">
-        <v>1.50864</v>
+        <v>1.54456</v>
       </c>
       <c r="G44">
         <v>0.444</v>
@@ -5270,45 +5270,45 @@
         <v>0.277</v>
       </c>
       <c r="M44">
-        <v>0.108471216</v>
+        <v>0.117077648</v>
       </c>
       <c r="N44">
-        <v>0.168528784</v>
+        <v>0.159922352</v>
       </c>
       <c r="O44">
-        <v>0.02696460544</v>
+        <v>0.02558757632</v>
       </c>
       <c r="P44">
-        <v>0.14156417856</v>
+        <v>0.13433477568</v>
       </c>
       <c r="Q44">
-        <v>0.28256417856</v>
+        <v>0.27533477568</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1361937803396136</v>
+        <v>0.1376218666047966</v>
       </c>
       <c r="T44">
-        <v>1.244304411044115</v>
+        <v>1.263962556023146</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.16</v>
       </c>
       <c r="W44">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.553672856400909</v>
+        <v>2.365951184806856</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5316,22 +5316,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1058234239647341</v>
+        <v>0.1059122153324923</v>
       </c>
       <c r="C45">
-        <v>1.97383928165056</v>
+        <v>1.935951490728417</v>
       </c>
       <c r="D45">
-        <v>3.07439928165056</v>
+        <v>3.072431490728417</v>
       </c>
       <c r="E45">
-        <v>1.37256</v>
+        <v>1.40848</v>
       </c>
       <c r="F45">
-        <v>1.54456</v>
+        <v>1.58048</v>
       </c>
       <c r="G45">
         <v>0.444</v>
@@ -5352,28 +5352,28 @@
         <v>0.277</v>
       </c>
       <c r="M45">
-        <v>0.117077648</v>
+        <v>0.119800384</v>
       </c>
       <c r="N45">
-        <v>0.159922352</v>
+        <v>0.157199616</v>
       </c>
       <c r="O45">
-        <v>0.02558757632</v>
+        <v>0.02515193856</v>
       </c>
       <c r="P45">
-        <v>0.13433477568</v>
+        <v>0.13204767744</v>
       </c>
       <c r="Q45">
-        <v>0.27533477568</v>
+        <v>0.27304767744</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1376218666047966</v>
+        <v>0.139100955950879</v>
       </c>
       <c r="T45">
-        <v>1.263962556023146</v>
+        <v>1.28432277760857</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.365951184806856</v>
+        <v>2.312179566970336</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5398,22 +5398,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1059122153324923</v>
+        <v>0.1060010067002505</v>
       </c>
       <c r="C46">
-        <v>1.935951490728417</v>
+        <v>1.898066217191893</v>
       </c>
       <c r="D46">
-        <v>3.072431490728417</v>
+        <v>3.070466217191893</v>
       </c>
       <c r="E46">
-        <v>1.40848</v>
+        <v>1.4444</v>
       </c>
       <c r="F46">
-        <v>1.58048</v>
+        <v>1.6164</v>
       </c>
       <c r="G46">
         <v>0.444</v>
@@ -5434,28 +5434,28 @@
         <v>0.277</v>
       </c>
       <c r="M46">
-        <v>0.119800384</v>
+        <v>0.12252312</v>
       </c>
       <c r="N46">
-        <v>0.157199616</v>
+        <v>0.15447688</v>
       </c>
       <c r="O46">
-        <v>0.02515193856</v>
+        <v>0.0247163008</v>
       </c>
       <c r="P46">
-        <v>0.13204767744</v>
+        <v>0.1297605792</v>
       </c>
       <c r="Q46">
-        <v>0.27304767744</v>
+        <v>0.2707605792</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.139100955950879</v>
+        <v>0.1406338303640917</v>
       </c>
       <c r="T46">
-        <v>1.28432277760857</v>
+        <v>1.30542337088801</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.312179566970336</v>
+        <v>2.26079779881544</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5480,22 +5480,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1060010067002505</v>
+        <v>0.1060897980680086</v>
       </c>
       <c r="C47">
-        <v>1.898066217191893</v>
+        <v>1.860183456213356</v>
       </c>
       <c r="D47">
-        <v>3.070466217191893</v>
+        <v>3.068503456213356</v>
       </c>
       <c r="E47">
-        <v>1.4444</v>
+        <v>1.48032</v>
       </c>
       <c r="F47">
-        <v>1.6164</v>
+        <v>1.65232</v>
       </c>
       <c r="G47">
         <v>0.444</v>
@@ -5516,28 +5516,28 @@
         <v>0.277</v>
       </c>
       <c r="M47">
-        <v>0.12252312</v>
+        <v>0.125245856</v>
       </c>
       <c r="N47">
-        <v>0.15447688</v>
+        <v>0.151754144</v>
       </c>
       <c r="O47">
-        <v>0.0247163008</v>
+        <v>0.02428066304</v>
       </c>
       <c r="P47">
-        <v>0.1297605792</v>
+        <v>0.12747348096</v>
       </c>
       <c r="Q47">
-        <v>0.2707605792</v>
+        <v>0.26847348096</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1406338303640917</v>
+        <v>0.1422234779037197</v>
       </c>
       <c r="T47">
-        <v>1.30542337088801</v>
+        <v>1.327305467622244</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.26079779881544</v>
+        <v>2.211650020580322</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5562,22 +5562,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1060897980680086</v>
+        <v>0.1061785894357668</v>
       </c>
       <c r="C48">
-        <v>1.860183456213356</v>
+        <v>1.822303202977511</v>
       </c>
       <c r="D48">
-        <v>3.068503456213356</v>
+        <v>3.066543202977511</v>
       </c>
       <c r="E48">
-        <v>1.48032</v>
+        <v>1.51624</v>
       </c>
       <c r="F48">
-        <v>1.65232</v>
+        <v>1.68824</v>
       </c>
       <c r="G48">
         <v>0.444</v>
@@ -5598,28 +5598,28 @@
         <v>0.277</v>
       </c>
       <c r="M48">
-        <v>0.125245856</v>
+        <v>0.127968592</v>
       </c>
       <c r="N48">
-        <v>0.151754144</v>
+        <v>0.149031408</v>
       </c>
       <c r="O48">
-        <v>0.02428066304</v>
+        <v>0.02384502528</v>
       </c>
       <c r="P48">
-        <v>0.12747348096</v>
+        <v>0.12518638272</v>
       </c>
       <c r="Q48">
-        <v>0.26847348096</v>
+        <v>0.2661863827199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1422234779037197</v>
+        <v>0.1438731121429563</v>
       </c>
       <c r="T48">
-        <v>1.327305467622244</v>
+        <v>1.350013303855883</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.211650020580322</v>
+        <v>2.164593637163719</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5644,22 +5644,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1061785894357668</v>
+        <v>0.106267380803525</v>
       </c>
       <c r="C49">
-        <v>1.822303202977511</v>
+        <v>1.784425452681361</v>
       </c>
       <c r="D49">
-        <v>3.066543202977511</v>
+        <v>3.064585452681361</v>
       </c>
       <c r="E49">
-        <v>1.51624</v>
+        <v>1.55216</v>
       </c>
       <c r="F49">
-        <v>1.68824</v>
+        <v>1.72416</v>
       </c>
       <c r="G49">
         <v>0.444</v>
@@ -5680,28 +5680,28 @@
         <v>0.277</v>
       </c>
       <c r="M49">
-        <v>0.127968592</v>
+        <v>0.130691328</v>
       </c>
       <c r="N49">
-        <v>0.149031408</v>
+        <v>0.146308672</v>
       </c>
       <c r="O49">
-        <v>0.02384502528</v>
+        <v>0.02340938752</v>
       </c>
       <c r="P49">
-        <v>0.12518638272</v>
+        <v>0.12289928448</v>
       </c>
       <c r="Q49">
-        <v>0.2661863827199999</v>
+        <v>0.26389928448</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1438731121429563</v>
+        <v>0.1455861938529327</v>
       </c>
       <c r="T49">
-        <v>1.350013303855883</v>
+        <v>1.3735945184062</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.164593637163719</v>
+        <v>2.119497936389475</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5726,22 +5726,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.106267380803525</v>
+        <v>0.1063561721712832</v>
       </c>
       <c r="C50">
-        <v>1.784425452681361</v>
+        <v>1.746550200534164</v>
       </c>
       <c r="D50">
-        <v>3.064585452681361</v>
+        <v>3.062630200534164</v>
       </c>
       <c r="E50">
-        <v>1.55216</v>
+        <v>1.58808</v>
       </c>
       <c r="F50">
-        <v>1.72416</v>
+        <v>1.76008</v>
       </c>
       <c r="G50">
         <v>0.444</v>
@@ -5762,28 +5762,28 @@
         <v>0.277</v>
       </c>
       <c r="M50">
-        <v>0.130691328</v>
+        <v>0.133414064</v>
       </c>
       <c r="N50">
-        <v>0.146308672</v>
+        <v>0.143585936</v>
       </c>
       <c r="O50">
-        <v>0.02340938752000001</v>
+        <v>0.02297374976</v>
       </c>
       <c r="P50">
-        <v>0.12289928448</v>
+        <v>0.12061218624</v>
       </c>
       <c r="Q50">
-        <v>0.26389928448</v>
+        <v>0.26161218624</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1455861938529327</v>
+        <v>0.1473664552378102</v>
       </c>
       <c r="T50">
-        <v>1.3735945184062</v>
+        <v>1.398100486468295</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.119497936389475</v>
+        <v>2.076242876463159</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5808,22 +5808,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1063561721712832</v>
+        <v>0.1064449635390414</v>
       </c>
       <c r="C51">
-        <v>1.746550200534164</v>
+        <v>1.708677441757397</v>
       </c>
       <c r="D51">
-        <v>3.062630200534164</v>
+        <v>3.060677441757397</v>
       </c>
       <c r="E51">
-        <v>1.58808</v>
+        <v>1.624</v>
       </c>
       <c r="F51">
-        <v>1.76008</v>
+        <v>1.796</v>
       </c>
       <c r="G51">
         <v>0.444</v>
@@ -5844,28 +5844,28 @@
         <v>0.277</v>
       </c>
       <c r="M51">
-        <v>0.133414064</v>
+        <v>0.1361368</v>
       </c>
       <c r="N51">
-        <v>0.143585936</v>
+        <v>0.1408632</v>
       </c>
       <c r="O51">
-        <v>0.02297374976</v>
+        <v>0.022538112</v>
       </c>
       <c r="P51">
-        <v>0.12061218624</v>
+        <v>0.118325088</v>
       </c>
       <c r="Q51">
-        <v>0.26161218624</v>
+        <v>0.259325088</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1473664552378102</v>
+        <v>0.1492179270780828</v>
       </c>
       <c r="T51">
-        <v>1.398100486468295</v>
+        <v>1.423586693252873</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.076242876463159</v>
+        <v>2.034718018933896</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5890,22 +5890,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1064449635390414</v>
+        <v>0.1126170349067996</v>
       </c>
       <c r="C52">
-        <v>1.708677441757397</v>
+        <v>1.542860901595282</v>
       </c>
       <c r="D52">
-        <v>3.060677441757397</v>
+        <v>2.930780901595282</v>
       </c>
       <c r="E52">
-        <v>1.624</v>
+        <v>1.65992</v>
       </c>
       <c r="F52">
-        <v>1.796</v>
+        <v>1.83192</v>
       </c>
       <c r="G52">
         <v>0.444</v>
@@ -5926,45 +5926,45 @@
         <v>0.277</v>
       </c>
       <c r="M52">
-        <v>0.1361368</v>
+        <v>0.1648728</v>
       </c>
       <c r="N52">
-        <v>0.1408632</v>
+        <v>0.1121272</v>
       </c>
       <c r="O52">
-        <v>0.022538112</v>
+        <v>0.01794035200000001</v>
       </c>
       <c r="P52">
-        <v>0.118325088</v>
+        <v>0.09418684800000003</v>
       </c>
       <c r="Q52">
-        <v>0.259325088</v>
+        <v>0.235186848</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1492179270780828</v>
+        <v>0.1511449691975502</v>
       </c>
       <c r="T52">
-        <v>1.423586693252873</v>
+        <v>1.450113153375598</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.16</v>
       </c>
       <c r="W52">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.034718018933896</v>
+        <v>1.680083070100102</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5972,22 +5972,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1126170349067996</v>
+        <v>0.1128251062745578</v>
       </c>
       <c r="C53">
-        <v>1.542860901595282</v>
+        <v>1.502753700322924</v>
       </c>
       <c r="D53">
-        <v>2.930780901595282</v>
+        <v>2.926593700322925</v>
       </c>
       <c r="E53">
-        <v>1.65992</v>
+        <v>1.69584</v>
       </c>
       <c r="F53">
-        <v>1.83192</v>
+        <v>1.86784</v>
       </c>
       <c r="G53">
         <v>0.444</v>
@@ -6008,28 +6008,28 @@
         <v>0.277</v>
       </c>
       <c r="M53">
-        <v>0.1648728</v>
+        <v>0.1681056</v>
       </c>
       <c r="N53">
-        <v>0.1121272</v>
+        <v>0.1088944</v>
       </c>
       <c r="O53">
-        <v>0.01794035200000001</v>
+        <v>0.017423104</v>
       </c>
       <c r="P53">
-        <v>0.09418684800000003</v>
+        <v>0.09147129600000001</v>
       </c>
       <c r="Q53">
-        <v>0.235186848</v>
+        <v>0.232471296</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1511449691975502</v>
+        <v>0.153152304738662</v>
       </c>
       <c r="T53">
-        <v>1.450113153375598</v>
+        <v>1.477744882670102</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.680083070100102</v>
+        <v>1.647773780290484</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6054,22 +6054,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1128251062745578</v>
+        <v>0.1130331776423159</v>
       </c>
       <c r="C54">
-        <v>1.502753700322924</v>
+        <v>1.462658446474785</v>
       </c>
       <c r="D54">
-        <v>2.926593700322925</v>
+        <v>2.922418446474785</v>
       </c>
       <c r="E54">
-        <v>1.69584</v>
+        <v>1.73176</v>
       </c>
       <c r="F54">
-        <v>1.86784</v>
+        <v>1.90376</v>
       </c>
       <c r="G54">
         <v>0.444</v>
@@ -6090,28 +6090,28 @@
         <v>0.277</v>
       </c>
       <c r="M54">
-        <v>0.1681056</v>
+        <v>0.1713384</v>
       </c>
       <c r="N54">
-        <v>0.1088944</v>
+        <v>0.1056616</v>
       </c>
       <c r="O54">
-        <v>0.017423104</v>
+        <v>0.016905856</v>
       </c>
       <c r="P54">
-        <v>0.09147129600000001</v>
+        <v>0.08875574400000003</v>
       </c>
       <c r="Q54">
-        <v>0.232471296</v>
+        <v>0.229755744</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.153152304738662</v>
+        <v>0.1552450588134382</v>
       </c>
       <c r="T54">
-        <v>1.477744882670102</v>
+        <v>1.506552430232458</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.647773780290484</v>
+        <v>1.616683708964249</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6136,22 +6136,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1130331776423159</v>
+        <v>0.1132412490100742</v>
       </c>
       <c r="C55">
-        <v>1.462658446474785</v>
+        <v>1.422575088988978</v>
       </c>
       <c r="D55">
-        <v>2.922418446474785</v>
+        <v>2.918255088988978</v>
       </c>
       <c r="E55">
-        <v>1.73176</v>
+        <v>1.76768</v>
       </c>
       <c r="F55">
-        <v>1.90376</v>
+        <v>1.93968</v>
       </c>
       <c r="G55">
         <v>0.444</v>
@@ -6172,28 +6172,28 @@
         <v>0.277</v>
       </c>
       <c r="M55">
-        <v>0.1713384</v>
+        <v>0.1745712</v>
       </c>
       <c r="N55">
-        <v>0.1056616</v>
+        <v>0.1024288</v>
       </c>
       <c r="O55">
-        <v>0.016905856</v>
+        <v>0.016388608</v>
       </c>
       <c r="P55">
-        <v>0.08875574400000003</v>
+        <v>0.08604019200000002</v>
       </c>
       <c r="Q55">
-        <v>0.229755744</v>
+        <v>0.227040192</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1552450588134382</v>
+        <v>0.1574288021958133</v>
       </c>
       <c r="T55">
-        <v>1.506552430232458</v>
+        <v>1.536612479862742</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.616683708964249</v>
+        <v>1.586745121761207</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6218,22 +6218,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1132412490100742</v>
+        <v>0.1134493203778323</v>
       </c>
       <c r="C56">
-        <v>1.422575088988978</v>
+        <v>1.382503577094181</v>
       </c>
       <c r="D56">
-        <v>2.918255088988978</v>
+        <v>2.914103577094182</v>
       </c>
       <c r="E56">
-        <v>1.76768</v>
+        <v>1.8036</v>
       </c>
       <c r="F56">
-        <v>1.93968</v>
+        <v>1.9756</v>
       </c>
       <c r="G56">
         <v>0.444</v>
@@ -6254,28 +6254,28 @@
         <v>0.277</v>
       </c>
       <c r="M56">
-        <v>0.1745712</v>
+        <v>0.177804</v>
       </c>
       <c r="N56">
-        <v>0.1024288</v>
+        <v>0.09919600000000001</v>
       </c>
       <c r="O56">
-        <v>0.016388608</v>
+        <v>0.01587136</v>
       </c>
       <c r="P56">
-        <v>0.08604019200000002</v>
+        <v>0.08332464000000001</v>
       </c>
       <c r="Q56">
-        <v>0.227040192</v>
+        <v>0.22432464</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1574288021958133</v>
+        <v>0.1597096008396274</v>
       </c>
       <c r="T56">
-        <v>1.536612479862742</v>
+        <v>1.568008531698817</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.586745121761207</v>
+        <v>1.557895210456458</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6300,22 +6300,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1134493203778323</v>
+        <v>0.1136573917455905</v>
       </c>
       <c r="C57">
-        <v>1.382503577094181</v>
+        <v>1.342443860307573</v>
       </c>
       <c r="D57">
-        <v>2.914103577094182</v>
+        <v>2.909963860307573</v>
       </c>
       <c r="E57">
-        <v>1.8036</v>
+        <v>1.83952</v>
       </c>
       <c r="F57">
-        <v>1.9756</v>
+        <v>2.01152</v>
       </c>
       <c r="G57">
         <v>0.444</v>
@@ -6336,28 +6336,28 @@
         <v>0.277</v>
       </c>
       <c r="M57">
-        <v>0.177804</v>
+        <v>0.1810368</v>
       </c>
       <c r="N57">
-        <v>0.09919600000000001</v>
+        <v>0.0959632</v>
       </c>
       <c r="O57">
-        <v>0.01587136</v>
+        <v>0.015354112</v>
       </c>
       <c r="P57">
-        <v>0.08332464000000001</v>
+        <v>0.080609088</v>
       </c>
       <c r="Q57">
-        <v>0.22432464</v>
+        <v>0.221609088</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1597096008396274</v>
+        <v>0.1620940721490694</v>
       </c>
       <c r="T57">
-        <v>1.568008531698817</v>
+        <v>1.600831676800168</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.557895210456458</v>
+        <v>1.530075653126878</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6382,22 +6382,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1136573917455905</v>
+        <v>0.1138654631133487</v>
       </c>
       <c r="C58">
-        <v>1.342443860307573</v>
+        <v>1.302395888432781</v>
       </c>
       <c r="D58">
-        <v>2.909963860307573</v>
+        <v>2.905835888432782</v>
       </c>
       <c r="E58">
-        <v>1.83952</v>
+        <v>1.87544</v>
       </c>
       <c r="F58">
-        <v>2.01152</v>
+        <v>2.04744</v>
       </c>
       <c r="G58">
         <v>0.444</v>
@@ -6418,28 +6418,28 @@
         <v>0.277</v>
       </c>
       <c r="M58">
-        <v>0.1810368</v>
+        <v>0.1842696</v>
       </c>
       <c r="N58">
-        <v>0.0959632</v>
+        <v>0.09273039999999999</v>
       </c>
       <c r="O58">
-        <v>0.015354112</v>
+        <v>0.014836864</v>
       </c>
       <c r="P58">
-        <v>0.080609088</v>
+        <v>0.07789353599999999</v>
       </c>
       <c r="Q58">
-        <v>0.221609088</v>
+        <v>0.218893536</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1620940721490694</v>
+        <v>0.1645894491008109</v>
       </c>
       <c r="T58">
-        <v>1.600831676800168</v>
+        <v>1.635181479813209</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.530075653126878</v>
+        <v>1.50323222061588</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6464,22 +6464,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1138654631133487</v>
+        <v>0.143522805424988</v>
       </c>
       <c r="C59">
-        <v>1.302395888432781</v>
+        <v>0.7777498946787365</v>
       </c>
       <c r="D59">
-        <v>2.905835888432782</v>
+        <v>2.417109894678737</v>
       </c>
       <c r="E59">
-        <v>1.87544</v>
+        <v>1.91136</v>
       </c>
       <c r="F59">
-        <v>2.04744</v>
+        <v>2.08336</v>
       </c>
       <c r="G59">
         <v>0.444</v>
@@ -6500,45 +6500,45 @@
         <v>0.277</v>
       </c>
       <c r="M59">
-        <v>0.1842696</v>
+        <v>0.3058372480000001</v>
       </c>
       <c r="N59">
-        <v>0.09273039999999999</v>
+        <v>-0.02883724800000004</v>
       </c>
       <c r="O59">
-        <v>0.014836864</v>
+        <v>-0.004613959680000006</v>
       </c>
       <c r="P59">
-        <v>0.07789353599999999</v>
+        <v>-0.02422328832000003</v>
       </c>
       <c r="Q59">
-        <v>0.218893536</v>
+        <v>0.11677671168</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1645894491008109</v>
+        <v>0.168374608313817</v>
       </c>
       <c r="T59">
-        <v>1.635181479813209</v>
+        <v>1.687285621133026</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.16</v>
+        <v>0.1449136764400914</v>
       </c>
       <c r="W59">
-        <v>0.0756</v>
+        <v>0.1255266722985946</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.50323222061588</v>
+        <v>0.9057104777505713</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6546,22 +6546,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.143522805424988</v>
+        <v>0.144532805424988</v>
       </c>
       <c r="C60">
-        <v>0.7777498946787369</v>
+        <v>0.7280641577703713</v>
       </c>
       <c r="D60">
-        <v>2.417109894678737</v>
+        <v>2.403344157770371</v>
       </c>
       <c r="E60">
-        <v>1.91136</v>
+        <v>1.94728</v>
       </c>
       <c r="F60">
-        <v>2.08336</v>
+        <v>2.11928</v>
       </c>
       <c r="G60">
         <v>0.444</v>
@@ -6582,37 +6582,37 @@
         <v>0.277</v>
       </c>
       <c r="M60">
-        <v>0.305837248</v>
+        <v>0.311110304</v>
       </c>
       <c r="N60">
-        <v>-0.02883724799999998</v>
+        <v>-0.03411030399999998</v>
       </c>
       <c r="O60">
-        <v>-0.004613959679999997</v>
+        <v>-0.005457648639999997</v>
       </c>
       <c r="P60">
-        <v>-0.02422328831999998</v>
+        <v>-0.02865265535999998</v>
       </c>
       <c r="Q60">
-        <v>0.11677671168</v>
+        <v>0.11234734464</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.168374608313817</v>
+        <v>0.1713642329068369</v>
       </c>
       <c r="T60">
-        <v>1.687285621133026</v>
+        <v>1.728438928965539</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1449136764400914</v>
+        <v>0.1424575124326323</v>
       </c>
       <c r="W60">
-        <v>0.1255266722985946</v>
+        <v>0.1258872371748896</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9057104777505716</v>
+        <v>0.8903594527039517</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6628,22 +6628,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.144532805424988</v>
+        <v>0.145542805424988</v>
       </c>
       <c r="C61">
-        <v>0.7280641577703713</v>
+        <v>0.6785343280669389</v>
       </c>
       <c r="D61">
-        <v>2.403344157770371</v>
+        <v>2.389734328066939</v>
       </c>
       <c r="E61">
-        <v>1.94728</v>
+        <v>1.9832</v>
       </c>
       <c r="F61">
-        <v>2.11928</v>
+        <v>2.1552</v>
       </c>
       <c r="G61">
         <v>0.444</v>
@@ -6664,37 +6664,37 @@
         <v>0.277</v>
       </c>
       <c r="M61">
-        <v>0.311110304</v>
+        <v>0.31638336</v>
       </c>
       <c r="N61">
-        <v>-0.03411030399999998</v>
+        <v>-0.03938335999999998</v>
       </c>
       <c r="O61">
-        <v>-0.005457648639999997</v>
+        <v>-0.006301337599999996</v>
       </c>
       <c r="P61">
-        <v>-0.02865265535999998</v>
+        <v>-0.03308202239999998</v>
       </c>
       <c r="Q61">
-        <v>0.11234734464</v>
+        <v>0.1079179776</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1713642329068369</v>
+        <v>0.1745033387295079</v>
       </c>
       <c r="T61">
-        <v>1.728438928965539</v>
+        <v>1.771649902189677</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1424575124326323</v>
+        <v>0.1400832205587551</v>
       </c>
       <c r="W61">
-        <v>0.1258872371748896</v>
+        <v>0.1262357832219748</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8903594527039517</v>
+        <v>0.8755201284922192</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6710,22 +6710,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.145542805424988</v>
+        <v>0.146552805424988</v>
       </c>
       <c r="C62">
-        <v>0.6785343280669389</v>
+        <v>0.6291577718354184</v>
       </c>
       <c r="D62">
-        <v>2.389734328066939</v>
+        <v>2.376277771835419</v>
       </c>
       <c r="E62">
-        <v>1.9832</v>
+        <v>2.01912</v>
       </c>
       <c r="F62">
-        <v>2.1552</v>
+        <v>2.19112</v>
       </c>
       <c r="G62">
         <v>0.444</v>
@@ -6746,37 +6746,37 @@
         <v>0.277</v>
       </c>
       <c r="M62">
-        <v>0.31638336</v>
+        <v>0.3216564160000001</v>
       </c>
       <c r="N62">
-        <v>-0.03938335999999998</v>
+        <v>-0.04465641600000003</v>
       </c>
       <c r="O62">
-        <v>-0.006301337599999996</v>
+        <v>-0.007145026560000005</v>
       </c>
       <c r="P62">
-        <v>-0.03308202239999998</v>
+        <v>-0.03751138944000003</v>
       </c>
       <c r="Q62">
-        <v>0.1079179776</v>
+        <v>0.10348861056</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1745033387295079</v>
+        <v>0.1778034243379568</v>
       </c>
       <c r="T62">
-        <v>1.771649902189677</v>
+        <v>1.817076822758644</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1400832205587551</v>
+        <v>0.1377867743200869</v>
       </c>
       <c r="W62">
-        <v>0.1262357832219748</v>
+        <v>0.1265729015298113</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8755201284922192</v>
+        <v>0.8611673395005432</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6792,22 +6792,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.146552805424988</v>
+        <v>0.147562805424988</v>
       </c>
       <c r="C63">
-        <v>0.6291577718354184</v>
+        <v>0.5799319143326551</v>
       </c>
       <c r="D63">
-        <v>2.376277771835419</v>
+        <v>2.362971914332655</v>
       </c>
       <c r="E63">
-        <v>2.01912</v>
+        <v>2.05504</v>
       </c>
       <c r="F63">
-        <v>2.19112</v>
+        <v>2.22704</v>
       </c>
       <c r="G63">
         <v>0.444</v>
@@ -6828,37 +6828,37 @@
         <v>0.277</v>
       </c>
       <c r="M63">
-        <v>0.3216564160000001</v>
+        <v>0.3269294720000001</v>
       </c>
       <c r="N63">
-        <v>-0.04465641600000003</v>
+        <v>-0.04992947200000003</v>
       </c>
       <c r="O63">
-        <v>-0.007145026560000005</v>
+        <v>-0.007988715520000005</v>
       </c>
       <c r="P63">
-        <v>-0.03751138944000003</v>
+        <v>-0.04194075648000002</v>
       </c>
       <c r="Q63">
-        <v>0.10348861056</v>
+        <v>0.09905924351999996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1778034243379568</v>
+        <v>0.1812771986626399</v>
       </c>
       <c r="T63">
-        <v>1.817076822758644</v>
+        <v>1.864894633883871</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1377867743200869</v>
+        <v>0.1355644069923436</v>
       </c>
       <c r="W63">
-        <v>0.1265729015298113</v>
+        <v>0.126899145053524</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8611673395005432</v>
+        <v>0.8472775437021474</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6874,22 +6874,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.147562805424988</v>
+        <v>0.148572805424988</v>
       </c>
       <c r="C64">
-        <v>0.5799319143326551</v>
+        <v>0.5308542381629997</v>
       </c>
       <c r="D64">
-        <v>2.362971914332655</v>
+        <v>2.349814238163</v>
       </c>
       <c r="E64">
-        <v>2.05504</v>
+        <v>2.09096</v>
       </c>
       <c r="F64">
-        <v>2.22704</v>
+        <v>2.26296</v>
       </c>
       <c r="G64">
         <v>0.444</v>
@@ -6910,37 +6910,37 @@
         <v>0.277</v>
       </c>
       <c r="M64">
-        <v>0.3269294720000001</v>
+        <v>0.3322025280000001</v>
       </c>
       <c r="N64">
-        <v>-0.04992947200000003</v>
+        <v>-0.05520252800000003</v>
       </c>
       <c r="O64">
-        <v>-0.007988715520000005</v>
+        <v>-0.008832404480000005</v>
       </c>
       <c r="P64">
-        <v>-0.04194075648000002</v>
+        <v>-0.04637012352000002</v>
       </c>
       <c r="Q64">
-        <v>0.09905924351999996</v>
+        <v>0.09462987647999996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1812771986626399</v>
+        <v>0.1849387445724409</v>
       </c>
       <c r="T64">
-        <v>1.864894633883871</v>
+        <v>1.915297191556408</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1355644069923436</v>
+        <v>0.1334125910083381</v>
       </c>
       <c r="W64">
-        <v>0.126899145053524</v>
+        <v>0.127215031639976</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8472775437021474</v>
+        <v>0.8338286938021133</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6956,22 +6956,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.148572805424988</v>
+        <v>0.149582805424988</v>
       </c>
       <c r="C65">
-        <v>0.5308542381629997</v>
+        <v>0.4819222816905171</v>
       </c>
       <c r="D65">
-        <v>2.349814238163</v>
+        <v>2.336802281690517</v>
       </c>
       <c r="E65">
-        <v>2.09096</v>
+        <v>2.12688</v>
       </c>
       <c r="F65">
-        <v>2.26296</v>
+        <v>2.29888</v>
       </c>
       <c r="G65">
         <v>0.444</v>
@@ -6992,37 +6992,37 @@
         <v>0.277</v>
       </c>
       <c r="M65">
-        <v>0.3322025280000001</v>
+        <v>0.3374755840000001</v>
       </c>
       <c r="N65">
-        <v>-0.05520252800000003</v>
+        <v>-0.06047558400000003</v>
       </c>
       <c r="O65">
-        <v>-0.008832404480000005</v>
+        <v>-0.009676093440000004</v>
       </c>
       <c r="P65">
-        <v>-0.04637012352000002</v>
+        <v>-0.05079949056000002</v>
       </c>
       <c r="Q65">
-        <v>0.09462987647999996</v>
+        <v>0.09020050943999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1849387445724409</v>
+        <v>0.1888037096994532</v>
       </c>
       <c r="T65">
-        <v>1.915297191556408</v>
+        <v>1.968499891321864</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1334125910083381</v>
+        <v>0.1313280192738329</v>
       </c>
       <c r="W65">
-        <v>0.127215031639976</v>
+        <v>0.1275210467706014</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8338286938021133</v>
+        <v>0.8208001204614553</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7038,22 +7038,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.149582805424988</v>
+        <v>0.150592805424988</v>
       </c>
       <c r="C66">
-        <v>0.4819222816905171</v>
+        <v>0.4331336375036572</v>
       </c>
       <c r="D66">
-        <v>2.336802281690517</v>
+        <v>2.323933637503657</v>
       </c>
       <c r="E66">
-        <v>2.12688</v>
+        <v>2.1628</v>
       </c>
       <c r="F66">
-        <v>2.29888</v>
+        <v>2.3348</v>
       </c>
       <c r="G66">
         <v>0.444</v>
@@ -7074,37 +7074,37 @@
         <v>0.277</v>
       </c>
       <c r="M66">
-        <v>0.3374755840000001</v>
+        <v>0.34274864</v>
       </c>
       <c r="N66">
-        <v>-0.06047558400000003</v>
+        <v>-0.06574864000000002</v>
       </c>
       <c r="O66">
-        <v>-0.009676093440000004</v>
+        <v>-0.0105197824</v>
       </c>
       <c r="P66">
-        <v>-0.05079949056000002</v>
+        <v>-0.05522885760000002</v>
       </c>
       <c r="Q66">
-        <v>0.09020050943999997</v>
+        <v>0.08577114239999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1888037096994532</v>
+        <v>0.1928895299765805</v>
       </c>
       <c r="T66">
-        <v>1.968499891321864</v>
+        <v>2.024742745359632</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1313280192738329</v>
+        <v>0.1293075882080816</v>
       </c>
       <c r="W66">
-        <v>0.1275210467706014</v>
+        <v>0.1278176460510536</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8208001204614553</v>
+        <v>0.8081724263005099</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7120,22 +7120,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.150592805424988</v>
+        <v>0.1885132198752059</v>
       </c>
       <c r="C67">
-        <v>0.4331336375036572</v>
+        <v>-0.0009540630656426075</v>
       </c>
       <c r="D67">
-        <v>2.323933637503657</v>
+        <v>1.925765936934358</v>
       </c>
       <c r="E67">
-        <v>2.1628</v>
+        <v>2.19872</v>
       </c>
       <c r="F67">
-        <v>2.3348</v>
+        <v>2.37072</v>
       </c>
       <c r="G67">
         <v>0.444</v>
@@ -7156,45 +7156,45 @@
         <v>0.277</v>
       </c>
       <c r="M67">
-        <v>0.34274864</v>
+        <v>0.4760405760000001</v>
       </c>
       <c r="N67">
-        <v>-0.06574864000000002</v>
+        <v>-0.1990405760000001</v>
       </c>
       <c r="O67">
-        <v>-0.0105197824</v>
+        <v>-0.03184649216000001</v>
       </c>
       <c r="P67">
-        <v>-0.05522885760000002</v>
+        <v>-0.1671940838400001</v>
       </c>
       <c r="Q67">
-        <v>0.08577114239999997</v>
+        <v>-0.02619408384000008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1928895299765805</v>
+        <v>0.2009522057118266</v>
       </c>
       <c r="T67">
-        <v>2.024742745359632</v>
+        <v>2.135728511686617</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1293075882080816</v>
+        <v>0.09310130739779628</v>
       </c>
       <c r="W67">
-        <v>0.1278176460510536</v>
+        <v>0.1821052574745225</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8081724263005099</v>
+        <v>0.5818831712362267</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7202,22 +7202,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1885132198752059</v>
+        <v>0.1900632198752059</v>
       </c>
       <c r="C68">
-        <v>-0.0009540630656426075</v>
+        <v>-0.0502669297934033</v>
       </c>
       <c r="D68">
-        <v>1.925765936934358</v>
+        <v>1.912373070206597</v>
       </c>
       <c r="E68">
-        <v>2.19872</v>
+        <v>2.23464</v>
       </c>
       <c r="F68">
-        <v>2.37072</v>
+        <v>2.40664</v>
       </c>
       <c r="G68">
         <v>0.444</v>
@@ -7238,37 +7238,37 @@
         <v>0.277</v>
       </c>
       <c r="M68">
-        <v>0.4760405760000001</v>
+        <v>0.4832533120000001</v>
       </c>
       <c r="N68">
-        <v>-0.1990405760000001</v>
+        <v>-0.2062533120000001</v>
       </c>
       <c r="O68">
-        <v>-0.03184649216000001</v>
+        <v>-0.03300052992000001</v>
       </c>
       <c r="P68">
-        <v>-0.1671940838400001</v>
+        <v>-0.1732527820800001</v>
       </c>
       <c r="Q68">
-        <v>-0.02619408384000008</v>
+        <v>-0.03225278208000007</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2009522057118266</v>
+        <v>0.2056537877030941</v>
       </c>
       <c r="T68">
-        <v>2.135728511686617</v>
+        <v>2.200447557495302</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09310130739779628</v>
+        <v>0.09171173564559036</v>
       </c>
       <c r="W68">
-        <v>0.1821052574745225</v>
+        <v>0.1823842834823655</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5818831712362267</v>
+        <v>0.5731983477849396</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7284,22 +7284,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1900632198752059</v>
+        <v>0.1916132198752059</v>
       </c>
       <c r="C69">
-        <v>-0.0502669297934033</v>
+        <v>-0.09939479993517075</v>
       </c>
       <c r="D69">
-        <v>1.912373070206597</v>
+        <v>1.899165200064829</v>
       </c>
       <c r="E69">
-        <v>2.23464</v>
+        <v>2.27056</v>
       </c>
       <c r="F69">
-        <v>2.40664</v>
+        <v>2.44256</v>
       </c>
       <c r="G69">
         <v>0.444</v>
@@ -7320,37 +7320,37 @@
         <v>0.277</v>
       </c>
       <c r="M69">
-        <v>0.4832533120000001</v>
+        <v>0.4904660480000001</v>
       </c>
       <c r="N69">
-        <v>-0.2062533120000001</v>
+        <v>-0.2134660480000001</v>
       </c>
       <c r="O69">
-        <v>-0.03300052992000001</v>
+        <v>-0.03415456768000001</v>
       </c>
       <c r="P69">
-        <v>-0.1732527820800001</v>
+        <v>-0.17931148032</v>
       </c>
       <c r="Q69">
-        <v>-0.03225278208000007</v>
+        <v>-0.03831148032000006</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2056537877030941</v>
+        <v>0.2106492185688158</v>
       </c>
       <c r="T69">
-        <v>2.200447557495302</v>
+        <v>2.26921154366703</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.09171173564559036</v>
+        <v>0.09036303365080225</v>
       </c>
       <c r="W69">
-        <v>0.1823842834823655</v>
+        <v>0.1826551028429189</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5731983477849396</v>
+        <v>0.5647689603175141</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7366,22 +7366,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1916132198752059</v>
+        <v>0.193163219875206</v>
       </c>
       <c r="C70">
-        <v>-0.09939479993517075</v>
+        <v>-0.1483414802551803</v>
       </c>
       <c r="D70">
-        <v>1.899165200064829</v>
+        <v>1.88613851974482</v>
       </c>
       <c r="E70">
-        <v>2.27056</v>
+        <v>2.30648</v>
       </c>
       <c r="F70">
-        <v>2.44256</v>
+        <v>2.47848</v>
       </c>
       <c r="G70">
         <v>0.444</v>
@@ -7402,37 +7402,37 @@
         <v>0.277</v>
       </c>
       <c r="M70">
-        <v>0.4904660480000001</v>
+        <v>0.497678784</v>
       </c>
       <c r="N70">
-        <v>-0.2134660480000001</v>
+        <v>-0.220678784</v>
       </c>
       <c r="O70">
-        <v>-0.03415456768000001</v>
+        <v>-0.03530860544</v>
       </c>
       <c r="P70">
-        <v>-0.17931148032</v>
+        <v>-0.18537017856</v>
       </c>
       <c r="Q70">
-        <v>-0.03831148032000006</v>
+        <v>-0.04437017856000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2106492185688158</v>
+        <v>0.2159669352968422</v>
       </c>
       <c r="T70">
-        <v>2.26921154366703</v>
+        <v>2.342411916043387</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.09036303365080225</v>
+        <v>0.08905342446745731</v>
       </c>
       <c r="W70">
-        <v>0.1826551028429189</v>
+        <v>0.1829180723669346</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5647689603175141</v>
+        <v>0.5565839029216082</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7448,22 +7448,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.193163219875206</v>
+        <v>0.1947132198752059</v>
       </c>
       <c r="C71">
-        <v>-0.1483414802551803</v>
+        <v>-0.1971106737843495</v>
       </c>
       <c r="D71">
-        <v>1.88613851974482</v>
+        <v>1.87328932621565</v>
       </c>
       <c r="E71">
-        <v>2.30648</v>
+        <v>2.3424</v>
       </c>
       <c r="F71">
-        <v>2.47848</v>
+        <v>2.5144</v>
       </c>
       <c r="G71">
         <v>0.444</v>
@@ -7484,37 +7484,37 @@
         <v>0.277</v>
       </c>
       <c r="M71">
-        <v>0.497678784</v>
+        <v>0.50489152</v>
       </c>
       <c r="N71">
-        <v>-0.220678784</v>
+        <v>-0.22789152</v>
       </c>
       <c r="O71">
-        <v>-0.03530860544</v>
+        <v>-0.03646264320000001</v>
       </c>
       <c r="P71">
-        <v>-0.18537017856</v>
+        <v>-0.1914288768</v>
       </c>
       <c r="Q71">
-        <v>-0.04437017856000003</v>
+        <v>-0.05042887680000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2159669352968422</v>
+        <v>0.2216391664734035</v>
       </c>
       <c r="T71">
-        <v>2.342411916043387</v>
+        <v>2.420492313244833</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08905342446745731</v>
+        <v>0.08778123268935077</v>
       </c>
       <c r="W71">
-        <v>0.1829180723669346</v>
+        <v>0.1831735284759784</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5565839029216082</v>
+        <v>0.5486327043084424</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7530,22 +7530,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1947132198752059</v>
+        <v>0.196263219875206</v>
       </c>
       <c r="C72">
-        <v>-0.1971106737843495</v>
+        <v>-0.2457059833297568</v>
       </c>
       <c r="D72">
-        <v>1.87328932621565</v>
+        <v>1.860614016670243</v>
       </c>
       <c r="E72">
-        <v>2.3424</v>
+        <v>2.37832</v>
       </c>
       <c r="F72">
-        <v>2.5144</v>
+        <v>2.55032</v>
       </c>
       <c r="G72">
         <v>0.444</v>
@@ -7566,37 +7566,37 @@
         <v>0.277</v>
       </c>
       <c r="M72">
-        <v>0.50489152</v>
+        <v>0.5121042560000001</v>
       </c>
       <c r="N72">
-        <v>-0.22789152</v>
+        <v>-0.2351042560000001</v>
       </c>
       <c r="O72">
-        <v>-0.03646264320000001</v>
+        <v>-0.03761668096000001</v>
       </c>
       <c r="P72">
-        <v>-0.1914288768</v>
+        <v>-0.1974875750400001</v>
       </c>
       <c r="Q72">
-        <v>-0.05042887680000002</v>
+        <v>-0.05648757504000007</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2216391664734035</v>
+        <v>0.2277025860069692</v>
       </c>
       <c r="T72">
-        <v>2.420492313244833</v>
+        <v>2.50395756542569</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08778123268935077</v>
+        <v>0.0865448772993599</v>
       </c>
       <c r="W72">
-        <v>0.1831735284759784</v>
+        <v>0.1834217886382885</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5486327043084424</v>
+        <v>0.5409054831209994</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7612,22 +7612,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1962632198752059</v>
+        <v>0.1978132198752059</v>
       </c>
       <c r="C73">
-        <v>-0.2457059833297564</v>
+        <v>-0.2941309148425897</v>
       </c>
       <c r="D73">
-        <v>1.860614016670244</v>
+        <v>1.84810908515741</v>
       </c>
       <c r="E73">
-        <v>2.37832</v>
+        <v>2.41424</v>
       </c>
       <c r="F73">
-        <v>2.55032</v>
+        <v>2.58624</v>
       </c>
       <c r="G73">
         <v>0.444</v>
@@ -7648,37 +7648,37 @@
         <v>0.277</v>
       </c>
       <c r="M73">
-        <v>0.5121042560000001</v>
+        <v>0.519316992</v>
       </c>
       <c r="N73">
-        <v>-0.2351042560000001</v>
+        <v>-0.242316992</v>
       </c>
       <c r="O73">
-        <v>-0.03761668096000001</v>
+        <v>-0.03877071872</v>
       </c>
       <c r="P73">
-        <v>-0.1974875750400001</v>
+        <v>-0.20354627328</v>
       </c>
       <c r="Q73">
-        <v>-0.05648757504000007</v>
+        <v>-0.06254627328000004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2277025860069692</v>
+        <v>0.2341991069357895</v>
       </c>
       <c r="T73">
-        <v>2.503957565425689</v>
+        <v>2.593384621333749</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0865448772993599</v>
+        <v>0.08534286511464659</v>
       </c>
       <c r="W73">
-        <v>0.1834217886382885</v>
+        <v>0.183663152684979</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5409054831209994</v>
+        <v>0.5333929069665412</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7694,22 +7694,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1978132198752059</v>
+        <v>0.1993632198752059</v>
       </c>
       <c r="C74">
-        <v>-0.2941309148425897</v>
+        <v>-0.3423888806511979</v>
       </c>
       <c r="D74">
-        <v>1.84810908515741</v>
+        <v>1.835771119348802</v>
       </c>
       <c r="E74">
-        <v>2.41424</v>
+        <v>2.45016</v>
       </c>
       <c r="F74">
-        <v>2.58624</v>
+        <v>2.62216</v>
       </c>
       <c r="G74">
         <v>0.444</v>
@@ -7730,37 +7730,37 @@
         <v>0.277</v>
       </c>
       <c r="M74">
-        <v>0.519316992</v>
+        <v>0.526529728</v>
       </c>
       <c r="N74">
-        <v>-0.242316992</v>
+        <v>-0.249529728</v>
       </c>
       <c r="O74">
-        <v>-0.03877071872</v>
+        <v>-0.03992475647999999</v>
       </c>
       <c r="P74">
-        <v>-0.20354627328</v>
+        <v>-0.20960497152</v>
       </c>
       <c r="Q74">
-        <v>-0.06254627328000004</v>
+        <v>-0.06860497151999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2341991069357895</v>
+        <v>0.241176851637115</v>
       </c>
       <c r="T74">
-        <v>2.593384621333749</v>
+        <v>2.689435903605369</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08534286511464659</v>
+        <v>0.08417378477061034</v>
       </c>
       <c r="W74">
-        <v>0.183663152684979</v>
+        <v>0.1838979040180614</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5333929069665412</v>
+        <v>0.5260861548163147</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7776,22 +7776,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1993632198752059</v>
+        <v>0.2009132198752059</v>
       </c>
       <c r="C75">
-        <v>-0.3423888806511979</v>
+        <v>-0.3904832025654899</v>
       </c>
       <c r="D75">
-        <v>1.835771119348802</v>
+        <v>1.82359679743451</v>
       </c>
       <c r="E75">
-        <v>2.45016</v>
+        <v>2.48608</v>
       </c>
       <c r="F75">
-        <v>2.62216</v>
+        <v>2.65808</v>
       </c>
       <c r="G75">
         <v>0.444</v>
@@ -7812,37 +7812,37 @@
         <v>0.277</v>
       </c>
       <c r="M75">
-        <v>0.526529728</v>
+        <v>0.533742464</v>
       </c>
       <c r="N75">
-        <v>-0.249529728</v>
+        <v>-0.256742464</v>
       </c>
       <c r="O75">
-        <v>-0.03992475647999999</v>
+        <v>-0.04107879424</v>
       </c>
       <c r="P75">
-        <v>-0.20960497152</v>
+        <v>-0.21566366976</v>
       </c>
       <c r="Q75">
-        <v>-0.06860497151999997</v>
+        <v>-0.07466366976000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.241176851637115</v>
+        <v>0.2486913459308502</v>
       </c>
       <c r="T75">
-        <v>2.689435903605369</v>
+        <v>2.792875746051729</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08417378477061034</v>
+        <v>0.08303630119262911</v>
       </c>
       <c r="W75">
-        <v>0.1838979040180614</v>
+        <v>0.1841263107205201</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5260861548163147</v>
+        <v>0.518976882453932</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7858,22 +7858,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2009132198752059</v>
+        <v>0.2024632198752059</v>
       </c>
       <c r="C76">
-        <v>-0.3904832025654899</v>
+        <v>-0.4384171148586287</v>
       </c>
       <c r="D76">
-        <v>1.82359679743451</v>
+        <v>1.811582885141371</v>
       </c>
       <c r="E76">
-        <v>2.48608</v>
+        <v>2.522</v>
       </c>
       <c r="F76">
-        <v>2.65808</v>
+        <v>2.694</v>
       </c>
       <c r="G76">
         <v>0.444</v>
@@ -7894,37 +7894,37 @@
         <v>0.277</v>
       </c>
       <c r="M76">
-        <v>0.533742464</v>
+        <v>0.5409552</v>
       </c>
       <c r="N76">
-        <v>-0.256742464</v>
+        <v>-0.2639551999999999</v>
       </c>
       <c r="O76">
-        <v>-0.04107879424</v>
+        <v>-0.04223283199999999</v>
       </c>
       <c r="P76">
-        <v>-0.21566366976</v>
+        <v>-0.2217223679999999</v>
       </c>
       <c r="Q76">
-        <v>-0.07466366976000002</v>
+        <v>-0.08072236799999996</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2486913459308502</v>
+        <v>0.2568069997680842</v>
       </c>
       <c r="T76">
-        <v>2.792875746051729</v>
+        <v>2.904590775893799</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08303630119262911</v>
+        <v>0.08192915051006074</v>
       </c>
       <c r="W76">
-        <v>0.1841263107205201</v>
+        <v>0.1843486265775798</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.518976882453932</v>
+        <v>0.5120571906878796</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7940,22 +7940,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2024632198752059</v>
+        <v>0.2040132198752059</v>
       </c>
       <c r="C77">
-        <v>-0.4384171148586287</v>
+        <v>-0.4861937671316308</v>
       </c>
       <c r="D77">
-        <v>1.811582885141371</v>
+        <v>1.799726232868369</v>
       </c>
       <c r="E77">
-        <v>2.522</v>
+        <v>2.55792</v>
       </c>
       <c r="F77">
-        <v>2.694</v>
+        <v>2.72992</v>
       </c>
       <c r="G77">
         <v>0.444</v>
@@ -7976,37 +7976,37 @@
         <v>0.277</v>
       </c>
       <c r="M77">
-        <v>0.5409552</v>
+        <v>0.548167936</v>
       </c>
       <c r="N77">
-        <v>-0.2639551999999999</v>
+        <v>-0.271167936</v>
       </c>
       <c r="O77">
-        <v>-0.04223283199999999</v>
+        <v>-0.04338686976</v>
       </c>
       <c r="P77">
-        <v>-0.2217223679999999</v>
+        <v>-0.22778106624</v>
       </c>
       <c r="Q77">
-        <v>-0.08072236799999996</v>
+        <v>-0.08678106624000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2568069997680842</v>
+        <v>0.2655989580917544</v>
       </c>
       <c r="T77">
-        <v>2.904590775893799</v>
+        <v>3.025615391556041</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08192915051006074</v>
+        <v>0.08085113537177045</v>
       </c>
       <c r="W77">
-        <v>0.1843486265775798</v>
+        <v>0.1845650920173485</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5120571906878796</v>
+        <v>0.5053195960735654</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8022,22 +8022,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2040132198752059</v>
+        <v>0.2330258474507737</v>
       </c>
       <c r="C78">
-        <v>-0.4861937671316308</v>
+        <v>-0.7185297434274029</v>
       </c>
       <c r="D78">
-        <v>1.799726232868369</v>
+        <v>1.603310256572597</v>
       </c>
       <c r="E78">
-        <v>2.55792</v>
+        <v>2.59384</v>
       </c>
       <c r="F78">
-        <v>2.72992</v>
+        <v>2.76584</v>
       </c>
       <c r="G78">
         <v>0.444</v>
@@ -8058,45 +8058,45 @@
         <v>0.277</v>
       </c>
       <c r="M78">
-        <v>0.548167936</v>
+        <v>0.6521850720000001</v>
       </c>
       <c r="N78">
-        <v>-0.271167936</v>
+        <v>-0.3751850720000001</v>
       </c>
       <c r="O78">
-        <v>-0.04338686976</v>
+        <v>-0.06002961152000001</v>
       </c>
       <c r="P78">
-        <v>-0.22778106624</v>
+        <v>-0.31515546048</v>
       </c>
       <c r="Q78">
-        <v>-0.08678106624000001</v>
+        <v>-0.1741554604800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2655989580917544</v>
+        <v>0.2773842500764732</v>
       </c>
       <c r="T78">
-        <v>3.025615391556041</v>
+        <v>3.187844371768321</v>
       </c>
       <c r="U78">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08085113537177045</v>
+        <v>0.0679561705760723</v>
       </c>
       <c r="W78">
-        <v>0.1845650920173485</v>
+        <v>0.2197759349781622</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5053195960735654</v>
+        <v>0.4247260661004519</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8104,22 +8104,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2330258474507737</v>
+        <v>0.2349258474507737</v>
       </c>
       <c r="C79">
-        <v>-0.7185297434274029</v>
+        <v>-0.7658276277772291</v>
       </c>
       <c r="D79">
-        <v>1.603310256572597</v>
+        <v>1.591932372222771</v>
       </c>
       <c r="E79">
-        <v>2.59384</v>
+        <v>2.62976</v>
       </c>
       <c r="F79">
-        <v>2.76584</v>
+        <v>2.80176</v>
       </c>
       <c r="G79">
         <v>0.444</v>
@@ -8140,37 +8140,37 @@
         <v>0.277</v>
       </c>
       <c r="M79">
-        <v>0.6521850720000001</v>
+        <v>0.6606550080000001</v>
       </c>
       <c r="N79">
-        <v>-0.3751850720000001</v>
+        <v>-0.3836550080000001</v>
       </c>
       <c r="O79">
-        <v>-0.06002961152000001</v>
+        <v>-0.06138480128000001</v>
       </c>
       <c r="P79">
-        <v>-0.31515546048</v>
+        <v>-0.3222702067200001</v>
       </c>
       <c r="Q79">
-        <v>-0.1741554604800001</v>
+        <v>-0.1812702067200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2773842500764732</v>
+        <v>0.287910806898131</v>
       </c>
       <c r="T79">
-        <v>3.187844371768321</v>
+        <v>3.332746388666881</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0679561705760723</v>
+        <v>0.06708493761996881</v>
       </c>
       <c r="W79">
-        <v>0.2197759349781622</v>
+        <v>0.2199813717092114</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4247260661004519</v>
+        <v>0.419280860124805</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8186,22 +8186,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2349258474507737</v>
+        <v>0.2368258474507737</v>
       </c>
       <c r="C80">
-        <v>-0.7658276277772291</v>
+        <v>-0.8129651638232591</v>
       </c>
       <c r="D80">
-        <v>1.591932372222771</v>
+        <v>1.580714836176741</v>
       </c>
       <c r="E80">
-        <v>2.62976</v>
+        <v>2.66568</v>
       </c>
       <c r="F80">
-        <v>2.80176</v>
+        <v>2.83768</v>
       </c>
       <c r="G80">
         <v>0.444</v>
@@ -8222,37 +8222,37 @@
         <v>0.277</v>
       </c>
       <c r="M80">
-        <v>0.6606550080000001</v>
+        <v>0.6691249440000001</v>
       </c>
       <c r="N80">
-        <v>-0.3836550080000001</v>
+        <v>-0.3921249440000001</v>
       </c>
       <c r="O80">
-        <v>-0.06138480128000001</v>
+        <v>-0.06273999104000001</v>
       </c>
       <c r="P80">
-        <v>-0.3222702067200001</v>
+        <v>-0.3293849529600001</v>
       </c>
       <c r="Q80">
-        <v>-0.1812702067200001</v>
+        <v>-0.1883849529600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.287910806898131</v>
+        <v>0.2994398929408992</v>
       </c>
       <c r="T80">
-        <v>3.332746388666881</v>
+        <v>3.491448597651019</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06708493761996881</v>
+        <v>0.06623576119439958</v>
       </c>
       <c r="W80">
-        <v>0.2199813717092114</v>
+        <v>0.2201816075103606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.419280860124805</v>
+        <v>0.4139735074649974</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8268,22 +8268,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2368258474507737</v>
+        <v>0.2387258474507737</v>
       </c>
       <c r="C81">
-        <v>-0.8129651638232591</v>
+        <v>-0.8599457175255987</v>
       </c>
       <c r="D81">
-        <v>1.580714836176741</v>
+        <v>1.569654282474402</v>
       </c>
       <c r="E81">
-        <v>2.66568</v>
+        <v>2.7016</v>
       </c>
       <c r="F81">
-        <v>2.83768</v>
+        <v>2.8736</v>
       </c>
       <c r="G81">
         <v>0.444</v>
@@ -8304,37 +8304,37 @@
         <v>0.277</v>
       </c>
       <c r="M81">
-        <v>0.6691249440000001</v>
+        <v>0.67759488</v>
       </c>
       <c r="N81">
-        <v>-0.3921249440000001</v>
+        <v>-0.40059488</v>
       </c>
       <c r="O81">
-        <v>-0.06273999104000001</v>
+        <v>-0.0640951808</v>
       </c>
       <c r="P81">
-        <v>-0.3293849529600001</v>
+        <v>-0.3364996992</v>
       </c>
       <c r="Q81">
-        <v>-0.1883849529600001</v>
+        <v>-0.1954996992</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2994398929408992</v>
+        <v>0.3121218875879442</v>
       </c>
       <c r="T81">
-        <v>3.491448597651019</v>
+        <v>3.66602102753357</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06623576119439958</v>
+        <v>0.0654078141794696</v>
       </c>
       <c r="W81">
-        <v>0.2201816075103606</v>
+        <v>0.2203768374164811</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4139735074649974</v>
+        <v>0.408798838621685</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8350,22 +8350,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2387258474507737</v>
+        <v>0.2406258474507737</v>
       </c>
       <c r="C82">
-        <v>-0.8599457175255987</v>
+        <v>-0.9067725612899902</v>
       </c>
       <c r="D82">
-        <v>1.569654282474402</v>
+        <v>1.55874743871001</v>
       </c>
       <c r="E82">
-        <v>2.7016</v>
+        <v>2.73752</v>
       </c>
       <c r="F82">
-        <v>2.8736</v>
+        <v>2.90952</v>
       </c>
       <c r="G82">
         <v>0.444</v>
@@ -8386,37 +8386,37 @@
         <v>0.277</v>
       </c>
       <c r="M82">
-        <v>0.67759488</v>
+        <v>0.686064816</v>
       </c>
       <c r="N82">
-        <v>-0.40059488</v>
+        <v>-0.409064816</v>
       </c>
       <c r="O82">
-        <v>-0.0640951808</v>
+        <v>-0.06545037056</v>
       </c>
       <c r="P82">
-        <v>-0.3364996992</v>
+        <v>-0.34361444544</v>
       </c>
       <c r="Q82">
-        <v>-0.1954996992</v>
+        <v>-0.20261444544</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3121218875879442</v>
+        <v>0.3261388290399412</v>
       </c>
       <c r="T82">
-        <v>3.66602102753357</v>
+        <v>3.858969502666916</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0654078141794696</v>
+        <v>0.06460031030071071</v>
       </c>
       <c r="W82">
-        <v>0.2203768374164811</v>
+        <v>0.2205672468310924</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.408798838621685</v>
+        <v>0.403751939379442</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8432,22 +8432,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2406258474507737</v>
+        <v>0.2425258474507737</v>
       </c>
       <c r="C83">
-        <v>-0.9067725612899902</v>
+        <v>-0.9534488771957303</v>
       </c>
       <c r="D83">
-        <v>1.55874743871001</v>
+        <v>1.54799112280427</v>
       </c>
       <c r="E83">
-        <v>2.73752</v>
+        <v>2.77344</v>
       </c>
       <c r="F83">
-        <v>2.90952</v>
+        <v>2.945440000000001</v>
       </c>
       <c r="G83">
         <v>0.444</v>
@@ -8468,37 +8468,37 @@
         <v>0.277</v>
       </c>
       <c r="M83">
-        <v>0.686064816</v>
+        <v>0.6945347520000001</v>
       </c>
       <c r="N83">
-        <v>-0.409064816</v>
+        <v>-0.4175347520000001</v>
       </c>
       <c r="O83">
-        <v>-0.06545037056</v>
+        <v>-0.06680556032000003</v>
       </c>
       <c r="P83">
-        <v>-0.34361444544</v>
+        <v>-0.3507291916800001</v>
       </c>
       <c r="Q83">
-        <v>-0.20261444544</v>
+        <v>-0.2097291916800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3261388290399412</v>
+        <v>0.3417132084310491</v>
       </c>
       <c r="T83">
-        <v>3.858969502666916</v>
+        <v>4.073356697259523</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06460031030071071</v>
+        <v>0.06381250163850692</v>
       </c>
       <c r="W83">
-        <v>0.2205672468310924</v>
+        <v>0.2207530121136401</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.403751939379442</v>
+        <v>0.3988281352406682</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8514,22 +8514,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2425258474507737</v>
+        <v>0.2444258474507737</v>
       </c>
       <c r="C84">
-        <v>-0.9534488771957303</v>
+        <v>-0.9999777600908459</v>
       </c>
       <c r="D84">
-        <v>1.54799112280427</v>
+        <v>1.537382239909155</v>
       </c>
       <c r="E84">
-        <v>2.77344</v>
+        <v>2.80936</v>
       </c>
       <c r="F84">
-        <v>2.945440000000001</v>
+        <v>2.98136</v>
       </c>
       <c r="G84">
         <v>0.444</v>
@@ -8550,37 +8550,37 @@
         <v>0.277</v>
       </c>
       <c r="M84">
-        <v>0.6945347520000001</v>
+        <v>0.7030046880000002</v>
       </c>
       <c r="N84">
-        <v>-0.4175347520000001</v>
+        <v>-0.4260046880000001</v>
       </c>
       <c r="O84">
-        <v>-0.06680556032000003</v>
+        <v>-0.06816075008000003</v>
       </c>
       <c r="P84">
-        <v>-0.3507291916800001</v>
+        <v>-0.3578439379200001</v>
       </c>
       <c r="Q84">
-        <v>-0.2097291916800001</v>
+        <v>-0.2168439379200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3417132084310491</v>
+        <v>0.3591198677505226</v>
       </c>
       <c r="T84">
-        <v>4.073356697259523</v>
+        <v>4.312965914745377</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06381250163850692</v>
+        <v>0.06304367631756105</v>
       </c>
       <c r="W84">
-        <v>0.2207530121136401</v>
+        <v>0.2209343011243191</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3988281352406682</v>
+        <v>0.3940229769847565</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8596,22 +8596,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2444258474507737</v>
+        <v>0.2463258474507737</v>
       </c>
       <c r="C85">
-        <v>-0.9999777600908459</v>
+        <v>-1.046362220560874</v>
       </c>
       <c r="D85">
-        <v>1.537382239909155</v>
+        <v>1.526917779439126</v>
       </c>
       <c r="E85">
-        <v>2.80936</v>
+        <v>2.84528</v>
       </c>
       <c r="F85">
-        <v>2.98136</v>
+        <v>3.01728</v>
       </c>
       <c r="G85">
         <v>0.444</v>
@@ -8632,37 +8632,37 @@
         <v>0.277</v>
       </c>
       <c r="M85">
-        <v>0.7030046880000002</v>
+        <v>0.7114746240000002</v>
       </c>
       <c r="N85">
-        <v>-0.4260046880000001</v>
+        <v>-0.4344746240000001</v>
       </c>
       <c r="O85">
-        <v>-0.06816075008000003</v>
+        <v>-0.06951593984000003</v>
       </c>
       <c r="P85">
-        <v>-0.3578439379200001</v>
+        <v>-0.3649586841600001</v>
       </c>
       <c r="Q85">
-        <v>-0.2168439379200001</v>
+        <v>-0.2239586841600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3591198677505226</v>
+        <v>0.3787023594849304</v>
       </c>
       <c r="T85">
-        <v>4.312965914745377</v>
+        <v>4.582526284416964</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06304367631756105</v>
+        <v>0.06229315636139961</v>
       </c>
       <c r="W85">
-        <v>0.2209343011243191</v>
+        <v>0.221111273729982</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3940229769847565</v>
+        <v>0.3893322272587475</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8678,22 +8678,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2463258474507737</v>
+        <v>0.2482258474507737</v>
       </c>
       <c r="C86">
-        <v>-1.046362220560874</v>
+        <v>-1.092605187777208</v>
       </c>
       <c r="D86">
-        <v>1.526917779439126</v>
+        <v>1.516594812222792</v>
       </c>
       <c r="E86">
-        <v>2.84528</v>
+        <v>2.8812</v>
       </c>
       <c r="F86">
-        <v>3.01728</v>
+        <v>3.0532</v>
       </c>
       <c r="G86">
         <v>0.444</v>
@@ -8714,37 +8714,37 @@
         <v>0.277</v>
       </c>
       <c r="M86">
-        <v>0.7114746240000001</v>
+        <v>0.71994456</v>
       </c>
       <c r="N86">
-        <v>-0.434474624</v>
+        <v>-0.4429445599999999</v>
       </c>
       <c r="O86">
-        <v>-0.06951593984000001</v>
+        <v>-0.07087112959999999</v>
       </c>
       <c r="P86">
-        <v>-0.36495868416</v>
+        <v>-0.3720734304</v>
       </c>
       <c r="Q86">
-        <v>-0.22395868416</v>
+        <v>-0.2310734304</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3787023594849301</v>
+        <v>0.4008958501172588</v>
       </c>
       <c r="T86">
-        <v>4.582526284416961</v>
+        <v>4.888028036711425</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06229315636139962</v>
+        <v>0.06156029569832434</v>
       </c>
       <c r="W86">
-        <v>0.221111273729982</v>
+        <v>0.2212840822743351</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3893322272587476</v>
+        <v>0.3847518481145271</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8760,22 +8760,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2482258474507737</v>
+        <v>0.2501258474507737</v>
       </c>
       <c r="C87">
-        <v>-1.092605187777208</v>
+        <v>-1.13870951223068</v>
       </c>
       <c r="D87">
-        <v>1.516594812222792</v>
+        <v>1.50641048776932</v>
       </c>
       <c r="E87">
-        <v>2.8812</v>
+        <v>2.91712</v>
       </c>
       <c r="F87">
-        <v>3.0532</v>
+        <v>3.08912</v>
       </c>
       <c r="G87">
         <v>0.444</v>
@@ -8796,37 +8796,37 @@
         <v>0.277</v>
       </c>
       <c r="M87">
-        <v>0.71994456</v>
+        <v>0.728414496</v>
       </c>
       <c r="N87">
-        <v>-0.4429445599999999</v>
+        <v>-0.4514144959999999</v>
       </c>
       <c r="O87">
-        <v>-0.07087112959999999</v>
+        <v>-0.07222631936</v>
       </c>
       <c r="P87">
-        <v>-0.3720734304</v>
+        <v>-0.3791881766399999</v>
       </c>
       <c r="Q87">
-        <v>-0.2310734304</v>
+        <v>-0.2381881766399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4008958501172588</v>
+        <v>0.4262598394113487</v>
       </c>
       <c r="T87">
-        <v>4.888028036711425</v>
+        <v>5.237172896476527</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06156029569832434</v>
+        <v>0.06084447830648336</v>
       </c>
       <c r="W87">
-        <v>0.2212840822743351</v>
+        <v>0.2214528720153312</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3847518481145271</v>
+        <v>0.3802779894155209</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8842,22 +8842,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2501258474507737</v>
+        <v>0.2520258474507737</v>
       </c>
       <c r="C88">
-        <v>-1.13870951223068</v>
+        <v>-1.184677968355745</v>
       </c>
       <c r="D88">
-        <v>1.50641048776932</v>
+        <v>1.496362031644255</v>
       </c>
       <c r="E88">
-        <v>2.91712</v>
+        <v>2.95304</v>
       </c>
       <c r="F88">
-        <v>3.08912</v>
+        <v>3.12504</v>
       </c>
       <c r="G88">
         <v>0.444</v>
@@ -8878,37 +8878,37 @@
         <v>0.277</v>
       </c>
       <c r="M88">
-        <v>0.728414496</v>
+        <v>0.7368844320000001</v>
       </c>
       <c r="N88">
-        <v>-0.4514144959999999</v>
+        <v>-0.4598844320000001</v>
       </c>
       <c r="O88">
-        <v>-0.07222631936</v>
+        <v>-0.07358150912000001</v>
       </c>
       <c r="P88">
-        <v>-0.3791881766399999</v>
+        <v>-0.3863029228800001</v>
       </c>
       <c r="Q88">
-        <v>-0.2381881766399999</v>
+        <v>-0.2453029228800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4262598394113487</v>
+        <v>0.4555259809045293</v>
       </c>
       <c r="T88">
-        <v>5.237172896476527</v>
+        <v>5.640032350051644</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06084447830648336</v>
+        <v>0.0601451164868686</v>
       </c>
       <c r="W88">
-        <v>0.2214528720153312</v>
+        <v>0.2216177815323964</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3802779894155209</v>
+        <v>0.3759069780429287</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8924,22 +8924,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2520258474507737</v>
+        <v>0.2539258474507737</v>
       </c>
       <c r="C89">
-        <v>-1.184677968355745</v>
+        <v>-1.230513257050325</v>
       </c>
       <c r="D89">
-        <v>1.496362031644255</v>
+        <v>1.486446742949675</v>
       </c>
       <c r="E89">
-        <v>2.95304</v>
+        <v>2.98896</v>
       </c>
       <c r="F89">
-        <v>3.12504</v>
+        <v>3.16096</v>
       </c>
       <c r="G89">
         <v>0.444</v>
@@ -8960,37 +8960,37 @@
         <v>0.277</v>
       </c>
       <c r="M89">
-        <v>0.7368844320000001</v>
+        <v>0.7453543680000001</v>
       </c>
       <c r="N89">
-        <v>-0.4598844320000001</v>
+        <v>-0.4683543680000001</v>
       </c>
       <c r="O89">
-        <v>-0.07358150912000001</v>
+        <v>-0.07493669888000001</v>
       </c>
       <c r="P89">
-        <v>-0.3863029228800001</v>
+        <v>-0.3934176691200001</v>
       </c>
       <c r="Q89">
-        <v>-0.2453029228800001</v>
+        <v>-0.2524176691200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4555259809045293</v>
+        <v>0.4896698126465736</v>
       </c>
       <c r="T89">
-        <v>5.640032350051644</v>
+        <v>6.110035045889282</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0601451164868686</v>
+        <v>0.05946164925406328</v>
       </c>
       <c r="W89">
-        <v>0.2216177815323964</v>
+        <v>0.2217789431058919</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3759069780429287</v>
+        <v>0.3716353078378954</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9006,22 +9006,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2539258474507737</v>
+        <v>0.2558258474507737</v>
       </c>
       <c r="C90">
-        <v>-1.230513257050325</v>
+        <v>-1.276218008096135</v>
       </c>
       <c r="D90">
-        <v>1.486446742949675</v>
+        <v>1.476661991903866</v>
       </c>
       <c r="E90">
-        <v>2.98896</v>
+        <v>3.02488</v>
       </c>
       <c r="F90">
-        <v>3.16096</v>
+        <v>3.19688</v>
       </c>
       <c r="G90">
         <v>0.444</v>
@@ -9042,37 +9042,37 @@
         <v>0.277</v>
       </c>
       <c r="M90">
-        <v>0.7453543680000001</v>
+        <v>0.7538243040000001</v>
       </c>
       <c r="N90">
-        <v>-0.4683543680000001</v>
+        <v>-0.4768243040000001</v>
       </c>
       <c r="O90">
-        <v>-0.07493669888000001</v>
+        <v>-0.07629188864000001</v>
       </c>
       <c r="P90">
-        <v>-0.3934176691200001</v>
+        <v>-0.4005324153600001</v>
       </c>
       <c r="Q90">
-        <v>-0.2524176691200001</v>
+        <v>-0.25953241536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4896698126465736</v>
+        <v>0.530021613796262</v>
       </c>
       <c r="T90">
-        <v>6.110035045889282</v>
+        <v>6.665492777333762</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05946164925406328</v>
+        <v>0.05879354083547828</v>
       </c>
       <c r="W90">
-        <v>0.2217789431058919</v>
+        <v>0.2219364830709942</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3716353078378954</v>
+        <v>0.3674596302217393</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9088,22 +9088,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2558258474507737</v>
+        <v>0.2577258474507736</v>
       </c>
       <c r="C91">
-        <v>-1.276218008096135</v>
+        <v>-1.321794782484036</v>
       </c>
       <c r="D91">
-        <v>1.476661991903866</v>
+        <v>1.467005217515964</v>
       </c>
       <c r="E91">
-        <v>3.02488</v>
+        <v>3.0608</v>
       </c>
       <c r="F91">
-        <v>3.19688</v>
+        <v>3.2328</v>
       </c>
       <c r="G91">
         <v>0.444</v>
@@ -9124,37 +9124,37 @@
         <v>0.277</v>
       </c>
       <c r="M91">
-        <v>0.7538243040000001</v>
+        <v>0.76229424</v>
       </c>
       <c r="N91">
-        <v>-0.4768243040000001</v>
+        <v>-0.48529424</v>
       </c>
       <c r="O91">
-        <v>-0.07629188864000001</v>
+        <v>-0.0776470784</v>
       </c>
       <c r="P91">
-        <v>-0.4005324153600001</v>
+        <v>-0.4076471616</v>
       </c>
       <c r="Q91">
-        <v>-0.25953241536</v>
+        <v>-0.2666471616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.530021613796262</v>
+        <v>0.5784437751758883</v>
       </c>
       <c r="T91">
-        <v>6.665492777333762</v>
+        <v>7.33204205506714</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05879354083547828</v>
+        <v>0.05814027927063965</v>
       </c>
       <c r="W91">
-        <v>0.2219364830709942</v>
+        <v>0.2220905221479832</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3674596302217393</v>
+        <v>0.3633767454414978</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9170,22 +9170,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2577258474507736</v>
+        <v>0.2596258474507737</v>
       </c>
       <c r="C92">
-        <v>-1.321794782484036</v>
+        <v>-1.367246074648753</v>
       </c>
       <c r="D92">
-        <v>1.467005217515964</v>
+        <v>1.457473925351247</v>
       </c>
       <c r="E92">
-        <v>3.0608</v>
+        <v>3.09672</v>
       </c>
       <c r="F92">
-        <v>3.2328</v>
+        <v>3.26872</v>
       </c>
       <c r="G92">
         <v>0.444</v>
@@ -9206,37 +9206,37 @@
         <v>0.277</v>
       </c>
       <c r="M92">
-        <v>0.76229424</v>
+        <v>0.770764176</v>
       </c>
       <c r="N92">
-        <v>-0.48529424</v>
+        <v>-0.493764176</v>
       </c>
       <c r="O92">
-        <v>-0.0776470784</v>
+        <v>-0.07900226816</v>
       </c>
       <c r="P92">
-        <v>-0.4076471616</v>
+        <v>-0.41476190784</v>
       </c>
       <c r="Q92">
-        <v>-0.2666471616</v>
+        <v>-0.27376190784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5784437751758883</v>
+        <v>0.6376264168620983</v>
       </c>
       <c r="T92">
-        <v>7.33204205506714</v>
+        <v>8.146713394519047</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05814027927063965</v>
+        <v>0.05750137510283043</v>
       </c>
       <c r="W92">
-        <v>0.2220905221479832</v>
+        <v>0.2222411757507526</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3633767454414978</v>
+        <v>0.3593835943926901</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9252,22 +9252,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2596258474507737</v>
+        <v>0.2615258474507737</v>
       </c>
       <c r="C93">
-        <v>-1.367246074648753</v>
+        <v>-1.412574314617016</v>
       </c>
       <c r="D93">
-        <v>1.457473925351247</v>
+        <v>1.448065685382984</v>
       </c>
       <c r="E93">
-        <v>3.09672</v>
+        <v>3.13264</v>
       </c>
       <c r="F93">
-        <v>3.26872</v>
+        <v>3.30464</v>
       </c>
       <c r="G93">
         <v>0.444</v>
@@ -9288,37 +9288,37 @@
         <v>0.277</v>
       </c>
       <c r="M93">
-        <v>0.770764176</v>
+        <v>0.779234112</v>
       </c>
       <c r="N93">
-        <v>-0.493764176</v>
+        <v>-0.502234112</v>
       </c>
       <c r="O93">
-        <v>-0.07900226816</v>
+        <v>-0.08035745792</v>
       </c>
       <c r="P93">
-        <v>-0.41476190784</v>
+        <v>-0.42187665408</v>
       </c>
       <c r="Q93">
-        <v>-0.27376190784</v>
+        <v>-0.2808766540800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6376264168620983</v>
+        <v>0.7116047189698607</v>
       </c>
       <c r="T93">
-        <v>8.146713394519047</v>
+        <v>9.165052568833929</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05750137510283043</v>
+        <v>0.05687636015606052</v>
       </c>
       <c r="W93">
-        <v>0.2222411757507526</v>
+        <v>0.2223885542752009</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3593835943926901</v>
+        <v>0.3554772509753783</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9334,22 +9334,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2615258474507737</v>
+        <v>0.2634258474507737</v>
       </c>
       <c r="C94">
-        <v>-1.412574314617016</v>
+        <v>-1.457781870073063</v>
       </c>
       <c r="D94">
-        <v>1.448065685382984</v>
+        <v>1.438778129926938</v>
       </c>
       <c r="E94">
-        <v>3.13264</v>
+        <v>3.16856</v>
       </c>
       <c r="F94">
-        <v>3.30464</v>
+        <v>3.34056</v>
       </c>
       <c r="G94">
         <v>0.444</v>
@@ -9370,37 +9370,37 @@
         <v>0.277</v>
       </c>
       <c r="M94">
-        <v>0.779234112</v>
+        <v>0.7877040480000002</v>
       </c>
       <c r="N94">
-        <v>-0.502234112</v>
+        <v>-0.5107040480000001</v>
       </c>
       <c r="O94">
-        <v>-0.08035745792</v>
+        <v>-0.08171264768000003</v>
       </c>
       <c r="P94">
-        <v>-0.42187665408</v>
+        <v>-0.4289914003200001</v>
       </c>
       <c r="Q94">
-        <v>-0.2808766540800001</v>
+        <v>-0.2879914003200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7116047189698607</v>
+        <v>0.806719678822698</v>
       </c>
       <c r="T94">
-        <v>9.165052568833929</v>
+        <v>10.47434579295306</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05687636015606052</v>
+        <v>0.05626478639094159</v>
       </c>
       <c r="W94">
-        <v>0.2223885542752009</v>
+        <v>0.222532763369016</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3554772509753783</v>
+        <v>0.3516549149433849</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9416,22 +9416,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2634258474507737</v>
+        <v>0.2653258474507737</v>
       </c>
       <c r="C95">
-        <v>-1.457781870073063</v>
+        <v>-1.502871048345141</v>
       </c>
       <c r="D95">
-        <v>1.438778129926938</v>
+        <v>1.429608951654859</v>
       </c>
       <c r="E95">
-        <v>3.16856</v>
+        <v>3.20448</v>
       </c>
       <c r="F95">
-        <v>3.34056</v>
+        <v>3.37648</v>
       </c>
       <c r="G95">
         <v>0.444</v>
@@ -9452,37 +9452,37 @@
         <v>0.277</v>
       </c>
       <c r="M95">
-        <v>0.7877040480000002</v>
+        <v>0.7961739840000002</v>
       </c>
       <c r="N95">
-        <v>-0.5107040480000001</v>
+        <v>-0.5191739840000001</v>
       </c>
       <c r="O95">
-        <v>-0.08171264768000003</v>
+        <v>-0.08306783744000003</v>
       </c>
       <c r="P95">
-        <v>-0.4289914003200001</v>
+        <v>-0.4361061465600001</v>
       </c>
       <c r="Q95">
-        <v>-0.2879914003200001</v>
+        <v>-0.2951061465600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.806719678822698</v>
+        <v>0.9335396252931478</v>
       </c>
       <c r="T95">
-        <v>10.47434579295306</v>
+        <v>12.22007009177858</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05626478639094159</v>
+        <v>0.05566622483359114</v>
       </c>
       <c r="W95">
-        <v>0.222532763369016</v>
+        <v>0.2226739041842392</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3516549149433849</v>
+        <v>0.3479139052099446</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9498,22 +9498,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2653258474507737</v>
+        <v>0.2672258474507737</v>
       </c>
       <c r="C96">
-        <v>-1.502871048345141</v>
+        <v>-1.547844098316543</v>
       </c>
       <c r="D96">
-        <v>1.429608951654859</v>
+        <v>1.420555901683457</v>
       </c>
       <c r="E96">
-        <v>3.20448</v>
+        <v>3.2404</v>
       </c>
       <c r="F96">
-        <v>3.37648</v>
+        <v>3.4124</v>
       </c>
       <c r="G96">
         <v>0.444</v>
@@ -9534,37 +9534,37 @@
         <v>0.277</v>
       </c>
       <c r="M96">
-        <v>0.7961739840000002</v>
+        <v>0.8046439200000001</v>
       </c>
       <c r="N96">
-        <v>-0.5191739840000001</v>
+        <v>-0.52764392</v>
       </c>
       <c r="O96">
-        <v>-0.08306783744000003</v>
+        <v>-0.08442302720000001</v>
       </c>
       <c r="P96">
-        <v>-0.4361061465600001</v>
+        <v>-0.4432208928</v>
       </c>
       <c r="Q96">
-        <v>-0.2951061465600001</v>
+        <v>-0.3022208928000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9335396252931478</v>
+        <v>1.111087550351778</v>
       </c>
       <c r="T96">
-        <v>12.22007009177858</v>
+        <v>14.6640841101343</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05566622483359114</v>
+        <v>0.05508026457218493</v>
       </c>
       <c r="W96">
-        <v>0.2226739041842392</v>
+        <v>0.2228120736138788</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3479139052099446</v>
+        <v>0.3442516535761557</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9580,22 +9580,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2672258474507737</v>
+        <v>0.2691258474507737</v>
       </c>
       <c r="C97">
-        <v>-1.547844098316543</v>
+        <v>-1.592703212264484</v>
       </c>
       <c r="D97">
-        <v>1.420555901683457</v>
+        <v>1.411616787735517</v>
       </c>
       <c r="E97">
-        <v>3.2404</v>
+        <v>3.27632</v>
       </c>
       <c r="F97">
-        <v>3.4124</v>
+        <v>3.44832</v>
       </c>
       <c r="G97">
         <v>0.444</v>
@@ -9616,37 +9616,37 @@
         <v>0.277</v>
       </c>
       <c r="M97">
-        <v>0.8046439200000001</v>
+        <v>0.8131138560000001</v>
       </c>
       <c r="N97">
-        <v>-0.52764392</v>
+        <v>-0.5361138560000001</v>
       </c>
       <c r="O97">
-        <v>-0.08442302720000001</v>
+        <v>-0.08577821696000001</v>
       </c>
       <c r="P97">
-        <v>-0.4432208928</v>
+        <v>-0.4503356390400001</v>
       </c>
       <c r="Q97">
-        <v>-0.3022208928000001</v>
+        <v>-0.3093356390400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.111087550351778</v>
+        <v>1.377409437939723</v>
       </c>
       <c r="T97">
-        <v>14.6640841101343</v>
+        <v>18.33010513766788</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05508026457218493</v>
+        <v>0.05450651181622466</v>
       </c>
       <c r="W97">
-        <v>0.2228120736138788</v>
+        <v>0.2229473645137342</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3442516535761557</v>
+        <v>0.3406656988514042</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9662,22 +9662,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2691258474507737</v>
+        <v>0.2710258474507737</v>
       </c>
       <c r="C98">
-        <v>-1.592703212264483</v>
+        <v>-1.637450527629987</v>
       </c>
       <c r="D98">
-        <v>1.411616787735517</v>
+        <v>1.402789472370013</v>
       </c>
       <c r="E98">
-        <v>3.27632</v>
+        <v>3.31224</v>
       </c>
       <c r="F98">
-        <v>3.44832</v>
+        <v>3.48424</v>
       </c>
       <c r="G98">
         <v>0.444</v>
@@ -9698,37 +9698,37 @@
         <v>0.277</v>
       </c>
       <c r="M98">
-        <v>0.813113856</v>
+        <v>0.821583792</v>
       </c>
       <c r="N98">
-        <v>-0.5361138559999999</v>
+        <v>-0.544583792</v>
       </c>
       <c r="O98">
-        <v>-0.08577821695999999</v>
+        <v>-0.08713340672</v>
       </c>
       <c r="P98">
-        <v>-0.45033563904</v>
+        <v>-0.4574503852799999</v>
       </c>
       <c r="Q98">
-        <v>-0.3093356390399999</v>
+        <v>-0.3164503852799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.37740943793972</v>
+        <v>1.821279250586293</v>
       </c>
       <c r="T98">
-        <v>18.33010513766783</v>
+        <v>24.44014018355711</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05450651181622467</v>
+        <v>0.05394458901399556</v>
       </c>
       <c r="W98">
-        <v>0.2229473645137342</v>
+        <v>0.2230798659104999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3406656988514042</v>
+        <v>0.3371536813374721</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9744,22 +9744,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2710258474507737</v>
+        <v>0.2729258474507737</v>
       </c>
       <c r="C99">
-        <v>-1.637450527629987</v>
+        <v>-1.682088128721776</v>
       </c>
       <c r="D99">
-        <v>1.402789472370013</v>
+        <v>1.394071871278224</v>
       </c>
       <c r="E99">
-        <v>3.31224</v>
+        <v>3.34816</v>
       </c>
       <c r="F99">
-        <v>3.48424</v>
+        <v>3.52016</v>
       </c>
       <c r="G99">
         <v>0.444</v>
@@ -9780,37 +9780,37 @@
         <v>0.277</v>
       </c>
       <c r="M99">
-        <v>0.821583792</v>
+        <v>0.8300537280000001</v>
       </c>
       <c r="N99">
-        <v>-0.544583792</v>
+        <v>-0.5530537280000001</v>
       </c>
       <c r="O99">
-        <v>-0.08713340672</v>
+        <v>-0.08848859648000001</v>
       </c>
       <c r="P99">
-        <v>-0.4574503852799999</v>
+        <v>-0.4645651315200001</v>
       </c>
       <c r="Q99">
-        <v>-0.3164503852799999</v>
+        <v>-0.3235651315200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.821279250586293</v>
+        <v>2.709018875879439</v>
       </c>
       <c r="T99">
-        <v>24.44014018355711</v>
+        <v>36.66021027533566</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05394458901399556</v>
+        <v>0.05339413402405681</v>
       </c>
       <c r="W99">
-        <v>0.2230798659104999</v>
+        <v>0.2232096631971274</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3371536813374721</v>
+        <v>0.333713337650355</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9826,22 +9826,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2729258474507737</v>
+        <v>0.2748258474507737</v>
       </c>
       <c r="C100">
-        <v>-1.682088128721776</v>
+        <v>-1.726618048357022</v>
       </c>
       <c r="D100">
-        <v>1.394071871278224</v>
+        <v>1.385461951642978</v>
       </c>
       <c r="E100">
-        <v>3.34816</v>
+        <v>3.38408</v>
       </c>
       <c r="F100">
-        <v>3.52016</v>
+        <v>3.55608</v>
       </c>
       <c r="G100">
         <v>0.444</v>
@@ -9862,37 +9862,37 @@
         <v>0.277</v>
       </c>
       <c r="M100">
-        <v>0.8300537280000001</v>
+        <v>0.8385236640000001</v>
       </c>
       <c r="N100">
-        <v>-0.5530537280000001</v>
+        <v>-0.5615236640000001</v>
       </c>
       <c r="O100">
-        <v>-0.08848859648000001</v>
+        <v>-0.08984378624000001</v>
       </c>
       <c r="P100">
-        <v>-0.4645651315200001</v>
+        <v>-0.4716798777600001</v>
       </c>
       <c r="Q100">
-        <v>-0.3235651315200001</v>
+        <v>-0.3306798777600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.709018875879439</v>
+        <v>5.372237751758878</v>
       </c>
       <c r="T100">
-        <v>36.66021027533566</v>
+        <v>73.32042055067133</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05339413402405681</v>
+        <v>0.05285479933694513</v>
       </c>
       <c r="W100">
-        <v>0.2232096631971274</v>
+        <v>0.2233368383163483</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9900,91 +9900,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.333713337650355</v>
+        <v>0.330342495855907</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2748258474507737</v>
-      </c>
-      <c r="C101">
-        <v>-1.726618048357022</v>
-      </c>
-      <c r="D101">
-        <v>1.385461951642978</v>
-      </c>
-      <c r="E101">
-        <v>3.38408</v>
-      </c>
-      <c r="F101">
-        <v>3.55608</v>
-      </c>
-      <c r="G101">
-        <v>0.444</v>
-      </c>
-      <c r="H101">
-        <v>3.42</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.418</v>
-      </c>
-      <c r="K101">
-        <v>0.141</v>
-      </c>
-      <c r="L101">
-        <v>0.277</v>
-      </c>
-      <c r="M101">
-        <v>0.8385236640000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.5615236640000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.08984378624000001</v>
-      </c>
-      <c r="P101">
-        <v>-0.4716798777600001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.3306798777600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.372237751758878</v>
-      </c>
-      <c r="T101">
-        <v>73.32042055067133</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05285479933694513</v>
-      </c>
-      <c r="W101">
-        <v>0.2233368383163483</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.330342495855907</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
